--- a/奇遇/宠物奇遇_通用全部.xlsx
+++ b/奇遇/宠物奇遇_通用全部.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JX3\Game\JX3\bin\zhcn_hd\interface\MY#DATA\!all-users@zhcn_hd\userdata\team_mon\remote\打包\奇遇\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{7030F852-DB8F-4A64-8D98-B6FDF3126CF6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{6EA9A4A2-FEDF-497C-B3C7-52D47F2B85C2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="茗伊团队监控数据手册" sheetId="2" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="2803" uniqueCount="1992">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="2813" uniqueCount="1998">
   <si>
     <t>标识</t>
   </si>
@@ -4989,1321 +4989,1383 @@
     <t>0,255,255,</t>
   </si>
   <si>
+    <t>豪猪</t>
+  </si>
+  <si>
+    <t>赵小凯·孩童书</t>
+  </si>
+  <si>
+    <t>道知·烹调法</t>
+  </si>
+  <si>
+    <t>闰水·缘来会</t>
+  </si>
+  <si>
+    <t>查小娘·缘来会</t>
+  </si>
+  <si>
+    <t>横小五·蟹卒</t>
+  </si>
+  <si>
+    <t>幼小的蛤蟆·大哈</t>
+  </si>
+  <si>
+    <t>毛丝鼠·谜书生</t>
+  </si>
+  <si>
+    <t>苏拂衣·江湖录</t>
+  </si>
+  <si>
+    <t>步虚尘·白雪忆</t>
+  </si>
+  <si>
+    <t>果子狸·稻稻</t>
+  </si>
+  <si>
+    <t>老不知·红衣歌</t>
+  </si>
+  <si>
+    <t>红师农·尘网中</t>
+  </si>
+  <si>
+    <t>喜小乐·蟹兵</t>
+  </si>
+  <si>
+    <t>{nClass=3,nIcon=6110,nFrame=7,szName="蟹兵·三十二·八·四",nTime=20,key="蹲宠提示0",},</t>
+  </si>
+  <si>
+    <t>寄居蟹·蟹仔</t>
+  </si>
+  <si>
+    <t>猫猫·破晓鸣</t>
+  </si>
+  <si>
+    <t>秦邑·破晓鸣</t>
+  </si>
+  <si>
+    <t>马四·枫林酒</t>
+  </si>
+  <si>
+    <t>阮染·锻剑女</t>
+  </si>
+  <si>
+    <t>亭十四·归安志</t>
+  </si>
+  <si>
+    <t>刘理阳·归安志</t>
+  </si>
+  <si>
+    <t>小花·鸠雀记</t>
+  </si>
+  <si>
+    <t>林小明·大头鹅</t>
+  </si>
+  <si>
+    <t>杨悦·一念间</t>
+  </si>
+  <si>
+    <t>陶九翁·捉妖记</t>
+  </si>
+  <si>
+    <t>卢蓉·烟花戏</t>
+  </si>
+  <si>
+    <t>皮皮·白鹅</t>
+  </si>
+  <si>
+    <t>车山果·嘟嘟</t>
+  </si>
+  <si>
+    <t>康永浩·东海客</t>
+  </si>
+  <si>
+    <t>桩桩·沙海谣</t>
+  </si>
+  <si>
+    <t>田语夕·锋芒展</t>
+  </si>
+  <si>
+    <t>铸剑大师·归乡路</t>
+  </si>
+  <si>
+    <t>王厨娘·莫贪杯</t>
+  </si>
+  <si>
+    <t>沈笑颜·竹马情</t>
+  </si>
+  <si>
+    <t>苗淼尔·滇南行</t>
+  </si>
+  <si>
+    <t>查飞天·至尊宝</t>
+  </si>
+  <si>
+    <t>虚弱的小狗·哈皮</t>
+  </si>
+  <si>
+    <t>吴为有·石敢当</t>
+  </si>
+  <si>
+    <t>唐御御·烟花戏</t>
+  </si>
+  <si>
+    <t>密探·蟹将·蟹帅</t>
+  </si>
+  <si>
+    <t>阿貘·烟花戏</t>
+  </si>
+  <si>
+    <t>雨芒·烟花戏</t>
+  </si>
+  <si>
+    <t>惊恐的灰鹅·小灰</t>
+  </si>
+  <si>
+    <t>错错·枉叹恨</t>
+  </si>
+  <si>
+    <t>苏临渊·稚子心</t>
+  </si>
+  <si>
+    <t>李嫂·稚子心</t>
+  </si>
+  <si>
+    <t>连九醉·烟花戏</t>
+  </si>
+  <si>
+    <t>小静静</t>
+  </si>
+  <si>
+    <t>九隆神丐·荆轲刺</t>
+  </si>
+  <si>
+    <t>孟乌·瀛洲梦</t>
+  </si>
+  <si>
+    <t>南静·关外商</t>
+  </si>
+  <si>
+    <t>白芷沅·戎马边</t>
+  </si>
+  <si>
+    <t>阿秋·儿女事</t>
+  </si>
+  <si>
+    <t>王老道·碎片五·清茗经</t>
+  </si>
+  <si>
+    <t>李尘缘·碎片八·清茗经</t>
+  </si>
+  <si>
+    <t>航小婷·胜负局</t>
+  </si>
+  <si>
+    <t>刘安·风雨意</t>
+  </si>
+  <si>
+    <t>曙曙·风雨意</t>
+  </si>
+  <si>
+    <t>野马烈风·青草歌</t>
+  </si>
+  <si>
+    <t>神秘商人·沧海笛</t>
+  </si>
+  <si>
+    <t>沙木沙克·幽海牧</t>
+  </si>
+  <si>
+    <t>小叮当·北行镖</t>
+  </si>
+  <si>
+    <t>边澈·太行道</t>
+  </si>
+  <si>
+    <t>林云飞·露园事</t>
+  </si>
+  <si>
+    <t>火头僧·客江干</t>
+  </si>
+  <si>
+    <t>焦福贵·秘宝图</t>
+  </si>
+  <si>
+    <t>落单少侠·瀛洲梦</t>
+  </si>
+  <si>
+    <t>算命先生·话玄虚</t>
+  </si>
+  <si>
+    <t>绿头鸭·滴水恩</t>
+  </si>
+  <si>
+    <t>宋旅·路投石</t>
+  </si>
+  <si>
+    <t>曾莲·捉贼记</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="曾莲·捉贼记",nMaxDistance=20,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>泥鳅·一枝栖</t>
+  </si>
+  <si>
+    <t>刘山夕·念旧林</t>
+  </si>
+  <si>
+    <t>小肥花·重洋客</t>
+  </si>
+  <si>
+    <t>礼礼·乱红鸾</t>
+  </si>
+  <si>
+    <t>晒太阳·寓天涯</t>
+  </si>
+  <si>
+    <t>崔有恒·子夜歌</t>
+  </si>
+  <si>
+    <t>姜堰·授太平</t>
+  </si>
+  <si>
+    <t>逗逗·夜哀鸣</t>
+  </si>
+  <si>
+    <t>槲生·故岁辞</t>
+  </si>
+  <si>
+    <t>语音报警.物件进入</t>
+  </si>
+  <si>
+    <t>团队报警.物件进入</t>
+  </si>
+  <si>
+    <t>密聊报警.物件进入</t>
+  </si>
+  <si>
+    <t>中央报警.物件进入</t>
+  </si>
+  <si>
+    <t>头顶警报.物件进入</t>
+  </si>
+  <si>
+    <t>全屏泛光.物件进入</t>
+  </si>
+  <si>
+    <t>语音报警.物件离开</t>
+  </si>
+  <si>
+    <t>团队报警.物件离开</t>
+  </si>
+  <si>
+    <t>密聊报警.物件离开</t>
+  </si>
+  <si>
+    <t>中央报警.物件离开</t>
+  </si>
+  <si>
+    <t>return {DOODAD={</t>
+  </si>
+  <si>
+    <t>盆栽·燕啼松</t>
+  </si>
+  <si>
+    <t>散落的书页·孩童书</t>
+  </si>
+  <si>
+    <t>酒葫芦·小果</t>
+  </si>
+  <si>
+    <t>一本书·蟹马蓝</t>
+  </si>
+  <si>
+    <t>埋东西的痕迹·烟花戏</t>
+  </si>
+  <si>
+    <t>奇怪的土堆·归安志</t>
+  </si>
+  <si>
+    <t>苜蓿草·谜书生</t>
+  </si>
+  <si>
+    <t>带血的金钗·谜书生</t>
+  </si>
+  <si>
+    <t>几页书稿·江湖录</t>
+  </si>
+  <si>
+    <t>小土堆·小花</t>
+  </si>
+  <si>
+    <t>遗失的包裹·归安志</t>
+  </si>
+  <si>
+    <t>招牌菜·义千金</t>
+  </si>
+  <si>
+    <t>秘方·义千金</t>
+  </si>
+  <si>
+    <t>小泥娃娃·红衣歌</t>
+  </si>
+  <si>
+    <t>古旧的卷轴·归安志</t>
+  </si>
+  <si>
+    <t>诱捕的笼子·破晓鸣</t>
+  </si>
+  <si>
+    <t>一本书·蟹相</t>
+  </si>
+  <si>
+    <t>沙土堆·枫林酒</t>
+  </si>
+  <si>
+    <t>陈旧的宝盒·三山四海</t>
+  </si>
+  <si>
+    <t>一本书·蟹士</t>
+  </si>
+  <si>
+    <t>张老头的竹筐·归安志</t>
+  </si>
+  <si>
+    <t>落叶堆·鸠雀记</t>
+  </si>
+  <si>
+    <t>酒坛·捉妖记</t>
+  </si>
+  <si>
+    <t>藏着木头鱼的鱼篓·捉妖记</t>
+  </si>
+  <si>
+    <t>风筝·捉妖记</t>
+  </si>
+  <si>
+    <t>川芎·烟花戏</t>
+  </si>
+  <si>
+    <t>一本书·蟹车蓝</t>
+  </si>
+  <si>
+    <t>一盏青头草·嘟嘟</t>
+  </si>
+  <si>
+    <t>夏枯草·东海客</t>
+  </si>
+  <si>
+    <t>半本秘诀·尘网中</t>
+  </si>
+  <si>
+    <t>遗失的画纸·沙海谣</t>
+  </si>
+  <si>
+    <t>深色的沙土堆·锋芒展</t>
+  </si>
+  <si>
+    <t>四散的弩箭·锋芒展</t>
+  </si>
+  <si>
+    <t>篝火残骸·锋芒展</t>
+  </si>
+  <si>
+    <t>散落的刀兵·锋芒展</t>
+  </si>
+  <si>
+    <t>商队货物·锋芒展</t>
+  </si>
+  <si>
+    <t>冰凌雪莲·冰蓝花客</t>
+  </si>
+  <si>
+    <t>一本书·蟹仕</t>
+  </si>
+  <si>
+    <t>一本书·蟹车红</t>
+  </si>
+  <si>
+    <t>破旧的纸卷·小诺</t>
+  </si>
+  <si>
+    <t>泥沙堆·红羽大将军</t>
+  </si>
+  <si>
+    <t>一个闪闪发光的物件·竹马情</t>
+  </si>
+  <si>
+    <t>小土堆·滇南行</t>
+  </si>
+  <si>
+    <t>换颜草·滇南行</t>
+  </si>
+  <si>
+    <t>日记1·东海客</t>
+  </si>
+  <si>
+    <t>日记2·东海客</t>
+  </si>
+  <si>
+    <t>日记3·东海客</t>
+  </si>
+  <si>
+    <t>日记4·东海客</t>
+  </si>
+  <si>
+    <t>日记5·东海客</t>
+  </si>
+  <si>
+    <t>一本书·蟹砲</t>
+  </si>
+  <si>
+    <t>小土堆·商周客</t>
+  </si>
+  <si>
+    <t>一本书·蟹马红</t>
+  </si>
+  <si>
+    <t>一本书·蟹象</t>
+  </si>
+  <si>
+    <t>神秘书籍·至尊宝</t>
+  </si>
+  <si>
+    <t>空酒坛子·至尊宝</t>
+  </si>
+  <si>
+    <t>不起眼的小土堆·至尊宝</t>
+  </si>
+  <si>
+    <t>一本书·蟹炮</t>
+  </si>
+  <si>
+    <t>小土堆·石敢当</t>
+  </si>
+  <si>
+    <t>竹叶青·烟花戏</t>
+  </si>
+  <si>
+    <t>道旁墓碑·沧海笛</t>
+  </si>
+  <si>
+    <t>奇怪的包袱·阿里</t>
+  </si>
+  <si>
+    <t>情报箱·兽王佩</t>
+  </si>
+  <si>
+    <t>一个小包裹·小锦</t>
+  </si>
+  <si>
+    <t>士兵的包裹·阿飞</t>
+  </si>
+  <si>
+    <t>桃花枝·稚子心</t>
+  </si>
+  <si>
+    <t>银鱼·稚子心</t>
+  </si>
+  <si>
+    <t>猴儿酒·稚子心</t>
+  </si>
+  <si>
+    <t>春风酿·烟花戏</t>
+  </si>
+  <si>
+    <t>鱼篓·醉烟波</t>
+  </si>
+  <si>
+    <t>酒·醉烟波</t>
+  </si>
+  <si>
+    <t>元和的弩弓·乱世舞姬</t>
+  </si>
+  <si>
+    <t>紫金匣·乱世舞姬</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="紫金匣·乱世",nMaxDistance=50,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>坚果·果果</t>
+  </si>
+  <si>
+    <t>被抢夺的矿石箱·太行道</t>
+  </si>
+  <si>
+    <t>边澈的辎重箱·太行道</t>
+  </si>
+  <si>
+    <t>奇怪的土堆·碎片一·清茗经</t>
+  </si>
+  <si>
+    <t>密宗宝图碎片·四·清茗经</t>
+  </si>
+  <si>
+    <t>拜火教箱子·青草歌</t>
+  </si>
+  <si>
+    <t>寒泉岩·太行道</t>
+  </si>
+  <si>
+    <t>武器箱·露园事</t>
+  </si>
+  <si>
+    <t>陷阱·露园事</t>
+  </si>
+  <si>
+    <t>坑洞·露园事</t>
+  </si>
+  <si>
+    <t>野菜·客江干</t>
+  </si>
+  <si>
+    <t>无名侠士之墓·客江干</t>
+  </si>
+  <si>
+    <t>奇怪的雪堆·客江干</t>
+  </si>
+  <si>
+    <t>一桌酒席·风雨意</t>
+  </si>
+  <si>
+    <t>特地留的书信·风雨意</t>
+  </si>
+  <si>
+    <t>沉甸甸的木桶·秘宝图</t>
+  </si>
+  <si>
+    <t>兔子的尸体·念旧林</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="兔子的尸体·念旧林",nMaxDistance=50,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>水缸·滴水恩</t>
+  </si>
+  <si>
+    <t>死去的鱼虾·滴水恩</t>
+  </si>
+  <si>
+    <t>小土堆·话玄虚</t>
+  </si>
+  <si>
+    <t>功夫·路投石</t>
+  </si>
+  <si>
+    <t>白六娘的樱桃树·丹青记</t>
+  </si>
+  <si>
+    <t>妙妙椅·侠行</t>
+  </si>
+  <si>
+    <t>千丝绸·侠行</t>
+  </si>
+  <si>
+    <t>神机轮·侠行</t>
+  </si>
+  <si>
+    <t>货物堆·觅知音</t>
+  </si>
+  <si>
+    <t>兔子窝1·白月皎</t>
+  </si>
+  <si>
+    <t>兔子窝2·白月皎</t>
+  </si>
+  <si>
+    <t>兔子窝3·白月皎</t>
+  </si>
+  <si>
+    <t>散落的画作·白月皎</t>
+  </si>
+  <si>
+    <t>散落的日记·白月皎</t>
+  </si>
+  <si>
+    <t>虫穴·念旧林</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="虫穴·念旧林",nMaxDistance=20,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>渔具·重洋客</t>
+  </si>
+  <si>
+    <t>光圈·乱红鸾</t>
+  </si>
+  <si>
+    <t>海螺壳·寓天涯</t>
+  </si>
+  <si>
+    <t>莓莓·寓天涯</t>
+  </si>
+  <si>
+    <t>虹下之泉·子夜歌</t>
+  </si>
+  <si>
+    <t>光圈·夜哀鸣</t>
+  </si>
+  <si>
+    <t>止血草·夜哀鸣</t>
+  </si>
+  <si>
+    <t>甜果·夜哀鸣</t>
+  </si>
+  <si>
+    <t>槲果·故岁辞</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="槲果·故岁辞",nMaxDistance=30,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>散落的羽毛·故岁辞</t>
+  </si>
+  <si>
+    <t>光圈·故岁辞</t>
+  </si>
+  <si>
+    <t>鸟笼·故岁辞</t>
+  </si>
+  <si>
+    <t>树叶堆·解心语</t>
+  </si>
+  <si>
+    <t>光圈·解心语</t>
+  </si>
+  <si>
+    <t>酒杯·破巧言</t>
+  </si>
+  <si>
+    <t>包袱·破巧言</t>
+  </si>
+  <si>
+    <t>洞口·匿沙影</t>
+  </si>
+  <si>
+    <t>喊话内容</t>
+  </si>
+  <si>
+    <t>子串搜索</t>
+  </si>
+  <si>
+    <t>正则匹配</t>
+  </si>
+  <si>
+    <t>语音报警.喊话</t>
+  </si>
+  <si>
+    <t>团队报警.喊话</t>
+  </si>
+  <si>
+    <t>密聊警报.喊话</t>
+  </si>
+  <si>
+    <t>中央报警.喊话</t>
+  </si>
+  <si>
+    <t>头顶报警.喊话</t>
+  </si>
+  <si>
+    <t>全屏泛光.喊话</t>
+  </si>
+  <si>
+    <t>return {TALK={</t>
+  </si>
+  <si>
+    <t>return {CHAT={</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="查飞天·至尊宝",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>永宁湾</t>
+  </si>
+  <si>
+    <t>河西瀚漠</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>听潮·换房记</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="听潮·换房记",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>皇城</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>饲料堆·妖与狸</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="饲料堆·妖与狸",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>伊丽川</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>米迦尔·追光记</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="米迦尔·追光记",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘一竿·碗中仙</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="刘一竿·碗中仙",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>流民老奶奶·燕难归</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="流民老奶奶·燕难归",nMaxDistance=30,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>庞以松·童蒙志</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="庞以松·童蒙志",nMaxDistance=30,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>唐素娘·龟影锋</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="唐素娘·龟影锋",nMaxDistance=30,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="赵小凯·孩童书",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="道知·烹调法",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="闰水·缘来会",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="查小娘·缘来会",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="毛丝鼠·谜书生",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="苏拂衣·江湖录",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="步虚尘·白雪忆",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="老不知·红衣歌",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="红师农·尘网中",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="猫猫·破晓鸣",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="秦邑·破晓鸣",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="马四·枫林酒",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="阮染·锻剑女",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="亭十四·归安志",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="刘理阳·归安志",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="小花·鸠雀记",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="杨悦·一念间",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="陶九翁·捉妖记",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="卢蓉·烟花戏",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="车山果·嘟嘟",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="康永浩·东海客",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="桩桩·沙海谣",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="田语夕·锋芒展",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="铸剑大师·归乡路",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="王厨娘·莫贪杯",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="沈笑颜·竹马情",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="苗淼尔·滇南行",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="唐御御·烟花戏",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="阿貘·烟花戏",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="雨芒·烟花戏",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="错错·枉叹恨",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="苏临渊·稚子心",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="李嫂·稚子心",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="连九醉·烟花戏",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="九隆神丐·荆轲刺",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="孟乌·瀛洲梦",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="南静·关外商",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="白芷沅·戎马边",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="阿秋·儿女事",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="王老道·碎片五·清茗经",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="航小婷·胜负局",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="刘安·风雨意",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="曙曙·风雨意",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="野马烈风·青草歌",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="神秘商人·沧海笛",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="沙木沙克·幽海牧",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="边澈·太行道",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="林云飞·露园事",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="火头僧·客江干",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="焦福贵·秘宝图",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="落单少侠·瀛洲梦",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="算命先生·话玄虚",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="绿头鸭·滴水恩",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="宋旅·路投石",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="泥鳅·一枝栖",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="小肥花·重洋客",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="礼礼·乱红鸾",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="晒太阳·寓天涯",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="崔有恒·子夜歌",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="姜堰·授太平",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="逗逗·夜哀鸣",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="槲生·故岁辞",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
     <t>{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>豪猪</t>
-  </si>
-  <si>
-    <t>赵小凯·孩童书</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="赵小凯·孩童书",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>道知·烹调法</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="道知·烹调法",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>闰水·缘来会</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="闰水·缘来会",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>查小娘·缘来会</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="查小娘·缘来会",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>横小五·蟹卒</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>{dwMapID=-1,szDisplay="横小五·蟹卒",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>幼小的蛤蟆·大哈</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>{dwMapID=-1,szDisplay="幼小的蛤蟆·大哈",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>毛丝鼠·谜书生</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="毛丝鼠·谜书生",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>苏拂衣·江湖录</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="苏拂衣·江湖录",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>步虚尘·白雪忆</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="步虚尘·白雪忆",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>果子狸·稻稻</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>{dwMapID=-1,szDisplay="果子狸·稻稻",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>老不知·红衣歌</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="老不知·红衣歌",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>红师农·尘网中</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="红师农·尘网中",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>喜小乐·蟹兵</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>{dwMapID=-1,szDisplay="喜小乐·蟹兵",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>{nClass=3,nIcon=6110,nFrame=7,szName="蟹兵·三十二·八·四",nTime=20,key="蹲宠提示0",},</t>
-  </si>
-  <si>
-    <t>寄居蟹·蟹仔</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>{dwMapID=-1,szDisplay="寄居蟹·蟹仔",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>猫猫·破晓鸣</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="猫猫·破晓鸣",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>秦邑·破晓鸣</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="秦邑·破晓鸣",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>马四·枫林酒</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="马四·枫林酒",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>阮染·锻剑女</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="阮染·锻剑女",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>亭十四·归安志</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="亭十四·归安志",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>刘理阳·归安志</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="刘理阳·归安志",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>小花·鸠雀记</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="小花·鸠雀记",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>林小明·大头鹅</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>{dwMapID=-1,szDisplay="林小明·大头鹅",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>杨悦·一念间</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="杨悦·一念间",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>陶九翁·捉妖记</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="陶九翁·捉妖记",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>卢蓉·烟花戏</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="卢蓉·烟花戏",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>皮皮·白鹅</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>{dwMapID=-1,szDisplay="皮皮·白鹅",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>车山果·嘟嘟</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="车山果·嘟嘟",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>康永浩·东海客</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="康永浩·东海客",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>桩桩·沙海谣</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="桩桩·沙海谣",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>田语夕·锋芒展</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="田语夕·锋芒展",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>铸剑大师·归乡路</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="铸剑大师·归乡路",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>王厨娘·莫贪杯</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="王厨娘·莫贪杯",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>沈笑颜·竹马情</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="沈笑颜·竹马情",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>苗淼尔·滇南行</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="苗淼尔·滇南行",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>查飞天·至尊宝</t>
-  </si>
-  <si>
-    <t>虚弱的小狗·哈皮</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>{dwMapID=-1,szDisplay="虚弱的小狗·哈皮",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>吴为有·石敢当</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="吴为有·石敢当",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>唐御御·烟花戏</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="唐御御·烟花戏",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>密探·蟹将·蟹帅</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="吴为有·石敢当",nMaxDistance=120,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>{dwMapID=-1,szDisplay="密探·蟹将·蟹帅",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>阿貘·烟花戏</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="阿貘·烟花戏",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>雨芒·烟花戏</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="雨芒·烟花戏",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>惊恐的灰鹅·小灰</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>{dwMapID=-1,szDisplay="惊恐的灰鹅·小灰",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>错错·枉叹恨</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="错错·枉叹恨",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>苏临渊·稚子心</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="苏临渊·稚子心",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>李嫂·稚子心</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="李嫂·稚子心",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>连九醉·烟花戏</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="连九醉·烟花戏",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>小静静</t>
-  </si>
-  <si>
-    <t>九隆神丐·荆轲刺</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="九隆神丐·荆轲刺",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>孟乌·瀛洲梦</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="孟乌·瀛洲梦",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>南静·关外商</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="南静·关外商",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>白芷沅·戎马边</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="白芷沅·戎马边",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>庞以松·童蒙志</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="庞以松·童蒙志",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>阿秋·儿女事</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="阿秋·儿女事",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>王老道·碎片五·清茗经</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="王老道·碎片五·清茗经",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>李尘缘·碎片八·清茗经</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="李尘缘·碎片八·清茗经",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>航小婷·胜负局</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="航小婷·胜负局",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>刘安·风雨意</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="刘安·风雨意",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>曙曙·风雨意</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="曙曙·风雨意",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>野马烈风·青草歌</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="野马烈风·青草歌",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>神秘商人·沧海笛</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="神秘商人·沧海笛",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>沙木沙克·幽海牧</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="沙木沙克·幽海牧",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>小叮当·北行镖</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="李尘缘·碎片八·清茗经",nMaxDistance=90,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>{dwMapID=-1,szDisplay="小叮当·北行镖",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>边澈·太行道</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="边澈·太行道",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>林云飞·露园事</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="林云飞·露园事",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>火头僧·客江干</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="火头僧·客江干",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>焦福贵·秘宝图</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="焦福贵·秘宝图",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>落单少侠·瀛洲梦</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="落单少侠·瀛洲梦",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>算命先生·话玄虚</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="算命先生·话玄虚",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>绿头鸭·滴水恩</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="绿头鸭·滴水恩",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>宋旅·路投石</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="宋旅·路投石",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>曾莲·捉贼记</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="曾莲·捉贼记",nMaxDistance=20,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>泥鳅·一枝栖</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="泥鳅·一枝栖",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>刘山夕·念旧林</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="刘山夕·念旧林",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>小肥花·重洋客</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="小肥花·重洋客",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>礼礼·乱红鸾</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="礼礼·乱红鸾",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>晒太阳·寓天涯</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="晒太阳·寓天涯",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>崔有恒·子夜歌</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="崔有恒·子夜歌",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>姜堰·授太平</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="姜堰·授太平",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>逗逗·夜哀鸣</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="逗逗·夜哀鸣",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>槲生·故岁辞</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="槲生·故岁辞",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>语音报警.物件进入</t>
-  </si>
-  <si>
-    <t>团队报警.物件进入</t>
-  </si>
-  <si>
-    <t>密聊报警.物件进入</t>
-  </si>
-  <si>
-    <t>中央报警.物件进入</t>
-  </si>
-  <si>
-    <t>头顶警报.物件进入</t>
-  </si>
-  <si>
-    <t>全屏泛光.物件进入</t>
-  </si>
-  <si>
-    <t>语音报警.物件离开</t>
-  </si>
-  <si>
-    <t>团队报警.物件离开</t>
-  </si>
-  <si>
-    <t>密聊报警.物件离开</t>
-  </si>
-  <si>
-    <t>中央报警.物件离开</t>
-  </si>
-  <si>
-    <t>return {DOODAD={</t>
-  </si>
-  <si>
-    <t>盆栽·燕啼松</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="盆栽·燕啼松",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>散落的书页·孩童书</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="散落的书页·孩童书",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>酒葫芦·小果</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="盆栽·燕啼松",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="散落的书页·孩童书",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="埋东西的痕迹·烟花戏",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="奇怪的土堆·归安志",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="苜蓿草·谜书生",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="带血的金钗·谜书生",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="几页书稿·江湖录",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="遗失的包裹·归安志",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="招牌菜·义千金",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="秘方·义千金",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="小泥娃娃·红衣歌",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="古旧的卷轴·归安志",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="诱捕的笼子·破晓鸣",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="沙土堆·枫林酒",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="陈旧的宝盒·三山",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="张老头的竹筐·归安志",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="落叶堆·鸠雀记",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="酒坛·捉妖记",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="藏木头鱼的鱼篓·捉妖记",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="风筝·捉妖记",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="川芎·烟花戏",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="一盏青头草·嘟嘟",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="夏枯草·东海客",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="半本秘诀·尘网中",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="遗失的画纸·沙海谣",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="深色的沙土堆·锋芒展",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="四散的弩箭·锋芒展",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="篝火残骸·锋芒展",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="散落的刀兵·锋芒展",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="商队货物·锋芒展",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="闪闪发光的物件·竹马情",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="小土堆·滇南行",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="换颜草·滇南行",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="日记1·东海客",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="日记2·东海客",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="日记3·东海客",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="日记4·东海客",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="日记5·东海客",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="神秘书籍·至尊宝",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="空酒坛子·至尊宝",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="不起眼的小土堆·至尊宝",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="小土堆·石敢当",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="竹叶青·烟花戏",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="道旁墓碑·沧海笛",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="情报箱·兽王佩",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="桃花枝·稚子心",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="银鱼·稚子心",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="猴儿酒·稚子心",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="春风酿·烟花戏",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="鱼篓·醉烟波",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="酒·醉烟波",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="元和的弩弓·乱世",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="被抢夺的矿石箱·太行道",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="边澈的辎重箱·太行道",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="土堆·碎片一·清茗经",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="拜火教箱子·青草歌",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="寒泉岩·太行道",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="武器箱·露园事",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="陷阱·露园事",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="坑洞·露园事",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="野菜·客江干",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="无名侠士之墓·客江干",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="奇怪的雪堆·客江干",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="一桌酒席·风雨意",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="特地留的书信·风雨意",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="沉甸甸的木桶·秘宝图",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="水缸·滴水恩",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="死去的鱼虾·滴水恩",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="小土堆·话玄虚",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="功夫·路投石",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="白六娘的樱桃树·丹青记",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="妙妙椅·侠行",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="千丝绸·侠行",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="神机轮·侠行",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="货物堆·觅知音",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="兔子窝1·白月皎",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="兔子窝2·白月皎",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="兔子窝3·白月皎",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="散落的画作·白月皎",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="散落的日记·白月皎",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="渔具·重洋客",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="光圈·乱红鸾",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="海螺壳·寓天涯",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="莓莓·寓天涯",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="虹下之泉·子夜歌",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="光圈·夜哀鸣",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="止血草·夜哀鸣",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="甜果·夜哀鸣",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="散落的羽毛·故岁辞",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="光圈·故岁辞",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="鸟笼·故岁辞",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="树叶堆·解心语",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="光圈·解心语",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="酒杯·破巧言",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="包袱·破巧言",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="洞口·匿沙影",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
   </si>
   <si>
     <t>{dwMapID=-1,szDisplay="酒葫芦·小果",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>一本书·蟹马蓝</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>{dwMapID=-1,szDisplay="一本书·蟹马蓝",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>埋东西的痕迹·烟花戏</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="埋东西的痕迹·烟花戏",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>奇怪的土堆·归安志</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="奇怪的土堆·归安志",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>苜蓿草·谜书生</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="苜蓿草·谜书生",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>带血的金钗·谜书生</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="带血的金钗·谜书生",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>几页书稿·江湖录</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="几页书稿·江湖录",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>小土堆·小花</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="小土堆·小花",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>遗失的包裹·归安志</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="遗失的包裹·归安志",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>招牌菜·义千金</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="招牌菜·义千金",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>秘方·义千金</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="秘方·义千金",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>小泥娃娃·红衣歌</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="小泥娃娃·红衣歌",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>古旧的卷轴·归安志</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="古旧的卷轴·归安志",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>诱捕的笼子·破晓鸣</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="诱捕的笼子·破晓鸣",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>一本书·蟹相</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="小土堆·小花",nMaxDistance=120,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>{dwMapID=-1,szDisplay="一本书·蟹相",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>沙土堆·枫林酒</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="沙土堆·枫林酒",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>陈旧的宝盒·三山四海</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="陈旧的宝盒·三山",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>一本书·蟹士</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>{dwMapID=-1,szDisplay="一本书·蟹士",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>张老头的竹筐·归安志</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="张老头的竹筐·归安志",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>落叶堆·鸠雀记</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="落叶堆·鸠雀记",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>酒坛·捉妖记</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="酒坛·捉妖记",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>藏着木头鱼的鱼篓·捉妖记</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="藏木头鱼的鱼篓·捉妖记",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>风筝·捉妖记</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="风筝·捉妖记",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>川芎·烟花戏</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="川芎·烟花戏",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>一本书·蟹车蓝</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>{dwMapID=-1,szDisplay="一本书·蟹车蓝",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>一盏青头草·嘟嘟</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="一盏青头草·嘟嘟",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>夏枯草·东海客</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="夏枯草·东海客",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>半本秘诀·尘网中</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="半本秘诀·尘网中",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>遗失的画纸·沙海谣</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="遗失的画纸·沙海谣",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>深色的沙土堆·锋芒展</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="深色的沙土堆·锋芒展",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>四散的弩箭·锋芒展</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="四散的弩箭·锋芒展",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>篝火残骸·锋芒展</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="篝火残骸·锋芒展",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>散落的刀兵·锋芒展</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="散落的刀兵·锋芒展",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>商队货物·锋芒展</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="商队货物·锋芒展",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>冰凌雪莲·冰蓝花客</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="冰凌雪莲·冰蓝花客",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>一本书·蟹仕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="冰凌雪莲·冰蓝花客",nMaxDistance=120,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>{dwMapID=-1,szDisplay="一本书·蟹仕",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>一本书·蟹车红</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>{dwMapID=-1,szDisplay="一本书·蟹车红",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>破旧的纸卷·小诺</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>{dwMapID=-1,szDisplay="破旧的纸卷·小诺",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>泥沙堆·红羽大将军</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>{dwMapID=-1,szDisplay="泥沙堆·红羽大将军",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>一个闪闪发光的物件·竹马情</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="闪闪发光的物件·竹马情",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>小土堆·滇南行</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="小土堆·滇南行",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>换颜草·滇南行</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="换颜草·滇南行",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>日记1·东海客</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="日记1·东海客",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>日记2·东海客</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="日记2·东海客",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>日记3·东海客</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="日记3·东海客",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>日记4·东海客</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="日记4·东海客",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>日记5·东海客</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="日记5·东海客",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>一本书·蟹砲</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>{dwMapID=-1,szDisplay="一本书·蟹砲",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>小土堆·商周客</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>{dwMapID=-1,szDisplay="小土堆·商周客",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>一本书·蟹马红</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>{dwMapID=-1,szDisplay="一本书·蟹马红",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>一本书·蟹象</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>{dwMapID=-1,szDisplay="一本书·蟹象",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>神秘书籍·至尊宝</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="神秘书籍·至尊宝",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>空酒坛子·至尊宝</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="空酒坛子·至尊宝",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>不起眼的小土堆·至尊宝</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="不起眼的小土堆·至尊宝",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>一本书·蟹炮</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>{dwMapID=-1,szDisplay="一本书·蟹炮",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>小土堆·石敢当</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="小土堆·石敢当",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>竹叶青·烟花戏</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="竹叶青·烟花戏",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>道旁墓碑·沧海笛</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="道旁墓碑·沧海笛",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>奇怪的包袱·阿里</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>{dwMapID=-1,szDisplay="奇怪的包袱·阿里",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>情报箱·兽王佩</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="情报箱·兽王佩",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>一个小包裹·小锦</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>{dwMapID=-1,szDisplay="一个小包裹·小锦",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>士兵的包裹·阿飞</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>{dwMapID=-1,szDisplay="士兵的包裹·阿飞",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>桃花枝·稚子心</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="桃花枝·稚子心",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>银鱼·稚子心</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="银鱼·稚子心",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>猴儿酒·稚子心</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="猴儿酒·稚子心",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>春风酿·烟花戏</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="春风酿·烟花戏",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>鱼篓·醉烟波</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="鱼篓·醉烟波",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>酒·醉烟波</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="酒·醉烟波",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>元和的弩弓·乱世舞姬</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="元和的弩弓·乱世",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>紫金匣·乱世舞姬</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="紫金匣·乱世",nMaxDistance=50,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>坚果·果果</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>{dwMapID=-1,szDisplay="坚果·果果",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>被抢夺的矿石箱·太行道</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="被抢夺的矿石箱·太行道",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>边澈的辎重箱·太行道</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="边澈的辎重箱·太行道",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>奇怪的土堆·碎片一·清茗经</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="土堆·碎片一·清茗经",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>密宗宝图碎片·四·清茗经</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>{dwMapID=-1,szDisplay="密宗宝图碎片四·清茗经",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>拜火教箱子·青草歌</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="拜火教箱子·青草歌",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>寒泉岩·太行道</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="寒泉岩·太行道",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>武器箱·露园事</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="武器箱·露园事",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>陷阱·露园事</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="陷阱·露园事",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>坑洞·露园事</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="坑洞·露园事",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>野菜·客江干</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="野菜·客江干",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>无名侠士之墓·客江干</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="无名侠士之墓·客江干",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>奇怪的雪堆·客江干</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="奇怪的雪堆·客江干",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>一桌酒席·风雨意</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="一桌酒席·风雨意",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>特地留的书信·风雨意</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="特地留的书信·风雨意",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>沉甸甸的木桶·秘宝图</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="沉甸甸的木桶·秘宝图",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>兔子的尸体·念旧林</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="兔子的尸体·念旧林",nMaxDistance=50,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>水缸·滴水恩</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="水缸·滴水恩",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>死去的鱼虾·滴水恩</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="死去的鱼虾·滴水恩",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>小土堆·话玄虚</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="小土堆·话玄虚",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>功夫·路投石</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="功夫·路投石",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>白六娘的樱桃树·丹青记</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="白六娘的樱桃树·丹青记",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>妙妙椅·侠行</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="妙妙椅·侠行",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>千丝绸·侠行</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="千丝绸·侠行",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>神机轮·侠行</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="神机轮·侠行",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>货物堆·觅知音</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="货物堆·觅知音",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>兔子窝1·白月皎</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="兔子窝1·白月皎",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>兔子窝2·白月皎</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="兔子窝2·白月皎",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>兔子窝3·白月皎</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="兔子窝3·白月皎",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>散落的画作·白月皎</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="散落的画作·白月皎",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>散落的日记·白月皎</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="散落的日记·白月皎",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>虫穴·念旧林</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="虫穴·念旧林",nMaxDistance=20,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>渔具·重洋客</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="渔具·重洋客",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>光圈·乱红鸾</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="光圈·乱红鸾",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>海螺壳·寓天涯</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="海螺壳·寓天涯",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>莓莓·寓天涯</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="莓莓·寓天涯",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>虹下之泉·子夜歌</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="虹下之泉·子夜歌",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>光圈·夜哀鸣</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="光圈·夜哀鸣",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>止血草·夜哀鸣</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="止血草·夜哀鸣",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>甜果·夜哀鸣</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="甜果·夜哀鸣",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>槲果·故岁辞</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="槲果·故岁辞",nMaxDistance=30,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>散落的羽毛·故岁辞</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="散落的羽毛·故岁辞",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>光圈·故岁辞</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="光圈·故岁辞",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>鸟笼·故岁辞</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="鸟笼·故岁辞",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>树叶堆·解心语</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="树叶堆·解心语",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>光圈·解心语</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="光圈·解心语",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>酒杯·破巧言</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="酒杯·破巧言",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>包袱·破巧言</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="包袱·破巧言",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>洞口·匿沙影</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="洞口·匿沙影",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-  </si>
-  <si>
-    <t>喊话内容</t>
-  </si>
-  <si>
-    <t>子串搜索</t>
-  </si>
-  <si>
-    <t>正则匹配</t>
-  </si>
-  <si>
-    <t>语音报警.喊话</t>
-  </si>
-  <si>
-    <t>团队报警.喊话</t>
-  </si>
-  <si>
-    <t>密聊警报.喊话</t>
-  </si>
-  <si>
-    <t>中央报警.喊话</t>
-  </si>
-  <si>
-    <t>头顶报警.喊话</t>
-  </si>
-  <si>
-    <t>全屏泛光.喊话</t>
-  </si>
-  <si>
-    <t>return {TALK={</t>
-  </si>
-  <si>
-    <t>return {CHAT={</t>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="查飞天·至尊宝",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>永宁湾</t>
-  </si>
-  <si>
-    <t>河西瀚漠</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>听潮·换房记</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="听潮·换房记",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>皇城</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>饲料堆·妖与狸</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="饲料堆·妖与狸",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>伊丽川</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>米迦尔·追光记</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{dwMapID=-1,szDisplay="米迦尔·追光记",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{dwMapID=-1,szDisplay="刘山夕·念旧林",nMaxDistance=120,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -7552,7 +7614,7 @@
     <row r="4" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A4" s="21" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1762067816380,</v>
+        <v>nTimeStamp = 1776955274450,</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>36</v>
@@ -17876,8 +17938,11 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B46870D8-A68E-4D61-AE2C-F45A527F02B0}">
-  <dimension ref="A1:X140"/>
+  <dimension ref="A1:X144"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="9" max="9" width="18.75" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
@@ -17961,7 +18026,7 @@
         <v>-15</v>
       </c>
       <c r="W2" t="str">
-        <f t="shared" ref="W2:W33" si="0">IF(ISBLANK(B2)=FALSE,IF(ISBLANK(B1),"},["&amp;B2&amp;"]={","["&amp;B2&amp;"]={"),IF(AND(ISBLANK(B2),ISBLANK(D2),ISBLANK(C2),OR(ISBLANK(B1)=FALSE,ISBLANK(D1)=FALSE,ISBLANK(C1)=FALSE)),"},},}",IF(ISBLANK(C2),"","{dwID="&amp;C2&amp;","&amp;"nFrame="&amp;D2&amp;","&amp;IF(E2&gt;0,"nCount="&amp;E2&amp;",","")&amp;IF(F2&gt;0,"bAllLeave=true,","")&amp;IF(G2&lt;&gt;"","szName="""&amp;G2&amp;""",","")&amp;IF(H2&lt;&gt;"","tKungFu={"&amp;H2&amp;"},","")&amp;IF(I2&lt;&gt;"","szNote="""&amp;I2&amp;""",","")&amp;IF(J2&lt;&gt;"","col={"&amp;J2&amp;"},","")&amp;"[3]={"&amp;IF(K2&lt;&gt;"","tMark={"&amp;K2&amp;"},","")&amp;IF(L2&lt;&gt;"","szVoice="""&amp;L2&amp;""",","")&amp;IF(M2&gt;0,"bTeamChannel=true,","")&amp;IF(N2&gt;0,"bWhisperChannel=true,","")&amp;IF(O2&gt;0,"bCenterAlarm=true,","")&amp;IF(P2&gt;0,"bScreenHead=true,","")&amp;IF(Q2&gt;0,"bFullScreen=true,","")&amp;"},"&amp;"[4]={"&amp;IF(R2&lt;&gt;"","szVoice="""&amp;R2&amp;""",","")&amp;IF(S2&gt;0,"bTeamChannel=true,","")&amp;IF(T2&gt;0,"bWhisperChannel=true,","")&amp;IF(U2&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(V2&lt;&gt;"","aFocus={"&amp;V2&amp;"},","")&amp;IF(X2&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,X2:AAA2)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" ref="W2:W65" si="0">IF(ISBLANK(B2)=FALSE,IF(ISBLANK(B1),"},["&amp;B2&amp;"]={","["&amp;B2&amp;"]={"),IF(AND(ISBLANK(B2),ISBLANK(D2),ISBLANK(C2),OR(ISBLANK(B1)=FALSE,ISBLANK(D1)=FALSE,ISBLANK(C1)=FALSE)),"},},}",IF(ISBLANK(C2),"","{dwID="&amp;C2&amp;","&amp;"nFrame="&amp;D2&amp;","&amp;IF(E2&gt;0,"nCount="&amp;E2&amp;",","")&amp;IF(F2&gt;0,"bAllLeave=true,","")&amp;IF(G2&lt;&gt;"","szName="""&amp;G2&amp;""",","")&amp;IF(H2&lt;&gt;"","tKungFu={"&amp;H2&amp;"},","")&amp;IF(I2&lt;&gt;"","szNote="""&amp;I2&amp;""",","")&amp;IF(J2&lt;&gt;"","col={"&amp;J2&amp;"},","")&amp;"[3]={"&amp;IF(K2&lt;&gt;"","tMark={"&amp;K2&amp;"},","")&amp;IF(L2&lt;&gt;"","szVoice="""&amp;L2&amp;""",","")&amp;IF(M2&gt;0,"bTeamChannel=true,","")&amp;IF(N2&gt;0,"bWhisperChannel=true,","")&amp;IF(O2&gt;0,"bCenterAlarm=true,","")&amp;IF(P2&gt;0,"bScreenHead=true,","")&amp;IF(Q2&gt;0,"bFullScreen=true,","")&amp;"},"&amp;"[4]={"&amp;IF(R2&lt;&gt;"","szVoice="""&amp;R2&amp;""",","")&amp;IF(S2&gt;0,"bTeamChannel=true,","")&amp;IF(T2&gt;0,"bWhisperChannel=true,","")&amp;IF(U2&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(V2&lt;&gt;"","aFocus={"&amp;V2&amp;"},","")&amp;IF(X2&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,X2:AAA2)&amp;"},","")&amp;"},")))</f>
         <v>[-15]={</v>
       </c>
     </row>
@@ -17982,7 +18047,7 @@
         <v>1</v>
       </c>
       <c r="V3" t="s">
-        <v>1556</v>
+        <v>1866</v>
       </c>
       <c r="W3" t="str">
         <f t="shared" si="0"/>
@@ -17997,7 +18062,7 @@
         <v>47</v>
       </c>
       <c r="I4" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="J4" t="s">
         <v>1555</v>
@@ -18006,7 +18071,7 @@
         <v>1</v>
       </c>
       <c r="V4" t="s">
-        <v>1556</v>
+        <v>1866</v>
       </c>
       <c r="W4" t="str">
         <f t="shared" si="0"/>
@@ -18033,7 +18098,7 @@
         <v>47</v>
       </c>
       <c r="I6" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="J6" t="s">
         <v>1555</v>
@@ -18042,11 +18107,11 @@
         <v>1</v>
       </c>
       <c r="V6" t="s">
-        <v>1559</v>
+        <v>1804</v>
       </c>
       <c r="W6" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=48105,nFrame=47,szNote="赵小凯·孩童书",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="赵小凯·孩童书",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=48105,nFrame=47,szNote="赵小凯·孩童书",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="赵小凯·孩童书",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.15">
@@ -18069,7 +18134,7 @@
         <v>47</v>
       </c>
       <c r="I8" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="J8" t="s">
         <v>1555</v>
@@ -18078,11 +18143,11 @@
         <v>1</v>
       </c>
       <c r="V8" t="s">
-        <v>1561</v>
+        <v>1805</v>
       </c>
       <c r="W8" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=58137,nFrame=47,szNote="道知·烹调法",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="道知·烹调法",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=58137,nFrame=47,szNote="道知·烹调法",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="道知·烹调法",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.15">
@@ -18093,7 +18158,7 @@
         <v>47</v>
       </c>
       <c r="I9" t="s">
-        <v>1562</v>
+        <v>1559</v>
       </c>
       <c r="J9" t="s">
         <v>1555</v>
@@ -18102,11 +18167,11 @@
         <v>1</v>
       </c>
       <c r="V9" t="s">
-        <v>1563</v>
+        <v>1806</v>
       </c>
       <c r="W9" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=68983,nFrame=47,szNote="闰水·缘来会",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="闰水·缘来会",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=68983,nFrame=47,szNote="闰水·缘来会",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="闰水·缘来会",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.15">
@@ -18117,7 +18182,7 @@
         <v>47</v>
       </c>
       <c r="I10" t="s">
-        <v>1564</v>
+        <v>1560</v>
       </c>
       <c r="J10" t="s">
         <v>1555</v>
@@ -18126,11 +18191,11 @@
         <v>1</v>
       </c>
       <c r="V10" t="s">
-        <v>1565</v>
+        <v>1807</v>
       </c>
       <c r="W10" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=68984,nFrame=47,szNote="查小娘·缘来会",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="查小娘·缘来会",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=68984,nFrame=47,szNote="查小娘·缘来会",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="查小娘·缘来会",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.15">
@@ -18153,7 +18218,7 @@
         <v>47</v>
       </c>
       <c r="I12" t="s">
-        <v>1566</v>
+        <v>1561</v>
       </c>
       <c r="J12" t="s">
         <v>1555</v>
@@ -18165,7 +18230,7 @@
         <v>1</v>
       </c>
       <c r="V12" t="s">
-        <v>1567</v>
+        <v>1867</v>
       </c>
       <c r="W12" t="str">
         <f t="shared" si="0"/>
@@ -18180,7 +18245,7 @@
         <v>47</v>
       </c>
       <c r="I13" t="s">
-        <v>1568</v>
+        <v>1562</v>
       </c>
       <c r="J13" t="s">
         <v>1555</v>
@@ -18192,7 +18257,7 @@
         <v>1</v>
       </c>
       <c r="V13" t="s">
-        <v>1569</v>
+        <v>1868</v>
       </c>
       <c r="W13" t="str">
         <f t="shared" si="0"/>
@@ -18207,7 +18272,7 @@
         <v>47</v>
       </c>
       <c r="I14" t="s">
-        <v>1570</v>
+        <v>1563</v>
       </c>
       <c r="J14" t="s">
         <v>1555</v>
@@ -18216,11 +18281,11 @@
         <v>1</v>
       </c>
       <c r="V14" t="s">
-        <v>1571</v>
+        <v>1808</v>
       </c>
       <c r="W14" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=65896,nFrame=47,szNote="毛丝鼠·谜书生",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="毛丝鼠·谜书生",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=65896,nFrame=47,szNote="毛丝鼠·谜书生",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="毛丝鼠·谜书生",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.15">
@@ -18231,7 +18296,7 @@
         <v>47</v>
       </c>
       <c r="I15" t="s">
-        <v>1572</v>
+        <v>1564</v>
       </c>
       <c r="J15" t="s">
         <v>1555</v>
@@ -18240,11 +18305,11 @@
         <v>1</v>
       </c>
       <c r="V15" t="s">
-        <v>1573</v>
+        <v>1809</v>
       </c>
       <c r="W15" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=69036,nFrame=47,szNote="苏拂衣·江湖录",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="苏拂衣·江湖录",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=69036,nFrame=47,szNote="苏拂衣·江湖录",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="苏拂衣·江湖录",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.15">
@@ -18267,7 +18332,7 @@
         <v>47</v>
       </c>
       <c r="I17" t="s">
-        <v>1574</v>
+        <v>1565</v>
       </c>
       <c r="J17" t="s">
         <v>1555</v>
@@ -18276,11 +18341,11 @@
         <v>1</v>
       </c>
       <c r="V17" t="s">
-        <v>1575</v>
+        <v>1810</v>
       </c>
       <c r="W17" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=59335,nFrame=47,szNote="步虚尘·白雪忆",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="步虚尘·白雪忆",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=59335,nFrame=47,szNote="步虚尘·白雪忆",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="步虚尘·白雪忆",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.15">
@@ -18303,7 +18368,7 @@
         <v>47</v>
       </c>
       <c r="I19" t="s">
-        <v>1576</v>
+        <v>1566</v>
       </c>
       <c r="J19" t="s">
         <v>1555</v>
@@ -18315,7 +18380,7 @@
         <v>1</v>
       </c>
       <c r="V19" t="s">
-        <v>1577</v>
+        <v>1869</v>
       </c>
       <c r="W19" t="str">
         <f t="shared" si="0"/>
@@ -18342,7 +18407,7 @@
         <v>47</v>
       </c>
       <c r="I21" t="s">
-        <v>1576</v>
+        <v>1566</v>
       </c>
       <c r="J21" t="s">
         <v>1555</v>
@@ -18354,7 +18419,7 @@
         <v>1</v>
       </c>
       <c r="V21" t="s">
-        <v>1577</v>
+        <v>1869</v>
       </c>
       <c r="W21" t="str">
         <f t="shared" si="0"/>
@@ -18369,7 +18434,7 @@
         <v>47</v>
       </c>
       <c r="I22" t="s">
-        <v>1578</v>
+        <v>1567</v>
       </c>
       <c r="J22" t="s">
         <v>1555</v>
@@ -18378,11 +18443,11 @@
         <v>1</v>
       </c>
       <c r="V22" t="s">
-        <v>1579</v>
+        <v>1811</v>
       </c>
       <c r="W22" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=47992,nFrame=47,szNote="老不知·红衣歌",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="老不知·红衣歌",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=47992,nFrame=47,szNote="老不知·红衣歌",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="老不知·红衣歌",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.15">
@@ -18393,7 +18458,7 @@
         <v>47</v>
       </c>
       <c r="I23" t="s">
-        <v>1580</v>
+        <v>1568</v>
       </c>
       <c r="J23" t="s">
         <v>1555</v>
@@ -18402,11 +18467,11 @@
         <v>1</v>
       </c>
       <c r="V23" t="s">
-        <v>1581</v>
+        <v>1812</v>
       </c>
       <c r="W23" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=102833,nFrame=47,szNote="红师农·尘网中",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红师农·尘网中",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=102833,nFrame=47,szNote="红师农·尘网中",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="红师农·尘网中",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.15">
@@ -18429,7 +18494,7 @@
         <v>47</v>
       </c>
       <c r="I25" t="s">
-        <v>1582</v>
+        <v>1569</v>
       </c>
       <c r="J25" t="s">
         <v>1555</v>
@@ -18441,14 +18506,14 @@
         <v>1</v>
       </c>
       <c r="V25" t="s">
-        <v>1583</v>
+        <v>1870</v>
       </c>
       <c r="W25" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=19323,nFrame=47,szNote="喜小乐·蟹兵",col={0,255,255,},[3]={bCenterAlarm=true,bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="喜小乐·蟹兵",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=3,nIcon=6110,nFrame=7,szName="蟹兵·三十二·八·四",nTime=20,key="蹲宠提示0",},},},</v>
       </c>
       <c r="X25" t="s">
-        <v>1584</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.15">
@@ -18459,7 +18524,7 @@
         <v>47</v>
       </c>
       <c r="I26" t="s">
-        <v>1585</v>
+        <v>1571</v>
       </c>
       <c r="J26" t="s">
         <v>1555</v>
@@ -18471,7 +18536,7 @@
         <v>1</v>
       </c>
       <c r="V26" t="s">
-        <v>1586</v>
+        <v>1871</v>
       </c>
       <c r="W26" t="str">
         <f t="shared" si="0"/>
@@ -18486,7 +18551,7 @@
         <v>47</v>
       </c>
       <c r="I27" t="s">
-        <v>1587</v>
+        <v>1572</v>
       </c>
       <c r="J27" t="s">
         <v>1555</v>
@@ -18495,11 +18560,11 @@
         <v>1</v>
       </c>
       <c r="V27" t="s">
-        <v>1588</v>
+        <v>1813</v>
       </c>
       <c r="W27" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=2350,nFrame=47,szNote="猫猫·破晓鸣",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="猫猫·破晓鸣",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=2350,nFrame=47,szNote="猫猫·破晓鸣",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="猫猫·破晓鸣",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.15">
@@ -18510,7 +18575,7 @@
         <v>47</v>
       </c>
       <c r="I28" t="s">
-        <v>1589</v>
+        <v>1573</v>
       </c>
       <c r="J28" t="s">
         <v>1555</v>
@@ -18519,11 +18584,11 @@
         <v>1</v>
       </c>
       <c r="V28" t="s">
-        <v>1590</v>
+        <v>1814</v>
       </c>
       <c r="W28" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=1274,nFrame=47,szNote="秦邑·破晓鸣",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="秦邑·破晓鸣",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=1274,nFrame=47,szNote="秦邑·破晓鸣",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="秦邑·破晓鸣",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.15">
@@ -18546,7 +18611,7 @@
         <v>47</v>
       </c>
       <c r="I30" t="s">
-        <v>1591</v>
+        <v>1574</v>
       </c>
       <c r="J30" t="s">
         <v>1555</v>
@@ -18555,11 +18620,11 @@
         <v>1</v>
       </c>
       <c r="V30" t="s">
-        <v>1592</v>
+        <v>1815</v>
       </c>
       <c r="W30" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=42874,nFrame=47,szNote="马四·枫林酒",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="马四·枫林酒",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=42874,nFrame=47,szNote="马四·枫林酒",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="马四·枫林酒",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.15">
@@ -18582,7 +18647,7 @@
         <v>47</v>
       </c>
       <c r="I32" t="s">
-        <v>1576</v>
+        <v>1566</v>
       </c>
       <c r="J32" t="s">
         <v>1555</v>
@@ -18594,7 +18659,7 @@
         <v>1</v>
       </c>
       <c r="V32" t="s">
-        <v>1577</v>
+        <v>1869</v>
       </c>
       <c r="W32" t="str">
         <f t="shared" si="0"/>
@@ -18609,7 +18674,7 @@
         <v>47</v>
       </c>
       <c r="I33" t="s">
-        <v>1593</v>
+        <v>1575</v>
       </c>
       <c r="J33" t="s">
         <v>1555</v>
@@ -18618,11 +18683,11 @@
         <v>1</v>
       </c>
       <c r="V33" t="s">
-        <v>1594</v>
+        <v>1816</v>
       </c>
       <c r="W33" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=59272,nFrame=47,szNote="阮染·锻剑女",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="阮染·锻剑女",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=59272,nFrame=47,szNote="阮染·锻剑女",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="阮染·锻剑女",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.15">
@@ -18633,7 +18698,7 @@
         <v>47</v>
       </c>
       <c r="I34" t="s">
-        <v>1595</v>
+        <v>1576</v>
       </c>
       <c r="J34" t="s">
         <v>1555</v>
@@ -18642,11 +18707,11 @@
         <v>1</v>
       </c>
       <c r="V34" t="s">
-        <v>1596</v>
+        <v>1817</v>
       </c>
       <c r="W34" t="str">
-        <f t="shared" ref="W34:W65" si="1">IF(ISBLANK(B34)=FALSE,IF(ISBLANK(B33),"},["&amp;B34&amp;"]={","["&amp;B34&amp;"]={"),IF(AND(ISBLANK(B34),ISBLANK(D34),ISBLANK(C34),OR(ISBLANK(B33)=FALSE,ISBLANK(D33)=FALSE,ISBLANK(C33)=FALSE)),"},},}",IF(ISBLANK(C34),"","{dwID="&amp;C34&amp;","&amp;"nFrame="&amp;D34&amp;","&amp;IF(E34&gt;0,"nCount="&amp;E34&amp;",","")&amp;IF(F34&gt;0,"bAllLeave=true,","")&amp;IF(G34&lt;&gt;"","szName="""&amp;G34&amp;""",","")&amp;IF(H34&lt;&gt;"","tKungFu={"&amp;H34&amp;"},","")&amp;IF(I34&lt;&gt;"","szNote="""&amp;I34&amp;""",","")&amp;IF(J34&lt;&gt;"","col={"&amp;J34&amp;"},","")&amp;"[3]={"&amp;IF(K34&lt;&gt;"","tMark={"&amp;K34&amp;"},","")&amp;IF(L34&lt;&gt;"","szVoice="""&amp;L34&amp;""",","")&amp;IF(M34&gt;0,"bTeamChannel=true,","")&amp;IF(N34&gt;0,"bWhisperChannel=true,","")&amp;IF(O34&gt;0,"bCenterAlarm=true,","")&amp;IF(P34&gt;0,"bScreenHead=true,","")&amp;IF(Q34&gt;0,"bFullScreen=true,","")&amp;"},"&amp;"[4]={"&amp;IF(R34&lt;&gt;"","szVoice="""&amp;R34&amp;""",","")&amp;IF(S34&gt;0,"bTeamChannel=true,","")&amp;IF(T34&gt;0,"bWhisperChannel=true,","")&amp;IF(U34&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(V34&lt;&gt;"","aFocus={"&amp;V34&amp;"},","")&amp;IF(X34&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,X34:AAA34)&amp;"},","")&amp;"},")))</f>
-        <v>{dwID=59794,nFrame=47,szNote="亭十四·归安志",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="亭十四·归安志",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="0"/>
+        <v>{dwID=59794,nFrame=47,szNote="亭十四·归安志",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="亭十四·归安志",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="35" spans="1:23" x14ac:dyDescent="0.15">
@@ -18657,7 +18722,7 @@
         <v>47</v>
       </c>
       <c r="I35" t="s">
-        <v>1597</v>
+        <v>1577</v>
       </c>
       <c r="J35" t="s">
         <v>1555</v>
@@ -18666,11 +18731,11 @@
         <v>1</v>
       </c>
       <c r="V35" t="s">
-        <v>1598</v>
+        <v>1818</v>
       </c>
       <c r="W35" t="str">
-        <f t="shared" si="1"/>
-        <v>{dwID=59796,nFrame=47,szNote="刘理阳·归安志",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="刘理阳·归安志",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="0"/>
+        <v>{dwID=59796,nFrame=47,szNote="刘理阳·归安志",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="刘理阳·归安志",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="36" spans="1:23" x14ac:dyDescent="0.15">
@@ -18681,7 +18746,7 @@
         <v>47</v>
       </c>
       <c r="I36" t="s">
-        <v>1599</v>
+        <v>1578</v>
       </c>
       <c r="J36" t="s">
         <v>1555</v>
@@ -18690,11 +18755,11 @@
         <v>1</v>
       </c>
       <c r="V36" t="s">
-        <v>1600</v>
+        <v>1819</v>
       </c>
       <c r="W36" t="str">
-        <f t="shared" si="1"/>
-        <v>{dwID=109278,nFrame=47,szNote="小花·鸠雀记",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="小花·鸠雀记",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="0"/>
+        <v>{dwID=109278,nFrame=47,szNote="小花·鸠雀记",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="小花·鸠雀记",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="37" spans="1:23" x14ac:dyDescent="0.15">
@@ -18705,7 +18770,7 @@
         <v>15</v>
       </c>
       <c r="W37" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>},[15]={</v>
       </c>
     </row>
@@ -18717,7 +18782,7 @@
         <v>47</v>
       </c>
       <c r="I38" t="s">
-        <v>1601</v>
+        <v>1579</v>
       </c>
       <c r="J38" t="s">
         <v>1555</v>
@@ -18729,10 +18794,10 @@
         <v>1</v>
       </c>
       <c r="V38" t="s">
-        <v>1602</v>
+        <v>1872</v>
       </c>
       <c r="W38" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>{dwID=19320,nFrame=47,szNote="林小明·大头鹅",col={0,255,255,},[3]={bCenterAlarm=true,bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="林小明·大头鹅",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
@@ -18744,7 +18809,7 @@
         <v>47</v>
       </c>
       <c r="I39" t="s">
-        <v>1603</v>
+        <v>1580</v>
       </c>
       <c r="J39" t="s">
         <v>1555</v>
@@ -18753,11 +18818,11 @@
         <v>1</v>
       </c>
       <c r="V39" t="s">
-        <v>1604</v>
+        <v>1820</v>
       </c>
       <c r="W39" t="str">
-        <f t="shared" si="1"/>
-        <v>{dwID=59322,nFrame=47,szNote="杨悦·一念间",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="杨悦·一念间",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="0"/>
+        <v>{dwID=59322,nFrame=47,szNote="杨悦·一念间",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="杨悦·一念间",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="40" spans="1:23" x14ac:dyDescent="0.15">
@@ -18768,7 +18833,7 @@
         <v>16</v>
       </c>
       <c r="W40" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>},[16]={</v>
       </c>
     </row>
@@ -18780,7 +18845,7 @@
         <v>47</v>
       </c>
       <c r="I41" t="s">
-        <v>1605</v>
+        <v>1581</v>
       </c>
       <c r="J41" t="s">
         <v>1555</v>
@@ -18789,11 +18854,11 @@
         <v>1</v>
       </c>
       <c r="V41" t="s">
-        <v>1606</v>
+        <v>1821</v>
       </c>
       <c r="W41" t="str">
-        <f t="shared" si="1"/>
-        <v>{dwID=36945,nFrame=47,szNote="陶九翁·捉妖记",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="陶九翁·捉妖记",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="0"/>
+        <v>{dwID=36945,nFrame=47,szNote="陶九翁·捉妖记",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="陶九翁·捉妖记",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="42" spans="1:23" x14ac:dyDescent="0.15">
@@ -18804,7 +18869,7 @@
         <v>47</v>
       </c>
       <c r="I42" t="s">
-        <v>1607</v>
+        <v>1582</v>
       </c>
       <c r="J42" t="s">
         <v>1555</v>
@@ -18813,11 +18878,11 @@
         <v>1</v>
       </c>
       <c r="V42" t="s">
-        <v>1608</v>
+        <v>1822</v>
       </c>
       <c r="W42" t="str">
-        <f t="shared" si="1"/>
-        <v>{dwID=59355,nFrame=47,szNote="卢蓉·烟花戏",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="卢蓉·烟花戏",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="0"/>
+        <v>{dwID=59355,nFrame=47,szNote="卢蓉·烟花戏",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="卢蓉·烟花戏",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="43" spans="1:23" x14ac:dyDescent="0.15">
@@ -18828,7 +18893,7 @@
         <v>21</v>
       </c>
       <c r="W43" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>},[21]={</v>
       </c>
     </row>
@@ -18840,7 +18905,7 @@
         <v>47</v>
       </c>
       <c r="I44" t="s">
-        <v>1609</v>
+        <v>1583</v>
       </c>
       <c r="J44" t="s">
         <v>1555</v>
@@ -18852,10 +18917,10 @@
         <v>1</v>
       </c>
       <c r="V44" t="s">
-        <v>1610</v>
+        <v>1873</v>
       </c>
       <c r="W44" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>{dwID=19321,nFrame=47,szNote="皮皮·白鹅",col={0,255,255,},[3]={bCenterAlarm=true,bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="皮皮·白鹅",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
@@ -18867,7 +18932,7 @@
         <v>22</v>
       </c>
       <c r="W45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>},[22]={</v>
       </c>
     </row>
@@ -18879,7 +18944,7 @@
         <v>47</v>
       </c>
       <c r="I46" t="s">
-        <v>1585</v>
+        <v>1571</v>
       </c>
       <c r="J46" t="s">
         <v>1555</v>
@@ -18891,10 +18956,10 @@
         <v>1</v>
       </c>
       <c r="V46" t="s">
-        <v>1586</v>
+        <v>1871</v>
       </c>
       <c r="W46" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>{dwID=27467,nFrame=47,szNote="寄居蟹·蟹仔",col={0,255,255,},[3]={bCenterAlarm=true,bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="寄居蟹·蟹仔",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
@@ -18906,7 +18971,7 @@
         <v>47</v>
       </c>
       <c r="I47" t="s">
-        <v>1611</v>
+        <v>1584</v>
       </c>
       <c r="J47" t="s">
         <v>1555</v>
@@ -18915,11 +18980,11 @@
         <v>1</v>
       </c>
       <c r="V47" t="s">
-        <v>1612</v>
+        <v>1823</v>
       </c>
       <c r="W47" t="str">
-        <f t="shared" si="1"/>
-        <v>{dwID=41126,nFrame=47,szNote="车山果·嘟嘟",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="车山果·嘟嘟",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="0"/>
+        <v>{dwID=41126,nFrame=47,szNote="车山果·嘟嘟",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="车山果·嘟嘟",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.15">
@@ -18930,7 +18995,7 @@
         <v>47</v>
       </c>
       <c r="I48" t="s">
-        <v>1613</v>
+        <v>1585</v>
       </c>
       <c r="J48" t="s">
         <v>1555</v>
@@ -18939,11 +19004,11 @@
         <v>1</v>
       </c>
       <c r="V48" t="s">
-        <v>1614</v>
+        <v>1824</v>
       </c>
       <c r="W48" t="str">
-        <f t="shared" si="1"/>
-        <v>{dwID=56477,nFrame=47,szNote="康永浩·东海客",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="康永浩·东海客",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="0"/>
+        <v>{dwID=56477,nFrame=47,szNote="康永浩·东海客",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="康永浩·东海客",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="49" spans="1:23" x14ac:dyDescent="0.15">
@@ -18954,7 +19019,7 @@
         <v>23</v>
       </c>
       <c r="W49" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>},[23]={</v>
       </c>
     </row>
@@ -18966,7 +19031,7 @@
         <v>47</v>
       </c>
       <c r="I50" t="s">
-        <v>1615</v>
+        <v>1586</v>
       </c>
       <c r="J50" t="s">
         <v>1555</v>
@@ -18975,11 +19040,11 @@
         <v>1</v>
       </c>
       <c r="V50" t="s">
-        <v>1616</v>
+        <v>1825</v>
       </c>
       <c r="W50" t="str">
-        <f t="shared" si="1"/>
-        <v>{dwID=51303,nFrame=47,szNote="桩桩·沙海谣",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="桩桩·沙海谣",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="0"/>
+        <v>{dwID=51303,nFrame=47,szNote="桩桩·沙海谣",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="桩桩·沙海谣",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="51" spans="1:23" x14ac:dyDescent="0.15">
@@ -18990,7 +19055,7 @@
         <v>47</v>
       </c>
       <c r="I51" t="s">
-        <v>1617</v>
+        <v>1587</v>
       </c>
       <c r="J51" t="s">
         <v>1555</v>
@@ -18999,11 +19064,11 @@
         <v>1</v>
       </c>
       <c r="V51" t="s">
-        <v>1618</v>
+        <v>1826</v>
       </c>
       <c r="W51" t="str">
-        <f t="shared" si="1"/>
-        <v>{dwID=57929,nFrame=47,szNote="田语夕·锋芒展",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="田语夕·锋芒展",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="0"/>
+        <v>{dwID=57929,nFrame=47,szNote="田语夕·锋芒展",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="田语夕·锋芒展",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="52" spans="1:23" x14ac:dyDescent="0.15">
@@ -19014,7 +19079,7 @@
         <v>49</v>
       </c>
       <c r="W52" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>},[49]={</v>
       </c>
     </row>
@@ -19026,7 +19091,7 @@
         <v>47</v>
       </c>
       <c r="I53" t="s">
-        <v>1619</v>
+        <v>1588</v>
       </c>
       <c r="J53" t="s">
         <v>1555</v>
@@ -19035,11 +19100,11 @@
         <v>1</v>
       </c>
       <c r="V53" t="s">
-        <v>1620</v>
+        <v>1827</v>
       </c>
       <c r="W53" t="str">
-        <f t="shared" si="1"/>
-        <v>{dwID=48171,nFrame=47,szNote="铸剑大师·归乡路",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="铸剑大师·归乡路",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="0"/>
+        <v>{dwID=48171,nFrame=47,szNote="铸剑大师·归乡路",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="铸剑大师·归乡路",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="54" spans="1:23" x14ac:dyDescent="0.15">
@@ -19050,7 +19115,7 @@
         <v>47</v>
       </c>
       <c r="I54" t="s">
-        <v>1621</v>
+        <v>1589</v>
       </c>
       <c r="J54" t="s">
         <v>1555</v>
@@ -19059,11 +19124,11 @@
         <v>1</v>
       </c>
       <c r="V54" t="s">
-        <v>1622</v>
+        <v>1828</v>
       </c>
       <c r="W54" t="str">
-        <f t="shared" si="1"/>
-        <v>{dwID=99195,nFrame=47,szNote="王厨娘·莫贪杯",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="王厨娘·莫贪杯",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="0"/>
+        <v>{dwID=99195,nFrame=47,szNote="王厨娘·莫贪杯",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="王厨娘·莫贪杯",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="55" spans="1:23" x14ac:dyDescent="0.15">
@@ -19074,7 +19139,7 @@
         <v>101</v>
       </c>
       <c r="W55" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>},[101]={</v>
       </c>
     </row>
@@ -19086,7 +19151,7 @@
         <v>47</v>
       </c>
       <c r="I56" t="s">
-        <v>1623</v>
+        <v>1590</v>
       </c>
       <c r="J56" t="s">
         <v>1555</v>
@@ -19095,11 +19160,11 @@
         <v>1</v>
       </c>
       <c r="V56" t="s">
-        <v>1624</v>
+        <v>1829</v>
       </c>
       <c r="W56" t="str">
-        <f t="shared" si="1"/>
-        <v>{dwID=51936,nFrame=47,szNote="沈笑颜·竹马情",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="沈笑颜·竹马情",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="0"/>
+        <v>{dwID=51936,nFrame=47,szNote="沈笑颜·竹马情",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="沈笑颜·竹马情",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="57" spans="1:23" x14ac:dyDescent="0.15">
@@ -19110,7 +19175,7 @@
         <v>102</v>
       </c>
       <c r="W57" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>},[102]={</v>
       </c>
     </row>
@@ -19122,7 +19187,7 @@
         <v>47</v>
       </c>
       <c r="I58" t="s">
-        <v>1625</v>
+        <v>1591</v>
       </c>
       <c r="J58" t="s">
         <v>1555</v>
@@ -19131,11 +19196,11 @@
         <v>1</v>
       </c>
       <c r="V58" t="s">
-        <v>1626</v>
+        <v>1830</v>
       </c>
       <c r="W58" t="str">
-        <f t="shared" si="1"/>
-        <v>{dwID=55289,nFrame=47,szNote="苗淼尔·滇南行",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="苗淼尔·滇南行",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="0"/>
+        <v>{dwID=55289,nFrame=47,szNote="苗淼尔·滇南行",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="苗淼尔·滇南行",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="59" spans="1:23" x14ac:dyDescent="0.15">
@@ -19146,7 +19211,7 @@
         <v>105</v>
       </c>
       <c r="W59" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>},[105]={</v>
       </c>
     </row>
@@ -19158,7 +19223,7 @@
         <v>47</v>
       </c>
       <c r="I60" t="s">
-        <v>1627</v>
+        <v>1592</v>
       </c>
       <c r="J60" t="s">
         <v>1555</v>
@@ -19167,10 +19232,10 @@
         <v>1</v>
       </c>
       <c r="V60" t="s">
-        <v>1981</v>
+        <v>1785</v>
       </c>
       <c r="W60" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>{dwID=51963,nFrame=47,szNote="查飞天·至尊宝",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="查飞天·至尊宝",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
@@ -19182,7 +19247,7 @@
         <v>108</v>
       </c>
       <c r="W61" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>},[108]={</v>
       </c>
     </row>
@@ -19194,7 +19259,7 @@
         <v>47</v>
       </c>
       <c r="I62" t="s">
-        <v>1628</v>
+        <v>1593</v>
       </c>
       <c r="J62" t="s">
         <v>1555</v>
@@ -19206,10 +19271,10 @@
         <v>1</v>
       </c>
       <c r="V62" t="s">
-        <v>1629</v>
+        <v>1874</v>
       </c>
       <c r="W62" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>{dwID=27081,nFrame=47,szNote="虚弱的小狗·哈皮",col={0,255,255,},[3]={bCenterAlarm=true,bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="虚弱的小狗·哈皮",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
@@ -19221,7 +19286,7 @@
         <v>47</v>
       </c>
       <c r="I63" t="s">
-        <v>1630</v>
+        <v>1594</v>
       </c>
       <c r="J63" t="s">
         <v>1555</v>
@@ -19233,11 +19298,11 @@
         <v>1</v>
       </c>
       <c r="V63" t="s">
-        <v>1631</v>
+        <v>1875</v>
       </c>
       <c r="W63" t="str">
-        <f t="shared" si="1"/>
-        <v>{dwID=11969,nFrame=47,szNote="吴为有·石敢当",col={0,255,255,},[3]={bCenterAlarm=true,bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="吴为有·石敢当",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="0"/>
+        <v>{dwID=11969,nFrame=47,szNote="吴为有·石敢当",col={0,255,255,},[3]={bCenterAlarm=true,bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="吴为有·石敢当",nMaxDistance=120,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="64" spans="1:23" x14ac:dyDescent="0.15">
@@ -19248,7 +19313,7 @@
         <v>122</v>
       </c>
       <c r="W64" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>},[122]={</v>
       </c>
     </row>
@@ -19260,7 +19325,7 @@
         <v>47</v>
       </c>
       <c r="I65" t="s">
-        <v>1632</v>
+        <v>1595</v>
       </c>
       <c r="J65" t="s">
         <v>1555</v>
@@ -19269,97 +19334,97 @@
         <v>1</v>
       </c>
       <c r="V65" t="s">
-        <v>1633</v>
+        <v>1831</v>
       </c>
       <c r="W65" t="str">
+        <f t="shared" si="0"/>
+        <v>{dwID=59356,nFrame=47,szNote="唐御御·烟花戏",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="唐御御·烟花戏",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+      </c>
+    </row>
+    <row r="66" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="C66">
+        <v>137328</v>
+      </c>
+      <c r="D66">
+        <v>47</v>
+      </c>
+      <c r="I66" t="s">
+        <v>1802</v>
+      </c>
+      <c r="J66" t="s">
+        <v>1555</v>
+      </c>
+      <c r="P66">
+        <v>1</v>
+      </c>
+      <c r="V66" t="s">
+        <v>1803</v>
+      </c>
+      <c r="W66" t="str">
+        <f t="shared" ref="W66:W129" si="1">IF(ISBLANK(B66)=FALSE,IF(ISBLANK(B65),"},["&amp;B66&amp;"]={","["&amp;B66&amp;"]={"),IF(AND(ISBLANK(B66),ISBLANK(D66),ISBLANK(C66),OR(ISBLANK(B65)=FALSE,ISBLANK(D65)=FALSE,ISBLANK(C65)=FALSE)),"},},}",IF(ISBLANK(C66),"","{dwID="&amp;C66&amp;","&amp;"nFrame="&amp;D66&amp;","&amp;IF(E66&gt;0,"nCount="&amp;E66&amp;",","")&amp;IF(F66&gt;0,"bAllLeave=true,","")&amp;IF(G66&lt;&gt;"","szName="""&amp;G66&amp;""",","")&amp;IF(H66&lt;&gt;"","tKungFu={"&amp;H66&amp;"},","")&amp;IF(I66&lt;&gt;"","szNote="""&amp;I66&amp;""",","")&amp;IF(J66&lt;&gt;"","col={"&amp;J66&amp;"},","")&amp;"[3]={"&amp;IF(K66&lt;&gt;"","tMark={"&amp;K66&amp;"},","")&amp;IF(L66&lt;&gt;"","szVoice="""&amp;L66&amp;""",","")&amp;IF(M66&gt;0,"bTeamChannel=true,","")&amp;IF(N66&gt;0,"bWhisperChannel=true,","")&amp;IF(O66&gt;0,"bCenterAlarm=true,","")&amp;IF(P66&gt;0,"bScreenHead=true,","")&amp;IF(Q66&gt;0,"bFullScreen=true,","")&amp;"},"&amp;"[4]={"&amp;IF(R66&lt;&gt;"","szVoice="""&amp;R66&amp;""",","")&amp;IF(S66&gt;0,"bTeamChannel=true,","")&amp;IF(T66&gt;0,"bWhisperChannel=true,","")&amp;IF(U66&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(V66&lt;&gt;"","aFocus={"&amp;V66&amp;"},","")&amp;IF(X66&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,X66:AAA66)&amp;"},","")&amp;"},")))</f>
+        <v>{dwID=137328,nFrame=47,szNote="唐素娘·龟影锋",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="唐素娘·龟影锋",nMaxDistance=30,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+      </c>
+    </row>
+    <row r="67" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A67" t="s">
+        <v>219</v>
+      </c>
+      <c r="B67">
+        <v>139</v>
+      </c>
+      <c r="W67" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=59356,nFrame=47,szNote="唐御御·烟花戏",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="唐御御·烟花戏",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
-      </c>
-    </row>
-    <row r="66" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A66" t="s">
-        <v>219</v>
-      </c>
-      <c r="B66">
-        <v>139</v>
-      </c>
-      <c r="W66" t="str">
-        <f t="shared" ref="W66:W97" si="2">IF(ISBLANK(B66)=FALSE,IF(ISBLANK(B65),"},["&amp;B66&amp;"]={","["&amp;B66&amp;"]={"),IF(AND(ISBLANK(B66),ISBLANK(D66),ISBLANK(C66),OR(ISBLANK(B65)=FALSE,ISBLANK(D65)=FALSE,ISBLANK(C65)=FALSE)),"},},}",IF(ISBLANK(C66),"","{dwID="&amp;C66&amp;","&amp;"nFrame="&amp;D66&amp;","&amp;IF(E66&gt;0,"nCount="&amp;E66&amp;",","")&amp;IF(F66&gt;0,"bAllLeave=true,","")&amp;IF(G66&lt;&gt;"","szName="""&amp;G66&amp;""",","")&amp;IF(H66&lt;&gt;"","tKungFu={"&amp;H66&amp;"},","")&amp;IF(I66&lt;&gt;"","szNote="""&amp;I66&amp;""",","")&amp;IF(J66&lt;&gt;"","col={"&amp;J66&amp;"},","")&amp;"[3]={"&amp;IF(K66&lt;&gt;"","tMark={"&amp;K66&amp;"},","")&amp;IF(L66&lt;&gt;"","szVoice="""&amp;L66&amp;""",","")&amp;IF(M66&gt;0,"bTeamChannel=true,","")&amp;IF(N66&gt;0,"bWhisperChannel=true,","")&amp;IF(O66&gt;0,"bCenterAlarm=true,","")&amp;IF(P66&gt;0,"bScreenHead=true,","")&amp;IF(Q66&gt;0,"bFullScreen=true,","")&amp;"},"&amp;"[4]={"&amp;IF(R66&lt;&gt;"","szVoice="""&amp;R66&amp;""",","")&amp;IF(S66&gt;0,"bTeamChannel=true,","")&amp;IF(T66&gt;0,"bWhisperChannel=true,","")&amp;IF(U66&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(V66&lt;&gt;"","aFocus={"&amp;V66&amp;"},","")&amp;IF(X66&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,X66:AAA66)&amp;"},","")&amp;"},")))</f>
         <v>},[139]={</v>
       </c>
     </row>
-    <row r="67" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="C67">
+    <row r="68" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="C68">
         <v>25531</v>
       </c>
-      <c r="D67">
+      <c r="D68">
         <v>47</v>
       </c>
-      <c r="I67" t="s">
-        <v>1634</v>
-      </c>
-      <c r="J67" t="s">
+      <c r="I68" t="s">
+        <v>1596</v>
+      </c>
+      <c r="J68" t="s">
         <v>1555</v>
       </c>
-      <c r="O67">
-        <v>1</v>
-      </c>
-      <c r="P67">
-        <v>1</v>
-      </c>
-      <c r="V67" t="s">
-        <v>1635</v>
-      </c>
-      <c r="W67" t="str">
-        <f t="shared" si="2"/>
+      <c r="O68">
+        <v>1</v>
+      </c>
+      <c r="P68">
+        <v>1</v>
+      </c>
+      <c r="V68" t="s">
+        <v>1876</v>
+      </c>
+      <c r="W68" t="str">
+        <f t="shared" si="1"/>
         <v>{dwID=25531,nFrame=47,szNote="密探·蟹将·蟹帅",col={0,255,255,},[3]={bCenterAlarm=true,bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="密探·蟹将·蟹帅",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
-    <row r="68" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A68" t="s">
+    <row r="69" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A69" t="s">
         <v>14</v>
       </c>
-      <c r="B68">
+      <c r="B69">
         <v>150</v>
       </c>
-      <c r="W68" t="str">
-        <f t="shared" si="2"/>
+      <c r="W69" t="str">
+        <f t="shared" si="1"/>
         <v>},[150]={</v>
-      </c>
-    </row>
-    <row r="69" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="C69">
-        <v>59336</v>
-      </c>
-      <c r="D69">
-        <v>47</v>
-      </c>
-      <c r="I69" t="s">
-        <v>1636</v>
-      </c>
-      <c r="J69" t="s">
-        <v>1555</v>
-      </c>
-      <c r="P69">
-        <v>1</v>
-      </c>
-      <c r="V69" t="s">
-        <v>1637</v>
-      </c>
-      <c r="W69" t="str">
-        <f t="shared" si="2"/>
-        <v>{dwID=59336,nFrame=47,szNote="阿貘·烟花戏",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="阿貘·烟花戏",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="70" spans="1:23" x14ac:dyDescent="0.15">
       <c r="C70">
-        <v>59337</v>
+        <v>59336</v>
       </c>
       <c r="D70">
         <v>47</v>
       </c>
       <c r="I70" t="s">
-        <v>1638</v>
+        <v>1597</v>
       </c>
       <c r="J70" t="s">
         <v>1555</v>
@@ -19368,121 +19433,121 @@
         <v>1</v>
       </c>
       <c r="V70" t="s">
-        <v>1639</v>
+        <v>1832</v>
       </c>
       <c r="W70" t="str">
-        <f t="shared" si="2"/>
-        <v>{dwID=59337,nFrame=47,szNote="雨芒·烟花戏",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="雨芒·烟花戏",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=59336,nFrame=47,szNote="阿貘·烟花戏",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="阿貘·烟花戏",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="71" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A71" t="s">
+      <c r="C71">
+        <v>59337</v>
+      </c>
+      <c r="D71">
+        <v>47</v>
+      </c>
+      <c r="I71" t="s">
+        <v>1598</v>
+      </c>
+      <c r="J71" t="s">
+        <v>1555</v>
+      </c>
+      <c r="P71">
+        <v>1</v>
+      </c>
+      <c r="V71" t="s">
+        <v>1833</v>
+      </c>
+      <c r="W71" t="str">
+        <f t="shared" si="1"/>
+        <v>{dwID=59337,nFrame=47,szNote="雨芒·烟花戏",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="雨芒·烟花戏",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+      </c>
+    </row>
+    <row r="72" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A72" t="s">
         <v>230</v>
       </c>
-      <c r="B71">
+      <c r="B72">
         <v>156</v>
       </c>
-      <c r="W71" t="str">
-        <f t="shared" si="2"/>
+      <c r="W72" t="str">
+        <f t="shared" si="1"/>
         <v>},[156]={</v>
-      </c>
-    </row>
-    <row r="72" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="C72">
-        <v>25524</v>
-      </c>
-      <c r="D72">
-        <v>47</v>
-      </c>
-      <c r="I72" t="s">
-        <v>1640</v>
-      </c>
-      <c r="J72" t="s">
-        <v>1555</v>
-      </c>
-      <c r="O72">
-        <v>1</v>
-      </c>
-      <c r="P72">
-        <v>1</v>
-      </c>
-      <c r="V72" t="s">
-        <v>1641</v>
-      </c>
-      <c r="W72" t="str">
-        <f t="shared" si="2"/>
-        <v>{dwID=25524,nFrame=47,szNote="惊恐的灰鹅·小灰",col={0,255,255,},[3]={bCenterAlarm=true,bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="惊恐的灰鹅·小灰",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="73" spans="1:23" x14ac:dyDescent="0.15">
       <c r="C73">
-        <v>109467</v>
+        <v>25524</v>
       </c>
       <c r="D73">
         <v>47</v>
       </c>
       <c r="I73" t="s">
-        <v>1642</v>
+        <v>1599</v>
       </c>
       <c r="J73" t="s">
         <v>1555</v>
       </c>
+      <c r="O73">
+        <v>1</v>
+      </c>
       <c r="P73">
         <v>1</v>
       </c>
       <c r="V73" t="s">
-        <v>1643</v>
+        <v>1877</v>
       </c>
       <c r="W73" t="str">
-        <f t="shared" si="2"/>
-        <v>{dwID=109467,nFrame=47,szNote="错错·枉叹恨",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="错错·枉叹恨",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=25524,nFrame=47,szNote="惊恐的灰鹅·小灰",col={0,255,255,},[3]={bCenterAlarm=true,bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="惊恐的灰鹅·小灰",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="74" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A74" t="s">
+      <c r="C74">
+        <v>109467</v>
+      </c>
+      <c r="D74">
+        <v>47</v>
+      </c>
+      <c r="I74" t="s">
+        <v>1600</v>
+      </c>
+      <c r="J74" t="s">
+        <v>1555</v>
+      </c>
+      <c r="P74">
+        <v>1</v>
+      </c>
+      <c r="V74" t="s">
+        <v>1834</v>
+      </c>
+      <c r="W74" t="str">
+        <f t="shared" si="1"/>
+        <v>{dwID=109467,nFrame=47,szNote="错错·枉叹恨",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="错错·枉叹恨",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+      </c>
+    </row>
+    <row r="75" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A75" t="s">
         <v>15</v>
       </c>
-      <c r="B74">
+      <c r="B75">
         <v>159</v>
       </c>
-      <c r="W74" t="str">
-        <f t="shared" si="2"/>
+      <c r="W75" t="str">
+        <f t="shared" si="1"/>
         <v>},[159]={</v>
-      </c>
-    </row>
-    <row r="75" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="C75">
-        <v>54677</v>
-      </c>
-      <c r="D75">
-        <v>47</v>
-      </c>
-      <c r="I75" t="s">
-        <v>1644</v>
-      </c>
-      <c r="J75" t="s">
-        <v>1555</v>
-      </c>
-      <c r="P75">
-        <v>1</v>
-      </c>
-      <c r="V75" t="s">
-        <v>1645</v>
-      </c>
-      <c r="W75" t="str">
-        <f t="shared" si="2"/>
-        <v>{dwID=54677,nFrame=47,szNote="苏临渊·稚子心",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="苏临渊·稚子心",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="76" spans="1:23" x14ac:dyDescent="0.15">
       <c r="C76">
-        <v>55065</v>
+        <v>54677</v>
       </c>
       <c r="D76">
         <v>47</v>
       </c>
       <c r="I76" t="s">
-        <v>1646</v>
+        <v>1601</v>
       </c>
       <c r="J76" t="s">
         <v>1555</v>
@@ -19491,22 +19556,22 @@
         <v>1</v>
       </c>
       <c r="V76" t="s">
-        <v>1647</v>
+        <v>1835</v>
       </c>
       <c r="W76" t="str">
-        <f t="shared" si="2"/>
-        <v>{dwID=55065,nFrame=47,szNote="李嫂·稚子心",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="李嫂·稚子心",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=54677,nFrame=47,szNote="苏临渊·稚子心",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="苏临渊·稚子心",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="77" spans="1:23" x14ac:dyDescent="0.15">
       <c r="C77">
-        <v>59352</v>
+        <v>55065</v>
       </c>
       <c r="D77">
         <v>47</v>
       </c>
       <c r="I77" t="s">
-        <v>1648</v>
+        <v>1602</v>
       </c>
       <c r="J77" t="s">
         <v>1555</v>
@@ -19515,85 +19580,85 @@
         <v>1</v>
       </c>
       <c r="V77" t="s">
-        <v>1649</v>
+        <v>1836</v>
       </c>
       <c r="W77" t="str">
-        <f t="shared" si="2"/>
-        <v>{dwID=59352,nFrame=47,szNote="连九醉·烟花戏",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="连九醉·烟花戏",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=55065,nFrame=47,szNote="李嫂·稚子心",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="李嫂·稚子心",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="78" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A78" t="s">
+      <c r="C78">
+        <v>59352</v>
+      </c>
+      <c r="D78">
+        <v>47</v>
+      </c>
+      <c r="I78" t="s">
+        <v>1603</v>
+      </c>
+      <c r="J78" t="s">
+        <v>1555</v>
+      </c>
+      <c r="P78">
+        <v>1</v>
+      </c>
+      <c r="V78" t="s">
+        <v>1837</v>
+      </c>
+      <c r="W78" t="str">
+        <f t="shared" si="1"/>
+        <v>{dwID=59352,nFrame=47,szNote="连九醉·烟花戏",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="连九醉·烟花戏",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+      </c>
+    </row>
+    <row r="79" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A79" t="s">
         <v>16</v>
       </c>
-      <c r="B78">
+      <c r="B79">
         <v>172</v>
       </c>
-      <c r="W78" t="str">
-        <f t="shared" si="2"/>
+      <c r="W79" t="str">
+        <f t="shared" si="1"/>
         <v>},[172]={</v>
-      </c>
-    </row>
-    <row r="79" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="C79">
-        <v>42868</v>
-      </c>
-      <c r="D79">
-        <v>47</v>
-      </c>
-      <c r="I79" t="s">
-        <v>1650</v>
-      </c>
-      <c r="J79" t="s">
-        <v>1555</v>
-      </c>
-      <c r="O79">
-        <v>1</v>
-      </c>
-      <c r="P79">
-        <v>1</v>
-      </c>
-      <c r="V79" t="s">
-        <v>1556</v>
-      </c>
-      <c r="W79" t="str">
-        <f t="shared" si="2"/>
-        <v>{dwID=42868,nFrame=47,szNote="小静静",col={0,255,255,},[3]={bCenterAlarm=true,bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="80" spans="1:23" x14ac:dyDescent="0.15">
       <c r="C80">
-        <v>51323</v>
+        <v>42868</v>
       </c>
       <c r="D80">
         <v>47</v>
       </c>
       <c r="I80" t="s">
-        <v>1651</v>
+        <v>1604</v>
       </c>
       <c r="J80" t="s">
         <v>1555</v>
       </c>
+      <c r="O80">
+        <v>1</v>
+      </c>
       <c r="P80">
         <v>1</v>
       </c>
       <c r="V80" t="s">
-        <v>1652</v>
+        <v>1866</v>
       </c>
       <c r="W80" t="str">
-        <f t="shared" si="2"/>
-        <v>{dwID=51323,nFrame=47,szNote="九隆神丐·荆轲刺",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="九隆神丐·荆轲刺",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=42868,nFrame=47,szNote="小静静",col={0,255,255,},[3]={bCenterAlarm=true,bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="81" spans="1:23" x14ac:dyDescent="0.15">
       <c r="C81">
-        <v>25876</v>
+        <v>51323</v>
       </c>
       <c r="D81">
         <v>47</v>
       </c>
       <c r="I81" t="s">
-        <v>1653</v>
+        <v>1605</v>
       </c>
       <c r="J81" t="s">
         <v>1555</v>
@@ -19602,58 +19667,58 @@
         <v>1</v>
       </c>
       <c r="V81" t="s">
-        <v>1654</v>
+        <v>1838</v>
       </c>
       <c r="W81" t="str">
-        <f t="shared" si="2"/>
-        <v>{dwID=25876,nFrame=47,szNote="孟乌·瀛洲梦",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="孟乌·瀛洲梦",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=51323,nFrame=47,szNote="九隆神丐·荆轲刺",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="九隆神丐·荆轲刺",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="82" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A82" t="s">
+      <c r="C82">
+        <v>25876</v>
+      </c>
+      <c r="D82">
+        <v>47</v>
+      </c>
+      <c r="I82" t="s">
+        <v>1606</v>
+      </c>
+      <c r="J82" t="s">
+        <v>1555</v>
+      </c>
+      <c r="P82">
+        <v>1</v>
+      </c>
+      <c r="V82" t="s">
+        <v>1839</v>
+      </c>
+      <c r="W82" t="str">
+        <f t="shared" si="1"/>
+        <v>{dwID=25876,nFrame=47,szNote="孟乌·瀛洲梦",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="孟乌·瀛洲梦",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+      </c>
+    </row>
+    <row r="83" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A83" t="s">
         <v>258</v>
       </c>
-      <c r="B82">
+      <c r="B83">
         <v>193</v>
       </c>
-      <c r="W82" t="str">
-        <f t="shared" si="2"/>
+      <c r="W83" t="str">
+        <f t="shared" si="1"/>
         <v>},[193]={</v>
-      </c>
-    </row>
-    <row r="83" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="C83">
-        <v>56476</v>
-      </c>
-      <c r="D83">
-        <v>47</v>
-      </c>
-      <c r="I83" t="s">
-        <v>1655</v>
-      </c>
-      <c r="J83" t="s">
-        <v>1555</v>
-      </c>
-      <c r="P83">
-        <v>1</v>
-      </c>
-      <c r="V83" t="s">
-        <v>1656</v>
-      </c>
-      <c r="W83" t="str">
-        <f t="shared" si="2"/>
-        <v>{dwID=56476,nFrame=47,szNote="南静·关外商",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="南静·关外商",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="84" spans="1:23" x14ac:dyDescent="0.15">
       <c r="C84">
-        <v>59328</v>
+        <v>56476</v>
       </c>
       <c r="D84">
         <v>47</v>
       </c>
       <c r="I84" t="s">
-        <v>1657</v>
+        <v>1607</v>
       </c>
       <c r="J84" t="s">
         <v>1555</v>
@@ -19662,70 +19727,82 @@
         <v>1</v>
       </c>
       <c r="V84" t="s">
-        <v>1658</v>
+        <v>1840</v>
       </c>
       <c r="W84" t="str">
-        <f t="shared" si="2"/>
-        <v>{dwID=59328,nFrame=47,szNote="白芷沅·戎马边",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="白芷沅·戎马边",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=56476,nFrame=47,szNote="南静·关外商",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="南静·关外商",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="85" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A85" t="s">
+      <c r="C85">
+        <v>59328</v>
+      </c>
+      <c r="D85">
+        <v>47</v>
+      </c>
+      <c r="I85" t="s">
+        <v>1608</v>
+      </c>
+      <c r="J85" t="s">
+        <v>1555</v>
+      </c>
+      <c r="P85">
+        <v>1</v>
+      </c>
+      <c r="V85" t="s">
+        <v>1841</v>
+      </c>
+      <c r="W85" t="str">
+        <f t="shared" si="1"/>
+        <v>{dwID=59328,nFrame=47,szNote="白芷沅·戎马边",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="白芷沅·戎马边",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+      </c>
+    </row>
+    <row r="86" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A86" t="s">
         <v>259</v>
       </c>
-      <c r="B85">
+      <c r="B86">
         <v>194</v>
       </c>
-      <c r="W85" t="str">
-        <f t="shared" si="2"/>
+      <c r="W86" t="str">
+        <f t="shared" si="1"/>
         <v>},[194]={</v>
       </c>
     </row>
-    <row r="86" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="C86">
+    <row r="87" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="C87">
         <v>107295</v>
       </c>
-      <c r="D86">
+      <c r="D87">
         <v>47</v>
       </c>
-      <c r="I86" t="s">
-        <v>1659</v>
-      </c>
-      <c r="J86" t="s">
+      <c r="I87" t="s">
+        <v>1800</v>
+      </c>
+      <c r="J87" t="s">
         <v>1555</v>
       </c>
-      <c r="P86">
-        <v>1</v>
-      </c>
-      <c r="V86" t="s">
-        <v>1660</v>
-      </c>
-      <c r="W86" t="str">
-        <f t="shared" si="2"/>
-        <v>{dwID=107295,nFrame=47,szNote="庞以松·童蒙志",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="庞以松·童蒙志",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
-      </c>
-    </row>
-    <row r="87" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A87" t="s">
-        <v>272</v>
-      </c>
-      <c r="B87">
-        <v>213</v>
+      <c r="P87">
+        <v>1</v>
+      </c>
+      <c r="V87" t="s">
+        <v>1801</v>
       </c>
       <c r="W87" t="str">
-        <f t="shared" si="2"/>
-        <v>},[213]={</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=107295,nFrame=47,szNote="庞以松·童蒙志",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="庞以松·童蒙志",nMaxDistance=30,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="88" spans="1:23" x14ac:dyDescent="0.15">
       <c r="C88">
-        <v>59052</v>
+        <v>137447</v>
       </c>
       <c r="D88">
         <v>47</v>
       </c>
       <c r="I88" t="s">
-        <v>1661</v>
+        <v>1798</v>
       </c>
       <c r="J88" t="s">
         <v>1555</v>
@@ -19734,34 +19811,34 @@
         <v>1</v>
       </c>
       <c r="V88" t="s">
-        <v>1662</v>
+        <v>1799</v>
       </c>
       <c r="W88" t="str">
-        <f t="shared" si="2"/>
-        <v>{dwID=59052,nFrame=47,szNote="阿秋·儿女事",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="阿秋·儿女事",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=137447,nFrame=47,szNote="流民老奶奶·燕难归",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="流民老奶奶·燕难归",nMaxDistance=30,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="89" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A89" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="B89">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="W89" t="str">
-        <f t="shared" si="2"/>
-        <v>},[214]={</v>
+        <f t="shared" si="1"/>
+        <v>},[213]={</v>
       </c>
     </row>
     <row r="90" spans="1:23" x14ac:dyDescent="0.15">
       <c r="C90">
-        <v>44430</v>
+        <v>59052</v>
       </c>
       <c r="D90">
         <v>47</v>
       </c>
       <c r="I90" t="s">
-        <v>1663</v>
+        <v>1609</v>
       </c>
       <c r="J90" t="s">
         <v>1555</v>
@@ -19770,109 +19847,97 @@
         <v>1</v>
       </c>
       <c r="V90" t="s">
-        <v>1664</v>
+        <v>1842</v>
       </c>
       <c r="W90" t="str">
-        <f t="shared" si="2"/>
-        <v>{dwID=44430,nFrame=47,szNote="王老道·碎片五·清茗经",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="王老道·碎片五·清茗经",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=59052,nFrame=47,szNote="阿秋·儿女事",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="阿秋·儿女事",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="91" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="C91">
-        <v>47878</v>
-      </c>
-      <c r="D91">
+      <c r="A91" t="s">
+        <v>18</v>
+      </c>
+      <c r="B91">
+        <v>214</v>
+      </c>
+      <c r="W91" t="str">
+        <f t="shared" si="1"/>
+        <v>},[214]={</v>
+      </c>
+    </row>
+    <row r="92" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="C92">
+        <v>44430</v>
+      </c>
+      <c r="D92">
         <v>47</v>
       </c>
-      <c r="I91" t="s">
-        <v>1665</v>
-      </c>
-      <c r="J91" t="s">
+      <c r="I92" t="s">
+        <v>1610</v>
+      </c>
+      <c r="J92" t="s">
         <v>1555</v>
       </c>
-      <c r="O91">
-        <v>1</v>
-      </c>
-      <c r="P91">
-        <v>1</v>
-      </c>
-      <c r="V91" t="s">
-        <v>1666</v>
-      </c>
-      <c r="W91" t="str">
-        <f t="shared" si="2"/>
-        <v>{dwID=47878,nFrame=47,szNote="李尘缘·碎片八·清茗经",col={0,255,255,},[3]={bCenterAlarm=true,bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="李尘缘·碎片八·清茗经",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
-      </c>
-    </row>
-    <row r="92" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A92" t="s">
-        <v>273</v>
-      </c>
-      <c r="B92">
-        <v>215</v>
+      <c r="P92">
+        <v>1</v>
+      </c>
+      <c r="V92" t="s">
+        <v>1843</v>
       </c>
       <c r="W92" t="str">
-        <f t="shared" si="2"/>
-        <v>},[215]={</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=44430,nFrame=47,szNote="王老道·碎片五·清茗经",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="王老道·碎片五·清茗经",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="93" spans="1:23" x14ac:dyDescent="0.15">
       <c r="C93">
-        <v>48057</v>
+        <v>47878</v>
       </c>
       <c r="D93">
         <v>47</v>
       </c>
       <c r="I93" t="s">
-        <v>1667</v>
+        <v>1611</v>
       </c>
       <c r="J93" t="s">
         <v>1555</v>
       </c>
+      <c r="O93">
+        <v>1</v>
+      </c>
       <c r="P93">
         <v>1</v>
       </c>
       <c r="V93" t="s">
-        <v>1668</v>
+        <v>1878</v>
       </c>
       <c r="W93" t="str">
-        <f t="shared" si="2"/>
-        <v>{dwID=48057,nFrame=47,szNote="航小婷·胜负局",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="航小婷·胜负局",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=47878,nFrame=47,szNote="李尘缘·碎片八·清茗经",col={0,255,255,},[3]={bCenterAlarm=true,bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="李尘缘·碎片八·清茗经",nMaxDistance=90,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="94" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="C94">
-        <v>107331</v>
-      </c>
-      <c r="D94">
-        <v>47</v>
-      </c>
-      <c r="I94" t="s">
-        <v>1669</v>
-      </c>
-      <c r="J94" t="s">
-        <v>1555</v>
-      </c>
-      <c r="P94">
-        <v>1</v>
-      </c>
-      <c r="V94" t="s">
-        <v>1670</v>
+      <c r="A94" t="s">
+        <v>273</v>
+      </c>
+      <c r="B94">
+        <v>215</v>
       </c>
       <c r="W94" t="str">
-        <f t="shared" si="2"/>
-        <v>{dwID=107331,nFrame=47,szNote="刘安·风雨意",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="刘安·风雨意",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="1"/>
+        <v>},[215]={</v>
       </c>
     </row>
     <row r="95" spans="1:23" x14ac:dyDescent="0.15">
       <c r="C95">
-        <v>107332</v>
+        <v>48057</v>
       </c>
       <c r="D95">
         <v>47</v>
       </c>
       <c r="I95" t="s">
-        <v>1671</v>
+        <v>1612</v>
       </c>
       <c r="J95" t="s">
         <v>1555</v>
@@ -19881,34 +19946,46 @@
         <v>1</v>
       </c>
       <c r="V95" t="s">
-        <v>1672</v>
+        <v>1844</v>
       </c>
       <c r="W95" t="str">
-        <f t="shared" si="2"/>
-        <v>{dwID=107332,nFrame=47,szNote="曙曙·风雨意",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="曙曙·风雨意",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=48057,nFrame=47,szNote="航小婷·胜负局",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="航小婷·胜负局",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="96" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A96" t="s">
-        <v>19</v>
-      </c>
-      <c r="B96">
-        <v>216</v>
+      <c r="C96">
+        <v>107331</v>
+      </c>
+      <c r="D96">
+        <v>47</v>
+      </c>
+      <c r="I96" t="s">
+        <v>1613</v>
+      </c>
+      <c r="J96" t="s">
+        <v>1555</v>
+      </c>
+      <c r="P96">
+        <v>1</v>
+      </c>
+      <c r="V96" t="s">
+        <v>1845</v>
       </c>
       <c r="W96" t="str">
-        <f t="shared" si="2"/>
-        <v>},[216]={</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=107331,nFrame=47,szNote="刘安·风雨意",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="刘安·风雨意",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="97" spans="1:23" x14ac:dyDescent="0.15">
       <c r="C97">
-        <v>55060</v>
+        <v>107332</v>
       </c>
       <c r="D97">
         <v>47</v>
       </c>
       <c r="I97" t="s">
-        <v>1673</v>
+        <v>1614</v>
       </c>
       <c r="J97" t="s">
         <v>1555</v>
@@ -19917,58 +19994,58 @@
         <v>1</v>
       </c>
       <c r="V97" t="s">
-        <v>1674</v>
+        <v>1846</v>
       </c>
       <c r="W97" t="str">
-        <f t="shared" si="2"/>
-        <v>{dwID=55060,nFrame=47,szNote="野马烈风·青草歌",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="野马烈风·青草歌",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=107332,nFrame=47,szNote="曙曙·风雨意",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="曙曙·风雨意",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="98" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="C98">
-        <v>65917</v>
-      </c>
-      <c r="D98">
+      <c r="A98" t="s">
+        <v>19</v>
+      </c>
+      <c r="B98">
+        <v>216</v>
+      </c>
+      <c r="W98" t="str">
+        <f t="shared" si="1"/>
+        <v>},[216]={</v>
+      </c>
+    </row>
+    <row r="99" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="C99">
+        <v>55060</v>
+      </c>
+      <c r="D99">
         <v>47</v>
       </c>
-      <c r="I98" t="s">
-        <v>1675</v>
-      </c>
-      <c r="J98" t="s">
+      <c r="I99" t="s">
+        <v>1615</v>
+      </c>
+      <c r="J99" t="s">
         <v>1555</v>
       </c>
-      <c r="P98">
-        <v>1</v>
-      </c>
-      <c r="V98" t="s">
-        <v>1676</v>
-      </c>
-      <c r="W98" t="str">
-        <f t="shared" ref="W98:W129" si="3">IF(ISBLANK(B98)=FALSE,IF(ISBLANK(B97),"},["&amp;B98&amp;"]={","["&amp;B98&amp;"]={"),IF(AND(ISBLANK(B98),ISBLANK(D98),ISBLANK(C98),OR(ISBLANK(B97)=FALSE,ISBLANK(D97)=FALSE,ISBLANK(C97)=FALSE)),"},},}",IF(ISBLANK(C98),"","{dwID="&amp;C98&amp;","&amp;"nFrame="&amp;D98&amp;","&amp;IF(E98&gt;0,"nCount="&amp;E98&amp;",","")&amp;IF(F98&gt;0,"bAllLeave=true,","")&amp;IF(G98&lt;&gt;"","szName="""&amp;G98&amp;""",","")&amp;IF(H98&lt;&gt;"","tKungFu={"&amp;H98&amp;"},","")&amp;IF(I98&lt;&gt;"","szNote="""&amp;I98&amp;""",","")&amp;IF(J98&lt;&gt;"","col={"&amp;J98&amp;"},","")&amp;"[3]={"&amp;IF(K98&lt;&gt;"","tMark={"&amp;K98&amp;"},","")&amp;IF(L98&lt;&gt;"","szVoice="""&amp;L98&amp;""",","")&amp;IF(M98&gt;0,"bTeamChannel=true,","")&amp;IF(N98&gt;0,"bWhisperChannel=true,","")&amp;IF(O98&gt;0,"bCenterAlarm=true,","")&amp;IF(P98&gt;0,"bScreenHead=true,","")&amp;IF(Q98&gt;0,"bFullScreen=true,","")&amp;"},"&amp;"[4]={"&amp;IF(R98&lt;&gt;"","szVoice="""&amp;R98&amp;""",","")&amp;IF(S98&gt;0,"bTeamChannel=true,","")&amp;IF(T98&gt;0,"bWhisperChannel=true,","")&amp;IF(U98&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(V98&lt;&gt;"","aFocus={"&amp;V98&amp;"},","")&amp;IF(X98&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,X98:AAA98)&amp;"},","")&amp;"},")))</f>
-        <v>{dwID=65917,nFrame=47,szNote="神秘商人·沧海笛",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="神秘商人·沧海笛",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
-      </c>
-    </row>
-    <row r="99" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A99" t="s">
-        <v>20</v>
-      </c>
-      <c r="B99">
-        <v>217</v>
+      <c r="P99">
+        <v>1</v>
+      </c>
+      <c r="V99" t="s">
+        <v>1847</v>
       </c>
       <c r="W99" t="str">
-        <f t="shared" si="3"/>
-        <v>},[217]={</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=55060,nFrame=47,szNote="野马烈风·青草歌",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="野马烈风·青草歌",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="100" spans="1:23" x14ac:dyDescent="0.15">
       <c r="C100">
-        <v>109423</v>
+        <v>65917</v>
       </c>
       <c r="D100">
         <v>47</v>
       </c>
       <c r="I100" t="s">
-        <v>1677</v>
+        <v>1616</v>
       </c>
       <c r="J100" t="s">
         <v>1555</v>
@@ -19977,109 +20054,109 @@
         <v>1</v>
       </c>
       <c r="V100" t="s">
-        <v>1678</v>
+        <v>1848</v>
       </c>
       <c r="W100" t="str">
-        <f t="shared" si="3"/>
-        <v>{dwID=109423,nFrame=47,szNote="沙木沙克·幽海牧",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="沙木沙克·幽海牧",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=65917,nFrame=47,szNote="神秘商人·沧海笛",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="神秘商人·沧海笛",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="101" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A101" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B101">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="W101" t="str">
-        <f t="shared" si="3"/>
-        <v>},[239]={</v>
+        <f t="shared" si="1"/>
+        <v>},[217]={</v>
       </c>
     </row>
     <row r="102" spans="1:23" x14ac:dyDescent="0.15">
       <c r="C102">
-        <v>56702</v>
+        <v>109423</v>
       </c>
       <c r="D102">
         <v>47</v>
       </c>
       <c r="I102" t="s">
-        <v>1679</v>
+        <v>1617</v>
       </c>
       <c r="J102" t="s">
         <v>1555</v>
       </c>
-      <c r="O102">
-        <v>1</v>
-      </c>
       <c r="P102">
         <v>1</v>
       </c>
       <c r="V102" t="s">
-        <v>1680</v>
+        <v>1849</v>
       </c>
       <c r="W102" t="str">
-        <f t="shared" si="3"/>
-        <v>{dwID=56702,nFrame=47,szNote="小叮当·北行镖",col={0,255,255,},[3]={bCenterAlarm=true,bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="小叮当·北行镖",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=109423,nFrame=47,szNote="沙木沙克·幽海牧",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="沙木沙克·幽海牧",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="103" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A103" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B103">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="W103" t="str">
-        <f t="shared" si="3"/>
-        <v>},[243]={</v>
+        <f t="shared" si="1"/>
+        <v>},[239]={</v>
       </c>
     </row>
     <row r="104" spans="1:23" x14ac:dyDescent="0.15">
       <c r="C104">
-        <v>62005</v>
+        <v>56702</v>
       </c>
       <c r="D104">
         <v>47</v>
       </c>
       <c r="I104" t="s">
-        <v>1681</v>
+        <v>1618</v>
       </c>
       <c r="J104" t="s">
         <v>1555</v>
       </c>
+      <c r="O104">
+        <v>1</v>
+      </c>
       <c r="P104">
         <v>1</v>
       </c>
       <c r="V104" t="s">
-        <v>1682</v>
+        <v>1879</v>
       </c>
       <c r="W104" t="str">
-        <f t="shared" si="3"/>
-        <v>{dwID=62005,nFrame=47,szNote="边澈·太行道",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="边澈·太行道",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=56702,nFrame=47,szNote="小叮当·北行镖",col={0,255,255,},[3]={bCenterAlarm=true,bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="小叮当·北行镖",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="105" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A105" t="s">
-        <v>364</v>
+        <v>22</v>
       </c>
       <c r="B105">
-        <v>325</v>
+        <v>243</v>
       </c>
       <c r="W105" t="str">
-        <f t="shared" si="3"/>
-        <v>},[325]={</v>
+        <f t="shared" si="1"/>
+        <v>},[243]={</v>
       </c>
     </row>
     <row r="106" spans="1:23" x14ac:dyDescent="0.15">
       <c r="C106">
-        <v>70597</v>
+        <v>62005</v>
       </c>
       <c r="D106">
         <v>47</v>
       </c>
       <c r="I106" t="s">
-        <v>1683</v>
+        <v>1619</v>
       </c>
       <c r="J106" t="s">
         <v>1555</v>
@@ -20088,34 +20165,34 @@
         <v>1</v>
       </c>
       <c r="V106" t="s">
-        <v>1684</v>
+        <v>1850</v>
       </c>
       <c r="W106" t="str">
-        <f t="shared" si="3"/>
-        <v>{dwID=70597,nFrame=47,szNote="林云飞·露园事",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="林云飞·露园事",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=62005,nFrame=47,szNote="边澈·太行道",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="边澈·太行道",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="107" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A107" t="s">
-        <v>24</v>
+        <v>364</v>
       </c>
       <c r="B107">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="W107" t="str">
-        <f t="shared" si="3"/>
-        <v>},[330]={</v>
+        <f t="shared" si="1"/>
+        <v>},[325]={</v>
       </c>
     </row>
     <row r="108" spans="1:23" x14ac:dyDescent="0.15">
       <c r="C108">
-        <v>62806</v>
+        <v>70597</v>
       </c>
       <c r="D108">
         <v>47</v>
       </c>
       <c r="I108" t="s">
-        <v>1685</v>
+        <v>1620</v>
       </c>
       <c r="J108" t="s">
         <v>1555</v>
@@ -20124,34 +20201,34 @@
         <v>1</v>
       </c>
       <c r="V108" t="s">
-        <v>1686</v>
+        <v>1851</v>
       </c>
       <c r="W108" t="str">
-        <f t="shared" si="3"/>
-        <v>{dwID=62806,nFrame=47,szNote="火头僧·客江干",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="火头僧·客江干",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=70597,nFrame=47,szNote="林云飞·露园事",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="林云飞·露园事",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="109" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A109" t="s">
-        <v>366</v>
+        <v>24</v>
       </c>
       <c r="B109">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="W109" t="str">
-        <f t="shared" si="3"/>
-        <v>},[332]={</v>
+        <f t="shared" si="1"/>
+        <v>},[330]={</v>
       </c>
     </row>
     <row r="110" spans="1:23" x14ac:dyDescent="0.15">
       <c r="C110">
-        <v>62788</v>
+        <v>62806</v>
       </c>
       <c r="D110">
         <v>47</v>
       </c>
       <c r="I110" t="s">
-        <v>1687</v>
+        <v>1621</v>
       </c>
       <c r="J110" t="s">
         <v>1555</v>
@@ -20160,34 +20237,34 @@
         <v>1</v>
       </c>
       <c r="V110" t="s">
-        <v>1688</v>
+        <v>1852</v>
       </c>
       <c r="W110" t="str">
-        <f t="shared" si="3"/>
-        <v>{dwID=62788,nFrame=47,szNote="焦福贵·秘宝图",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="焦福贵·秘宝图",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=62806,nFrame=47,szNote="火头僧·客江干",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="火头僧·客江干",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="111" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A111" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B111">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="W111" t="str">
-        <f t="shared" si="3"/>
-        <v>},[333]={</v>
+        <f t="shared" si="1"/>
+        <v>},[332]={</v>
       </c>
     </row>
     <row r="112" spans="1:23" x14ac:dyDescent="0.15">
       <c r="C112">
-        <v>99178</v>
+        <v>62788</v>
       </c>
       <c r="D112">
         <v>47</v>
       </c>
       <c r="I112" t="s">
-        <v>1689</v>
+        <v>1622</v>
       </c>
       <c r="J112" t="s">
         <v>1555</v>
@@ -20196,34 +20273,34 @@
         <v>1</v>
       </c>
       <c r="V112" t="s">
-        <v>1690</v>
+        <v>1853</v>
       </c>
       <c r="W112" t="str">
-        <f t="shared" si="3"/>
-        <v>{dwID=99178,nFrame=47,szNote="落单少侠·瀛洲梦",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="落单少侠·瀛洲梦",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=62788,nFrame=47,szNote="焦福贵·秘宝图",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="焦福贵·秘宝图",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="113" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A113" t="s">
-        <v>25</v>
+        <v>367</v>
       </c>
       <c r="B113">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="W113" t="str">
-        <f t="shared" si="3"/>
-        <v>},[334]={</v>
+        <f t="shared" si="1"/>
+        <v>},[333]={</v>
       </c>
     </row>
     <row r="114" spans="1:23" x14ac:dyDescent="0.15">
       <c r="C114">
-        <v>102012</v>
+        <v>99178</v>
       </c>
       <c r="D114">
         <v>47</v>
       </c>
       <c r="I114" t="s">
-        <v>1691</v>
+        <v>1623</v>
       </c>
       <c r="J114" t="s">
         <v>1555</v>
@@ -20232,34 +20309,34 @@
         <v>1</v>
       </c>
       <c r="V114" t="s">
-        <v>1692</v>
+        <v>1854</v>
       </c>
       <c r="W114" t="str">
-        <f t="shared" si="3"/>
-        <v>{dwID=102012,nFrame=47,szNote="算命先生·话玄虚",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="算命先生·话玄虚",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=99178,nFrame=47,szNote="落单少侠·瀛洲梦",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="落单少侠·瀛洲梦",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="115" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A115" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B115">
-        <v>411</v>
+        <v>334</v>
       </c>
       <c r="W115" t="str">
-        <f t="shared" si="3"/>
-        <v>},[411]={</v>
+        <f t="shared" si="1"/>
+        <v>},[334]={</v>
       </c>
     </row>
     <row r="116" spans="1:23" x14ac:dyDescent="0.15">
       <c r="C116">
-        <v>65578</v>
+        <v>102012</v>
       </c>
       <c r="D116">
         <v>47</v>
       </c>
       <c r="I116" t="s">
-        <v>1693</v>
+        <v>1624</v>
       </c>
       <c r="J116" t="s">
         <v>1555</v>
@@ -20268,58 +20345,58 @@
         <v>1</v>
       </c>
       <c r="V116" t="s">
-        <v>1694</v>
+        <v>1855</v>
       </c>
       <c r="W116" t="str">
-        <f t="shared" si="3"/>
-        <v>{dwID=65578,nFrame=47,szNote="绿头鸭·滴水恩",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="绿头鸭·滴水恩",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=102012,nFrame=47,szNote="算命先生·话玄虚",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="算命先生·话玄虚",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="117" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="C117">
-        <v>127964</v>
-      </c>
-      <c r="D117">
+      <c r="A117" t="s">
+        <v>26</v>
+      </c>
+      <c r="B117">
+        <v>411</v>
+      </c>
+      <c r="W117" t="str">
+        <f t="shared" si="1"/>
+        <v>},[411]={</v>
+      </c>
+    </row>
+    <row r="118" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="C118">
+        <v>65578</v>
+      </c>
+      <c r="D118">
         <v>47</v>
       </c>
-      <c r="I117" t="s">
-        <v>1695</v>
-      </c>
-      <c r="J117" t="s">
+      <c r="I118" t="s">
+        <v>1625</v>
+      </c>
+      <c r="J118" t="s">
         <v>1555</v>
       </c>
-      <c r="P117">
-        <v>1</v>
-      </c>
-      <c r="V117" t="s">
-        <v>1696</v>
-      </c>
-      <c r="W117" t="str">
-        <f t="shared" si="3"/>
-        <v>{dwID=127964,nFrame=47,szNote="宋旅·路投石",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="宋旅·路投石",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
-      </c>
-    </row>
-    <row r="118" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A118" t="s">
-        <v>435</v>
-      </c>
-      <c r="B118">
-        <v>455</v>
+      <c r="P118">
+        <v>1</v>
+      </c>
+      <c r="V118" t="s">
+        <v>1856</v>
       </c>
       <c r="W118" t="str">
-        <f t="shared" si="3"/>
-        <v>},[455]={</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=65578,nFrame=47,szNote="绿头鸭·滴水恩",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="绿头鸭·滴水恩",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="119" spans="1:23" x14ac:dyDescent="0.15">
       <c r="C119">
-        <v>104935</v>
+        <v>127964</v>
       </c>
       <c r="D119">
         <v>47</v>
       </c>
       <c r="I119" t="s">
-        <v>1697</v>
+        <v>1626</v>
       </c>
       <c r="J119" t="s">
         <v>1555</v>
@@ -20328,34 +20405,34 @@
         <v>1</v>
       </c>
       <c r="V119" t="s">
-        <v>1698</v>
+        <v>1857</v>
       </c>
       <c r="W119" t="str">
-        <f t="shared" si="3"/>
-        <v>{dwID=104935,nFrame=47,szNote="曾莲·捉贼记",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="曾莲·捉贼记",nMaxDistance=20,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=127964,nFrame=47,szNote="宋旅·路投石",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="宋旅·路投石",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="120" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A120" t="s">
-        <v>450</v>
+        <v>435</v>
       </c>
       <c r="B120">
-        <v>471</v>
+        <v>455</v>
       </c>
       <c r="W120" t="str">
-        <f t="shared" si="3"/>
-        <v>},[471]={</v>
+        <f t="shared" si="1"/>
+        <v>},[455]={</v>
       </c>
     </row>
     <row r="121" spans="1:23" x14ac:dyDescent="0.15">
       <c r="C121">
-        <v>99555</v>
+        <v>104935</v>
       </c>
       <c r="D121">
         <v>47</v>
       </c>
       <c r="I121" t="s">
-        <v>1699</v>
+        <v>1627</v>
       </c>
       <c r="J121" t="s">
         <v>1555</v>
@@ -20364,23 +20441,23 @@
         <v>1</v>
       </c>
       <c r="V121" t="s">
-        <v>1700</v>
+        <v>1628</v>
       </c>
       <c r="W121" t="str">
-        <f t="shared" si="3"/>
-        <v>{dwID=99555,nFrame=47,szNote="泥鳅·一枝栖",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="泥鳅·一枝栖",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=104935,nFrame=47,szNote="曾莲·捉贼记",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="曾莲·捉贼记",nMaxDistance=20,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="122" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A122" t="s">
-        <v>463</v>
+        <v>450</v>
       </c>
       <c r="B122">
-        <v>486</v>
+        <v>471</v>
       </c>
       <c r="W122" t="str">
-        <f t="shared" si="3"/>
-        <v>},[486]={</v>
+        <f t="shared" si="1"/>
+        <v>},[471]={</v>
       </c>
     </row>
     <row r="123" spans="1:23" x14ac:dyDescent="0.15">
@@ -20391,7 +20468,7 @@
         <v>47</v>
       </c>
       <c r="I123" t="s">
-        <v>1699</v>
+        <v>1629</v>
       </c>
       <c r="J123" t="s">
         <v>1555</v>
@@ -20400,109 +20477,109 @@
         <v>1</v>
       </c>
       <c r="V123" t="s">
-        <v>1700</v>
+        <v>1858</v>
       </c>
       <c r="W123" t="str">
-        <f t="shared" si="3"/>
-        <v>{dwID=99555,nFrame=47,szNote="泥鳅·一枝栖",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="泥鳅·一枝栖",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=99555,nFrame=47,szNote="泥鳅·一枝栖",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="泥鳅·一枝栖",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="124" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A124" t="s">
-        <v>502</v>
+        <v>463</v>
       </c>
       <c r="B124">
-        <v>526</v>
+        <v>486</v>
       </c>
       <c r="W124" t="str">
-        <f t="shared" si="3"/>
-        <v>},[526]={</v>
+        <f t="shared" si="1"/>
+        <v>},[486]={</v>
       </c>
     </row>
     <row r="125" spans="1:23" x14ac:dyDescent="0.15">
       <c r="C125">
-        <v>106832</v>
+        <v>99555</v>
       </c>
       <c r="D125">
         <v>47</v>
       </c>
       <c r="I125" t="s">
-        <v>1701</v>
+        <v>1629</v>
       </c>
       <c r="J125" t="s">
         <v>1555</v>
       </c>
-      <c r="O125">
-        <v>1</v>
-      </c>
       <c r="P125">
         <v>1</v>
       </c>
       <c r="V125" t="s">
-        <v>1702</v>
+        <v>1858</v>
       </c>
       <c r="W125" t="str">
-        <f t="shared" si="3"/>
-        <v>{dwID=106832,nFrame=47,szNote="刘山夕·念旧林",col={0,255,255,},[3]={bCenterAlarm=true,bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="刘山夕·念旧林",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=99555,nFrame=47,szNote="泥鳅·一枝栖",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="泥鳅·一枝栖",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="126" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A126" t="s">
-        <v>547</v>
+        <v>502</v>
       </c>
       <c r="B126">
-        <v>578</v>
+        <v>526</v>
       </c>
       <c r="W126" t="str">
-        <f t="shared" si="3"/>
-        <v>},[578]={</v>
+        <f t="shared" si="1"/>
+        <v>},[526]={</v>
       </c>
     </row>
     <row r="127" spans="1:23" x14ac:dyDescent="0.15">
       <c r="C127">
-        <v>112804</v>
+        <v>106832</v>
       </c>
       <c r="D127">
         <v>47</v>
       </c>
       <c r="I127" t="s">
-        <v>1703</v>
+        <v>1630</v>
       </c>
       <c r="J127" t="s">
         <v>1555</v>
       </c>
+      <c r="O127">
+        <v>1</v>
+      </c>
       <c r="P127">
         <v>1</v>
       </c>
       <c r="V127" t="s">
-        <v>1704</v>
+        <v>1997</v>
       </c>
       <c r="W127" t="str">
-        <f t="shared" si="3"/>
-        <v>{dwID=112804,nFrame=47,szNote="小肥花·重洋客",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="小肥花·重洋客",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=106832,nFrame=47,szNote="刘山夕·念旧林",col={0,255,255,},[3]={bCenterAlarm=true,bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="刘山夕·念旧林",nMaxDistance=120,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="128" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A128" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B128">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="W128" t="str">
-        <f t="shared" si="3"/>
-        <v>},[579]={</v>
+        <f t="shared" si="1"/>
+        <v>},[578]={</v>
       </c>
     </row>
     <row r="129" spans="1:23" x14ac:dyDescent="0.15">
       <c r="C129">
-        <v>122983</v>
+        <v>112804</v>
       </c>
       <c r="D129">
         <v>47</v>
       </c>
       <c r="I129" t="s">
-        <v>1705</v>
+        <v>1631</v>
       </c>
       <c r="J129" t="s">
         <v>1555</v>
@@ -20511,58 +20588,58 @@
         <v>1</v>
       </c>
       <c r="V129" t="s">
-        <v>1706</v>
+        <v>1859</v>
       </c>
       <c r="W129" t="str">
-        <f t="shared" si="3"/>
-        <v>{dwID=122983,nFrame=47,szNote="礼礼·乱红鸾",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="礼礼·乱红鸾",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=112804,nFrame=47,szNote="小肥花·重洋客",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="小肥花·重洋客",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="130" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="C130">
-        <v>126031</v>
-      </c>
-      <c r="D130">
+      <c r="A130" t="s">
+        <v>548</v>
+      </c>
+      <c r="B130">
+        <v>579</v>
+      </c>
+      <c r="W130" t="str">
+        <f t="shared" ref="W130:W144" si="2">IF(ISBLANK(B130)=FALSE,IF(ISBLANK(B129),"},["&amp;B130&amp;"]={","["&amp;B130&amp;"]={"),IF(AND(ISBLANK(B130),ISBLANK(D130),ISBLANK(C130),OR(ISBLANK(B129)=FALSE,ISBLANK(D129)=FALSE,ISBLANK(C129)=FALSE)),"},},}",IF(ISBLANK(C130),"","{dwID="&amp;C130&amp;","&amp;"nFrame="&amp;D130&amp;","&amp;IF(E130&gt;0,"nCount="&amp;E130&amp;",","")&amp;IF(F130&gt;0,"bAllLeave=true,","")&amp;IF(G130&lt;&gt;"","szName="""&amp;G130&amp;""",","")&amp;IF(H130&lt;&gt;"","tKungFu={"&amp;H130&amp;"},","")&amp;IF(I130&lt;&gt;"","szNote="""&amp;I130&amp;""",","")&amp;IF(J130&lt;&gt;"","col={"&amp;J130&amp;"},","")&amp;"[3]={"&amp;IF(K130&lt;&gt;"","tMark={"&amp;K130&amp;"},","")&amp;IF(L130&lt;&gt;"","szVoice="""&amp;L130&amp;""",","")&amp;IF(M130&gt;0,"bTeamChannel=true,","")&amp;IF(N130&gt;0,"bWhisperChannel=true,","")&amp;IF(O130&gt;0,"bCenterAlarm=true,","")&amp;IF(P130&gt;0,"bScreenHead=true,","")&amp;IF(Q130&gt;0,"bFullScreen=true,","")&amp;"},"&amp;"[4]={"&amp;IF(R130&lt;&gt;"","szVoice="""&amp;R130&amp;""",","")&amp;IF(S130&gt;0,"bTeamChannel=true,","")&amp;IF(T130&gt;0,"bWhisperChannel=true,","")&amp;IF(U130&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(V130&lt;&gt;"","aFocus={"&amp;V130&amp;"},","")&amp;IF(X130&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,X130:AAA130)&amp;"},","")&amp;"},")))</f>
+        <v>},[579]={</v>
+      </c>
+    </row>
+    <row r="131" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="C131">
+        <v>122983</v>
+      </c>
+      <c r="D131">
         <v>47</v>
       </c>
-      <c r="I130" t="s">
-        <v>1707</v>
-      </c>
-      <c r="J130" t="s">
+      <c r="I131" t="s">
+        <v>1632</v>
+      </c>
+      <c r="J131" t="s">
         <v>1555</v>
       </c>
-      <c r="P130">
-        <v>1</v>
-      </c>
-      <c r="V130" t="s">
-        <v>1708</v>
-      </c>
-      <c r="W130" t="str">
-        <f t="shared" ref="W130:W139" si="4">IF(ISBLANK(B130)=FALSE,IF(ISBLANK(B129),"},["&amp;B130&amp;"]={","["&amp;B130&amp;"]={"),IF(AND(ISBLANK(B130),ISBLANK(D130),ISBLANK(C130),OR(ISBLANK(B129)=FALSE,ISBLANK(D129)=FALSE,ISBLANK(C129)=FALSE)),"},},}",IF(ISBLANK(C130),"","{dwID="&amp;C130&amp;","&amp;"nFrame="&amp;D130&amp;","&amp;IF(E130&gt;0,"nCount="&amp;E130&amp;",","")&amp;IF(F130&gt;0,"bAllLeave=true,","")&amp;IF(G130&lt;&gt;"","szName="""&amp;G130&amp;""",","")&amp;IF(H130&lt;&gt;"","tKungFu={"&amp;H130&amp;"},","")&amp;IF(I130&lt;&gt;"","szNote="""&amp;I130&amp;""",","")&amp;IF(J130&lt;&gt;"","col={"&amp;J130&amp;"},","")&amp;"[3]={"&amp;IF(K130&lt;&gt;"","tMark={"&amp;K130&amp;"},","")&amp;IF(L130&lt;&gt;"","szVoice="""&amp;L130&amp;""",","")&amp;IF(M130&gt;0,"bTeamChannel=true,","")&amp;IF(N130&gt;0,"bWhisperChannel=true,","")&amp;IF(O130&gt;0,"bCenterAlarm=true,","")&amp;IF(P130&gt;0,"bScreenHead=true,","")&amp;IF(Q130&gt;0,"bFullScreen=true,","")&amp;"},"&amp;"[4]={"&amp;IF(R130&lt;&gt;"","szVoice="""&amp;R130&amp;""",","")&amp;IF(S130&gt;0,"bTeamChannel=true,","")&amp;IF(T130&gt;0,"bWhisperChannel=true,","")&amp;IF(U130&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(V130&lt;&gt;"","aFocus={"&amp;V130&amp;"},","")&amp;IF(X130&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,X130:AAA130)&amp;"},","")&amp;"},")))</f>
-        <v>{dwID=126031,nFrame=47,szNote="晒太阳·寓天涯",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="晒太阳·寓天涯",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
-      </c>
-    </row>
-    <row r="131" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A131" t="s">
-        <v>549</v>
-      </c>
-      <c r="B131">
-        <v>580</v>
+      <c r="P131">
+        <v>1</v>
+      </c>
+      <c r="V131" t="s">
+        <v>1860</v>
       </c>
       <c r="W131" t="str">
-        <f t="shared" si="4"/>
-        <v>},[580]={</v>
+        <f t="shared" si="2"/>
+        <v>{dwID=122983,nFrame=47,szNote="礼礼·乱红鸾",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="礼礼·乱红鸾",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="132" spans="1:23" x14ac:dyDescent="0.15">
       <c r="C132">
-        <v>112639</v>
+        <v>126031</v>
       </c>
       <c r="D132">
         <v>47</v>
       </c>
       <c r="I132" t="s">
-        <v>1709</v>
+        <v>1633</v>
       </c>
       <c r="J132" t="s">
         <v>1555</v>
@@ -20571,34 +20648,34 @@
         <v>1</v>
       </c>
       <c r="V132" t="s">
-        <v>1710</v>
+        <v>1861</v>
       </c>
       <c r="W132" t="str">
-        <f t="shared" si="4"/>
-        <v>{dwID=112639,nFrame=47,szNote="崔有恒·子夜歌",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="崔有恒·子夜歌",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="2"/>
+        <v>{dwID=126031,nFrame=47,szNote="晒太阳·寓天涯",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="晒太阳·寓天涯",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="133" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A133" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B133">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="W133" t="str">
-        <f t="shared" si="4"/>
-        <v>},[581]={</v>
+        <f t="shared" si="2"/>
+        <v>},[580]={</v>
       </c>
     </row>
     <row r="134" spans="1:23" x14ac:dyDescent="0.15">
       <c r="C134">
-        <v>132204</v>
+        <v>112639</v>
       </c>
       <c r="D134">
         <v>47</v>
       </c>
       <c r="I134" t="s">
-        <v>1711</v>
+        <v>1634</v>
       </c>
       <c r="J134" t="s">
         <v>1555</v>
@@ -20607,58 +20684,58 @@
         <v>1</v>
       </c>
       <c r="V134" t="s">
-        <v>1712</v>
+        <v>1862</v>
       </c>
       <c r="W134" t="str">
-        <f t="shared" si="4"/>
-        <v>{dwID=132204,nFrame=47,szNote="姜堰·授太平",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="姜堰·授太平",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="2"/>
+        <v>{dwID=112639,nFrame=47,szNote="崔有恒·子夜歌",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="崔有恒·子夜歌",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="135" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="C135">
-        <v>122790</v>
-      </c>
-      <c r="D135">
+      <c r="A135" t="s">
+        <v>550</v>
+      </c>
+      <c r="B135">
+        <v>581</v>
+      </c>
+      <c r="W135" t="str">
+        <f t="shared" si="2"/>
+        <v>},[581]={</v>
+      </c>
+    </row>
+    <row r="136" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="C136">
+        <v>132204</v>
+      </c>
+      <c r="D136">
         <v>47</v>
       </c>
-      <c r="I135" t="s">
-        <v>1713</v>
-      </c>
-      <c r="J135" t="s">
+      <c r="I136" t="s">
+        <v>1635</v>
+      </c>
+      <c r="J136" t="s">
         <v>1555</v>
       </c>
-      <c r="P135">
-        <v>1</v>
-      </c>
-      <c r="V135" t="s">
-        <v>1714</v>
-      </c>
-      <c r="W135" t="str">
-        <f t="shared" si="4"/>
-        <v>{dwID=122790,nFrame=47,szNote="逗逗·夜哀鸣",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="逗逗·夜哀鸣",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
-      </c>
-    </row>
-    <row r="136" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A136" t="s">
-        <v>29</v>
-      </c>
-      <c r="B136">
-        <v>582</v>
+      <c r="P136">
+        <v>1</v>
+      </c>
+      <c r="V136" t="s">
+        <v>1863</v>
       </c>
       <c r="W136" t="str">
-        <f t="shared" si="4"/>
-        <v>},[582]={</v>
+        <f t="shared" si="2"/>
+        <v>{dwID=132204,nFrame=47,szNote="姜堰·授太平",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="姜堰·授太平",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="137" spans="1:23" x14ac:dyDescent="0.15">
       <c r="C137">
-        <v>113068</v>
+        <v>122790</v>
       </c>
       <c r="D137">
         <v>47</v>
       </c>
       <c r="I137" t="s">
-        <v>1715</v>
+        <v>1636</v>
       </c>
       <c r="J137" t="s">
         <v>1555</v>
@@ -20667,34 +20744,34 @@
         <v>1</v>
       </c>
       <c r="V137" t="s">
-        <v>1716</v>
+        <v>1864</v>
       </c>
       <c r="W137" t="str">
-        <f t="shared" si="4"/>
-        <v>{dwID=113068,nFrame=47,szNote="槲生·故岁辞",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="槲生·故岁辞",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <f t="shared" si="2"/>
+        <v>{dwID=122790,nFrame=47,szNote="逗逗·夜哀鸣",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="逗逗·夜哀鸣",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="138" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A138" t="s">
-        <v>1989</v>
+        <v>29</v>
       </c>
       <c r="B138">
-        <v>713</v>
+        <v>582</v>
       </c>
       <c r="W138" t="str">
-        <f t="shared" ref="W138:W140" si="5">IF(ISBLANK(B138)=FALSE,IF(ISBLANK(B137),"},["&amp;B138&amp;"]={","["&amp;B138&amp;"]={"),IF(AND(ISBLANK(B138),ISBLANK(D138),ISBLANK(C138),OR(ISBLANK(B137)=FALSE,ISBLANK(D137)=FALSE,ISBLANK(C137)=FALSE)),"},},}",IF(ISBLANK(C138),"","{dwID="&amp;C138&amp;","&amp;"nFrame="&amp;D138&amp;","&amp;IF(E138&gt;0,"nCount="&amp;E138&amp;",","")&amp;IF(F138&gt;0,"bAllLeave=true,","")&amp;IF(G138&lt;&gt;"","szName="""&amp;G138&amp;""",","")&amp;IF(H138&lt;&gt;"","tKungFu={"&amp;H138&amp;"},","")&amp;IF(I138&lt;&gt;"","szNote="""&amp;I138&amp;""",","")&amp;IF(J138&lt;&gt;"","col={"&amp;J138&amp;"},","")&amp;"[3]={"&amp;IF(K138&lt;&gt;"","tMark={"&amp;K138&amp;"},","")&amp;IF(L138&lt;&gt;"","szVoice="""&amp;L138&amp;""",","")&amp;IF(M138&gt;0,"bTeamChannel=true,","")&amp;IF(N138&gt;0,"bWhisperChannel=true,","")&amp;IF(O138&gt;0,"bCenterAlarm=true,","")&amp;IF(P138&gt;0,"bScreenHead=true,","")&amp;IF(Q138&gt;0,"bFullScreen=true,","")&amp;"},"&amp;"[4]={"&amp;IF(R138&lt;&gt;"","szVoice="""&amp;R138&amp;""",","")&amp;IF(S138&gt;0,"bTeamChannel=true,","")&amp;IF(T138&gt;0,"bWhisperChannel=true,","")&amp;IF(U138&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(V138&lt;&gt;"","aFocus={"&amp;V138&amp;"},","")&amp;IF(X138&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,X138:AAA138)&amp;"},","")&amp;"},")))</f>
-        <v>},[713]={</v>
+        <f t="shared" si="2"/>
+        <v>},[582]={</v>
       </c>
     </row>
     <row r="139" spans="1:23" x14ac:dyDescent="0.15">
       <c r="C139">
-        <v>135609</v>
+        <v>113068</v>
       </c>
       <c r="D139">
         <v>47</v>
       </c>
       <c r="I139" t="s">
-        <v>1990</v>
+        <v>1637</v>
       </c>
       <c r="J139" t="s">
         <v>1555</v>
@@ -20703,16 +20780,88 @@
         <v>1</v>
       </c>
       <c r="V139" t="s">
-        <v>1991</v>
+        <v>1865</v>
       </c>
       <c r="W139" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
+        <v>{dwID=113068,nFrame=47,szNote="槲生·故岁辞",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="槲生·故岁辞",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+      </c>
+    </row>
+    <row r="140" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A140" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B140">
+        <v>713</v>
+      </c>
+      <c r="W140" t="str">
+        <f t="shared" si="2"/>
+        <v>},[713]={</v>
+      </c>
+    </row>
+    <row r="141" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="C141">
+        <v>135609</v>
+      </c>
+      <c r="D141">
+        <v>47</v>
+      </c>
+      <c r="I141" t="s">
+        <v>1794</v>
+      </c>
+      <c r="J141" t="s">
+        <v>1555</v>
+      </c>
+      <c r="P141">
+        <v>1</v>
+      </c>
+      <c r="V141" t="s">
+        <v>1795</v>
+      </c>
+      <c r="W141" t="str">
+        <f t="shared" si="2"/>
         <v>{dwID=135609,nFrame=47,szNote="米迦尔·追光记",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="米迦尔·追光记",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
-    <row r="140" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="W140" t="str">
-        <f t="shared" si="5"/>
+    <row r="142" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A142" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B142">
+        <v>718</v>
+      </c>
+      <c r="W142" t="str">
+        <f t="shared" si="2"/>
+        <v>},[718]={</v>
+      </c>
+    </row>
+    <row r="143" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="C143">
+        <v>137476</v>
+      </c>
+      <c r="D143">
+        <v>47</v>
+      </c>
+      <c r="I143" t="s">
+        <v>1796</v>
+      </c>
+      <c r="J143" t="s">
+        <v>1555</v>
+      </c>
+      <c r="P143">
+        <v>1</v>
+      </c>
+      <c r="V143" t="s">
+        <v>1797</v>
+      </c>
+      <c r="W143" t="str">
+        <f t="shared" si="2"/>
+        <v>{dwID=137476,nFrame=47,szNote="刘一竿·碗中仙",col={0,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="刘一竿·碗中仙",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+      </c>
+    </row>
+    <row r="144" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="W144" t="str">
+        <f t="shared" si="2"/>
         <v>},},}</v>
       </c>
     </row>
@@ -20757,40 +20906,40 @@
         <v>1491</v>
       </c>
       <c r="J1" t="s">
-        <v>1717</v>
+        <v>1638</v>
       </c>
       <c r="K1" t="s">
-        <v>1718</v>
+        <v>1639</v>
       </c>
       <c r="L1" t="s">
-        <v>1719</v>
+        <v>1640</v>
       </c>
       <c r="M1" t="s">
-        <v>1720</v>
+        <v>1641</v>
       </c>
       <c r="N1" t="s">
-        <v>1721</v>
+        <v>1642</v>
       </c>
       <c r="O1" t="s">
-        <v>1722</v>
+        <v>1643</v>
       </c>
       <c r="P1" t="s">
-        <v>1723</v>
+        <v>1644</v>
       </c>
       <c r="Q1" t="s">
-        <v>1724</v>
+        <v>1645</v>
       </c>
       <c r="R1" t="s">
-        <v>1725</v>
+        <v>1646</v>
       </c>
       <c r="S1" t="s">
-        <v>1726</v>
+        <v>1647</v>
       </c>
       <c r="T1" t="s">
         <v>1551</v>
       </c>
       <c r="U1" t="s">
-        <v>1727</v>
+        <v>1648</v>
       </c>
       <c r="V1" t="s">
         <v>1523</v>
@@ -20813,7 +20962,7 @@
         <v>11143</v>
       </c>
       <c r="H3" t="s">
-        <v>1728</v>
+        <v>1649</v>
       </c>
       <c r="I3" t="s">
         <v>1555</v>
@@ -20822,11 +20971,11 @@
         <v>1</v>
       </c>
       <c r="T3" t="s">
-        <v>1729</v>
+        <v>1880</v>
       </c>
       <c r="U3" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=11143,szNote="盆栽·燕啼松",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="盆栽·燕啼松",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=11143,szNote="盆栽·燕啼松",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="盆栽·燕啼松",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.15">
@@ -20834,7 +20983,7 @@
         <v>4696</v>
       </c>
       <c r="H4" t="s">
-        <v>1730</v>
+        <v>1650</v>
       </c>
       <c r="I4" t="s">
         <v>1555</v>
@@ -20843,11 +20992,11 @@
         <v>1</v>
       </c>
       <c r="T4" t="s">
-        <v>1731</v>
+        <v>1881</v>
       </c>
       <c r="U4" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=4696,szNote="散落的书页·孩童书",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="散落的书页·孩童书",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=4696,szNote="散落的书页·孩童书",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="散落的书页·孩童书",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.15">
@@ -20867,7 +21016,7 @@
         <v>4582</v>
       </c>
       <c r="H6" t="s">
-        <v>1732</v>
+        <v>1651</v>
       </c>
       <c r="I6" t="s">
         <v>1555</v>
@@ -20879,7 +21028,7 @@
         <v>1</v>
       </c>
       <c r="T6" t="s">
-        <v>1733</v>
+        <v>1976</v>
       </c>
       <c r="U6" t="str">
         <f t="shared" si="0"/>
@@ -20903,7 +21052,7 @@
         <v>5321</v>
       </c>
       <c r="H8" t="s">
-        <v>1734</v>
+        <v>1652</v>
       </c>
       <c r="I8" t="s">
         <v>1555</v>
@@ -20915,7 +21064,7 @@
         <v>1</v>
       </c>
       <c r="T8" t="s">
-        <v>1735</v>
+        <v>1977</v>
       </c>
       <c r="U8" t="str">
         <f t="shared" si="0"/>
@@ -20927,7 +21076,7 @@
         <v>6914</v>
       </c>
       <c r="H9" t="s">
-        <v>1736</v>
+        <v>1653</v>
       </c>
       <c r="I9" t="s">
         <v>1555</v>
@@ -20936,11 +21085,11 @@
         <v>1</v>
       </c>
       <c r="T9" t="s">
-        <v>1737</v>
+        <v>1882</v>
       </c>
       <c r="U9" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=6914,szNote="埋东西的痕迹·烟花戏",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="埋东西的痕迹·烟花戏",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=6914,szNote="埋东西的痕迹·烟花戏",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="埋东西的痕迹·烟花戏",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.15">
@@ -20948,7 +21097,7 @@
         <v>6987</v>
       </c>
       <c r="H10" t="s">
-        <v>1738</v>
+        <v>1654</v>
       </c>
       <c r="I10" t="s">
         <v>1555</v>
@@ -20957,11 +21106,11 @@
         <v>1</v>
       </c>
       <c r="T10" t="s">
-        <v>1739</v>
+        <v>1883</v>
       </c>
       <c r="U10" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=6987,szNote="奇怪的土堆·归安志",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="奇怪的土堆·归安志",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=6987,szNote="奇怪的土堆·归安志",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="奇怪的土堆·归安志",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.15">
@@ -20969,7 +21118,7 @@
         <v>7763</v>
       </c>
       <c r="H11" t="s">
-        <v>1740</v>
+        <v>1655</v>
       </c>
       <c r="I11" t="s">
         <v>1555</v>
@@ -20978,11 +21127,11 @@
         <v>1</v>
       </c>
       <c r="T11" t="s">
-        <v>1741</v>
+        <v>1884</v>
       </c>
       <c r="U11" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=7763,szNote="苜蓿草·谜书生",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="苜蓿草·谜书生",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=7763,szNote="苜蓿草·谜书生",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="苜蓿草·谜书生",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.15">
@@ -20990,7 +21139,7 @@
         <v>7772</v>
       </c>
       <c r="H12" t="s">
-        <v>1742</v>
+        <v>1656</v>
       </c>
       <c r="I12" t="s">
         <v>1555</v>
@@ -20999,11 +21148,11 @@
         <v>1</v>
       </c>
       <c r="T12" t="s">
-        <v>1743</v>
+        <v>1885</v>
       </c>
       <c r="U12" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=7772,szNote="带血的金钗·谜书生",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="带血的金钗·谜书生",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=7772,szNote="带血的金钗·谜书生",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="带血的金钗·谜书生",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.15">
@@ -21011,7 +21160,7 @@
         <v>8045</v>
       </c>
       <c r="H13" t="s">
-        <v>1744</v>
+        <v>1657</v>
       </c>
       <c r="I13" t="s">
         <v>1555</v>
@@ -21020,11 +21169,11 @@
         <v>1</v>
       </c>
       <c r="T13" t="s">
-        <v>1745</v>
+        <v>1886</v>
       </c>
       <c r="U13" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=8045,szNote="几页书稿·江湖录",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="几页书稿·江湖录",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=8045,szNote="几页书稿·江湖录",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="几页书稿·江湖录",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.15">
@@ -21044,7 +21193,7 @@
         <v>4706</v>
       </c>
       <c r="H15" t="s">
-        <v>1746</v>
+        <v>1658</v>
       </c>
       <c r="I15" t="s">
         <v>1555</v>
@@ -21056,11 +21205,11 @@
         <v>1</v>
       </c>
       <c r="T15" t="s">
-        <v>1747</v>
+        <v>1978</v>
       </c>
       <c r="U15" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=4706,szNote="小土堆·小花",col={0,255,255,},[17]={bCenterAlarm=true,bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="小土堆·小花",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=4706,szNote="小土堆·小花",col={0,255,255,},[17]={bCenterAlarm=true,bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="小土堆·小花",nMaxDistance=120,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.15">
@@ -21068,7 +21217,7 @@
         <v>6988</v>
       </c>
       <c r="H16" t="s">
-        <v>1748</v>
+        <v>1659</v>
       </c>
       <c r="I16" t="s">
         <v>1555</v>
@@ -21077,11 +21226,11 @@
         <v>1</v>
       </c>
       <c r="T16" t="s">
-        <v>1749</v>
+        <v>1887</v>
       </c>
       <c r="U16" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=6988,szNote="遗失的包裹·归安志",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="遗失的包裹·归安志",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=6988,szNote="遗失的包裹·归安志",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="遗失的包裹·归安志",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.15">
@@ -21089,7 +21238,7 @@
         <v>10680</v>
       </c>
       <c r="H17" t="s">
-        <v>1750</v>
+        <v>1660</v>
       </c>
       <c r="I17" t="s">
         <v>1555</v>
@@ -21098,11 +21247,11 @@
         <v>1</v>
       </c>
       <c r="T17" t="s">
-        <v>1751</v>
+        <v>1888</v>
       </c>
       <c r="U17" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=10680,szNote="招牌菜·义千金",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="招牌菜·义千金",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=10680,szNote="招牌菜·义千金",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="招牌菜·义千金",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.15">
@@ -21110,7 +21259,7 @@
         <v>10681</v>
       </c>
       <c r="H18" t="s">
-        <v>1752</v>
+        <v>1661</v>
       </c>
       <c r="I18" t="s">
         <v>1555</v>
@@ -21119,11 +21268,11 @@
         <v>1</v>
       </c>
       <c r="T18" t="s">
-        <v>1753</v>
+        <v>1889</v>
       </c>
       <c r="U18" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=10681,szNote="秘方·义千金",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="秘方·义千金",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=10681,szNote="秘方·义千金",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="秘方·义千金",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.15">
@@ -21143,7 +21292,7 @@
         <v>4776</v>
       </c>
       <c r="H20" t="s">
-        <v>1754</v>
+        <v>1662</v>
       </c>
       <c r="I20" t="s">
         <v>1555</v>
@@ -21152,11 +21301,11 @@
         <v>1</v>
       </c>
       <c r="T20" t="s">
-        <v>1755</v>
+        <v>1890</v>
       </c>
       <c r="U20" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=4776,szNote="小泥娃娃·红衣歌",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="小泥娃娃·红衣歌",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=4776,szNote="小泥娃娃·红衣歌",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="小泥娃娃·红衣歌",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.15">
@@ -21164,7 +21313,7 @@
         <v>6986</v>
       </c>
       <c r="H21" t="s">
-        <v>1756</v>
+        <v>1663</v>
       </c>
       <c r="I21" t="s">
         <v>1555</v>
@@ -21173,11 +21322,11 @@
         <v>1</v>
       </c>
       <c r="T21" t="s">
-        <v>1757</v>
+        <v>1891</v>
       </c>
       <c r="U21" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=6986,szNote="古旧的卷轴·归安志",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="古旧的卷轴·归安志",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=6986,szNote="古旧的卷轴·归安志",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="古旧的卷轴·归安志",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.15">
@@ -21197,7 +21346,7 @@
         <v>6093</v>
       </c>
       <c r="H23" t="s">
-        <v>1758</v>
+        <v>1664</v>
       </c>
       <c r="I23" t="s">
         <v>1555</v>
@@ -21206,11 +21355,11 @@
         <v>1</v>
       </c>
       <c r="T23" t="s">
-        <v>1759</v>
+        <v>1892</v>
       </c>
       <c r="U23" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=6093,szNote="诱捕的笼子·破晓鸣",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="诱捕的笼子·破晓鸣",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=6093,szNote="诱捕的笼子·破晓鸣",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="诱捕的笼子·破晓鸣",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.15">
@@ -21230,7 +21379,7 @@
         <v>4713</v>
       </c>
       <c r="H25" t="s">
-        <v>1760</v>
+        <v>1665</v>
       </c>
       <c r="I25" t="s">
         <v>1555</v>
@@ -21242,7 +21391,7 @@
         <v>1</v>
       </c>
       <c r="T25" t="s">
-        <v>1761</v>
+        <v>1979</v>
       </c>
       <c r="U25" t="str">
         <f t="shared" si="0"/>
@@ -21254,7 +21403,7 @@
         <v>5158</v>
       </c>
       <c r="H26" t="s">
-        <v>1762</v>
+        <v>1666</v>
       </c>
       <c r="I26" t="s">
         <v>1555</v>
@@ -21263,11 +21412,11 @@
         <v>1</v>
       </c>
       <c r="T26" t="s">
-        <v>1763</v>
+        <v>1893</v>
       </c>
       <c r="U26" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=5158,szNote="沙土堆·枫林酒",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="沙土堆·枫林酒",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=5158,szNote="沙土堆·枫林酒",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="沙土堆·枫林酒",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.15">
@@ -21287,7 +21436,7 @@
         <v>5245</v>
       </c>
       <c r="H28" t="s">
-        <v>1764</v>
+        <v>1667</v>
       </c>
       <c r="I28" t="s">
         <v>1555</v>
@@ -21296,11 +21445,11 @@
         <v>1</v>
       </c>
       <c r="T28" t="s">
-        <v>1765</v>
+        <v>1894</v>
       </c>
       <c r="U28" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=5245,szNote="陈旧的宝盒·三山四海",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="陈旧的宝盒·三山",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=5245,szNote="陈旧的宝盒·三山四海",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="陈旧的宝盒·三山",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.15">
@@ -21308,7 +21457,7 @@
         <v>5052</v>
       </c>
       <c r="H29" t="s">
-        <v>1766</v>
+        <v>1668</v>
       </c>
       <c r="I29" t="s">
         <v>1555</v>
@@ -21320,7 +21469,7 @@
         <v>1</v>
       </c>
       <c r="T29" t="s">
-        <v>1767</v>
+        <v>1980</v>
       </c>
       <c r="U29" t="str">
         <f t="shared" si="0"/>
@@ -21332,7 +21481,7 @@
         <v>6985</v>
       </c>
       <c r="H30" t="s">
-        <v>1768</v>
+        <v>1669</v>
       </c>
       <c r="I30" t="s">
         <v>1555</v>
@@ -21341,11 +21490,11 @@
         <v>1</v>
       </c>
       <c r="T30" t="s">
-        <v>1769</v>
+        <v>1895</v>
       </c>
       <c r="U30" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=6985,szNote="张老头的竹筐·归安志",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="张老头的竹筐·归安志",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=6985,szNote="张老头的竹筐·归安志",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="张老头的竹筐·归安志",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.15">
@@ -21353,7 +21502,7 @@
         <v>9637</v>
       </c>
       <c r="H31" t="s">
-        <v>1770</v>
+        <v>1670</v>
       </c>
       <c r="I31" t="s">
         <v>1555</v>
@@ -21362,11 +21511,11 @@
         <v>1</v>
       </c>
       <c r="T31" t="s">
-        <v>1771</v>
+        <v>1896</v>
       </c>
       <c r="U31" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=9637,szNote="落叶堆·鸠雀记",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="落叶堆·鸠雀记",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=9637,szNote="落叶堆·鸠雀记",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="落叶堆·鸠雀记",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.15">
@@ -21386,7 +21535,7 @@
         <v>5812</v>
       </c>
       <c r="H33" t="s">
-        <v>1772</v>
+        <v>1671</v>
       </c>
       <c r="I33" t="s">
         <v>1555</v>
@@ -21395,11 +21544,11 @@
         <v>1</v>
       </c>
       <c r="T33" t="s">
-        <v>1773</v>
+        <v>1897</v>
       </c>
       <c r="U33" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=5812,szNote="酒坛·捉妖记",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="酒坛·捉妖记",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=5812,szNote="酒坛·捉妖记",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="酒坛·捉妖记",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.15">
@@ -21407,7 +21556,7 @@
         <v>4774</v>
       </c>
       <c r="H34" t="s">
-        <v>1774</v>
+        <v>1672</v>
       </c>
       <c r="I34" t="s">
         <v>1555</v>
@@ -21416,11 +21565,11 @@
         <v>1</v>
       </c>
       <c r="T34" t="s">
-        <v>1775</v>
+        <v>1898</v>
       </c>
       <c r="U34" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=4774,szNote="藏着木头鱼的鱼篓·捉妖记",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="藏木头鱼的鱼篓·捉妖记",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=4774,szNote="藏着木头鱼的鱼篓·捉妖记",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="藏木头鱼的鱼篓·捉妖记",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.15">
@@ -21428,7 +21577,7 @@
         <v>4705</v>
       </c>
       <c r="H35" t="s">
-        <v>1776</v>
+        <v>1673</v>
       </c>
       <c r="I35" t="s">
         <v>1555</v>
@@ -21437,11 +21586,11 @@
         <v>1</v>
       </c>
       <c r="T35" t="s">
-        <v>1777</v>
+        <v>1899</v>
       </c>
       <c r="U35" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=4705,szNote="风筝·捉妖记",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="风筝·捉妖记",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=4705,szNote="风筝·捉妖记",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="风筝·捉妖记",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.15">
@@ -21449,7 +21598,7 @@
         <v>6915</v>
       </c>
       <c r="H36" t="s">
-        <v>1778</v>
+        <v>1674</v>
       </c>
       <c r="I36" t="s">
         <v>1555</v>
@@ -21458,11 +21607,11 @@
         <v>1</v>
       </c>
       <c r="T36" t="s">
-        <v>1779</v>
+        <v>1900</v>
       </c>
       <c r="U36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=6915,szNote="川芎·烟花戏",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="川芎·烟花戏",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=6915,szNote="川芎·烟花戏",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="川芎·烟花戏",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.15">
@@ -21482,7 +21631,7 @@
         <v>5154</v>
       </c>
       <c r="H38" t="s">
-        <v>1780</v>
+        <v>1675</v>
       </c>
       <c r="I38" t="s">
         <v>1555</v>
@@ -21494,7 +21643,7 @@
         <v>1</v>
       </c>
       <c r="T38" t="s">
-        <v>1781</v>
+        <v>1981</v>
       </c>
       <c r="U38" t="str">
         <f t="shared" si="0"/>
@@ -21518,7 +21667,7 @@
         <v>5054</v>
       </c>
       <c r="H40" t="s">
-        <v>1782</v>
+        <v>1676</v>
       </c>
       <c r="I40" t="s">
         <v>1555</v>
@@ -21527,11 +21676,11 @@
         <v>1</v>
       </c>
       <c r="T40" t="s">
-        <v>1783</v>
+        <v>1901</v>
       </c>
       <c r="U40" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=5054,szNote="一盏青头草·嘟嘟",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="一盏青头草·嘟嘟",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=5054,szNote="一盏青头草·嘟嘟",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="一盏青头草·嘟嘟",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.15">
@@ -21539,7 +21688,7 @@
         <v>6500</v>
       </c>
       <c r="H41" t="s">
-        <v>1784</v>
+        <v>1677</v>
       </c>
       <c r="I41" t="s">
         <v>1555</v>
@@ -21548,11 +21697,11 @@
         <v>1</v>
       </c>
       <c r="T41" t="s">
-        <v>1785</v>
+        <v>1902</v>
       </c>
       <c r="U41" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=6500,szNote="夏枯草·东海客",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="夏枯草·东海客",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=6500,szNote="夏枯草·东海客",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="夏枯草·东海客",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.15">
@@ -21560,7 +21709,7 @@
         <v>8762</v>
       </c>
       <c r="H42" t="s">
-        <v>1786</v>
+        <v>1678</v>
       </c>
       <c r="I42" t="s">
         <v>1555</v>
@@ -21569,11 +21718,11 @@
         <v>1</v>
       </c>
       <c r="T42" t="s">
-        <v>1787</v>
+        <v>1903</v>
       </c>
       <c r="U42" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=8762,szNote="半本秘诀·尘网中",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="半本秘诀·尘网中",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=8762,szNote="半本秘诀·尘网中",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="半本秘诀·尘网中",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.15">
@@ -21593,7 +21742,7 @@
         <v>6058</v>
       </c>
       <c r="H44" t="s">
-        <v>1788</v>
+        <v>1679</v>
       </c>
       <c r="I44" t="s">
         <v>1555</v>
@@ -21602,11 +21751,11 @@
         <v>1</v>
       </c>
       <c r="T44" t="s">
-        <v>1789</v>
+        <v>1904</v>
       </c>
       <c r="U44" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=6058,szNote="遗失的画纸·沙海谣",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="遗失的画纸·沙海谣",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=6058,szNote="遗失的画纸·沙海谣",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="遗失的画纸·沙海谣",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.15">
@@ -21614,7 +21763,7 @@
         <v>6708</v>
       </c>
       <c r="H45" t="s">
-        <v>1790</v>
+        <v>1680</v>
       </c>
       <c r="I45" t="s">
         <v>1555</v>
@@ -21623,11 +21772,11 @@
         <v>1</v>
       </c>
       <c r="T45" t="s">
-        <v>1791</v>
+        <v>1905</v>
       </c>
       <c r="U45" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=6708,szNote="深色的沙土堆·锋芒展",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="深色的沙土堆·锋芒展",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=6708,szNote="深色的沙土堆·锋芒展",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="深色的沙土堆·锋芒展",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.15">
@@ -21635,7 +21784,7 @@
         <v>6709</v>
       </c>
       <c r="H46" t="s">
-        <v>1792</v>
+        <v>1681</v>
       </c>
       <c r="I46" t="s">
         <v>1555</v>
@@ -21644,11 +21793,11 @@
         <v>1</v>
       </c>
       <c r="T46" t="s">
-        <v>1793</v>
+        <v>1906</v>
       </c>
       <c r="U46" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=6709,szNote="四散的弩箭·锋芒展",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="四散的弩箭·锋芒展",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=6709,szNote="四散的弩箭·锋芒展",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="四散的弩箭·锋芒展",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.15">
@@ -21656,7 +21805,7 @@
         <v>6861</v>
       </c>
       <c r="H47" t="s">
-        <v>1794</v>
+        <v>1682</v>
       </c>
       <c r="I47" t="s">
         <v>1555</v>
@@ -21665,11 +21814,11 @@
         <v>1</v>
       </c>
       <c r="T47" t="s">
-        <v>1795</v>
+        <v>1907</v>
       </c>
       <c r="U47" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=6861,szNote="篝火残骸·锋芒展",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="篝火残骸·锋芒展",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=6861,szNote="篝火残骸·锋芒展",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="篝火残骸·锋芒展",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.15">
@@ -21677,7 +21826,7 @@
         <v>6726</v>
       </c>
       <c r="H48" t="s">
-        <v>1796</v>
+        <v>1683</v>
       </c>
       <c r="I48" t="s">
         <v>1555</v>
@@ -21686,11 +21835,11 @@
         <v>1</v>
       </c>
       <c r="T48" t="s">
-        <v>1797</v>
+        <v>1908</v>
       </c>
       <c r="U48" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=6726,szNote="散落的刀兵·锋芒展",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="散落的刀兵·锋芒展",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=6726,szNote="散落的刀兵·锋芒展",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="散落的刀兵·锋芒展",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.15">
@@ -21698,7 +21847,7 @@
         <v>6727</v>
       </c>
       <c r="H49" t="s">
-        <v>1798</v>
+        <v>1684</v>
       </c>
       <c r="I49" t="s">
         <v>1555</v>
@@ -21707,11 +21856,11 @@
         <v>1</v>
       </c>
       <c r="T49" t="s">
-        <v>1799</v>
+        <v>1909</v>
       </c>
       <c r="U49" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=6727,szNote="商队货物·锋芒展",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="商队货物·锋芒展",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=6727,szNote="商队货物·锋芒展",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="商队货物·锋芒展",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.15">
@@ -21731,7 +21880,7 @@
         <v>5053</v>
       </c>
       <c r="H51" t="s">
-        <v>1800</v>
+        <v>1685</v>
       </c>
       <c r="I51" t="s">
         <v>1555</v>
@@ -21743,11 +21892,11 @@
         <v>1</v>
       </c>
       <c r="T51" t="s">
-        <v>1801</v>
+        <v>1982</v>
       </c>
       <c r="U51" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=5053,szNote="冰凌雪莲·冰蓝花客",col={0,255,255,},[17]={bCenterAlarm=true,bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="冰凌雪莲·冰蓝花客",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=5053,szNote="冰凌雪莲·冰蓝花客",col={0,255,255,},[17]={bCenterAlarm=true,bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="冰凌雪莲·冰蓝花客",nMaxDistance=120,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.15">
@@ -21767,7 +21916,7 @@
         <v>5051</v>
       </c>
       <c r="H53" t="s">
-        <v>1802</v>
+        <v>1686</v>
       </c>
       <c r="I53" t="s">
         <v>1555</v>
@@ -21779,7 +21928,7 @@
         <v>1</v>
       </c>
       <c r="T53" t="s">
-        <v>1803</v>
+        <v>1983</v>
       </c>
       <c r="U53" t="str">
         <f t="shared" si="0"/>
@@ -21803,7 +21952,7 @@
         <v>5245</v>
       </c>
       <c r="H55" t="s">
-        <v>1764</v>
+        <v>1667</v>
       </c>
       <c r="I55" t="s">
         <v>1555</v>
@@ -21812,11 +21961,11 @@
         <v>1</v>
       </c>
       <c r="T55" t="s">
-        <v>1765</v>
+        <v>1894</v>
       </c>
       <c r="U55" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=5245,szNote="陈旧的宝盒·三山四海",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="陈旧的宝盒·三山",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=5245,szNote="陈旧的宝盒·三山四海",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="陈旧的宝盒·三山",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.15">
@@ -21824,7 +21973,7 @@
         <v>5153</v>
       </c>
       <c r="H56" t="s">
-        <v>1804</v>
+        <v>1687</v>
       </c>
       <c r="I56" t="s">
         <v>1555</v>
@@ -21836,7 +21985,7 @@
         <v>1</v>
       </c>
       <c r="T56" t="s">
-        <v>1805</v>
+        <v>1984</v>
       </c>
       <c r="U56" t="str">
         <f t="shared" si="0"/>
@@ -21848,7 +21997,7 @@
         <v>4763</v>
       </c>
       <c r="H57" t="s">
-        <v>1806</v>
+        <v>1688</v>
       </c>
       <c r="I57" t="s">
         <v>1555</v>
@@ -21860,7 +22009,7 @@
         <v>1</v>
       </c>
       <c r="T57" t="s">
-        <v>1807</v>
+        <v>1985</v>
       </c>
       <c r="U57" t="str">
         <f t="shared" si="0"/>
@@ -21884,7 +22033,7 @@
         <v>5155</v>
       </c>
       <c r="H59" t="s">
-        <v>1808</v>
+        <v>1689</v>
       </c>
       <c r="I59" t="s">
         <v>1555</v>
@@ -21896,7 +22045,7 @@
         <v>1</v>
       </c>
       <c r="T59" t="s">
-        <v>1809</v>
+        <v>1986</v>
       </c>
       <c r="U59" t="str">
         <f t="shared" si="0"/>
@@ -21908,7 +22057,7 @@
         <v>6101</v>
       </c>
       <c r="H60" t="s">
-        <v>1810</v>
+        <v>1690</v>
       </c>
       <c r="I60" t="s">
         <v>1555</v>
@@ -21917,11 +22066,11 @@
         <v>1</v>
       </c>
       <c r="T60" t="s">
-        <v>1811</v>
+        <v>1910</v>
       </c>
       <c r="U60" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=6101,szNote="一个闪闪发光的物件·竹马情",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="闪闪发光的物件·竹马情",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=6101,szNote="一个闪闪发光的物件·竹马情",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="闪闪发光的物件·竹马情",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.15">
@@ -21941,7 +22090,7 @@
         <v>6366</v>
       </c>
       <c r="H62" t="s">
-        <v>1812</v>
+        <v>1691</v>
       </c>
       <c r="I62" t="s">
         <v>1555</v>
@@ -21950,11 +22099,11 @@
         <v>1</v>
       </c>
       <c r="T62" t="s">
-        <v>1813</v>
+        <v>1911</v>
       </c>
       <c r="U62" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=6366,szNote="小土堆·滇南行",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="小土堆·滇南行",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=6366,szNote="小土堆·滇南行",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="小土堆·滇南行",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.15">
@@ -21962,7 +22111,7 @@
         <v>6367</v>
       </c>
       <c r="H63" t="s">
-        <v>1814</v>
+        <v>1692</v>
       </c>
       <c r="I63" t="s">
         <v>1555</v>
@@ -21971,11 +22120,11 @@
         <v>1</v>
       </c>
       <c r="T63" t="s">
-        <v>1815</v>
+        <v>1912</v>
       </c>
       <c r="U63" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=6367,szNote="换颜草·滇南行",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="换颜草·滇南行",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=6367,szNote="换颜草·滇南行",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="换颜草·滇南行",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.15">
@@ -21983,14 +22132,14 @@
         <v>6514</v>
       </c>
       <c r="H64" t="s">
-        <v>1816</v>
+        <v>1693</v>
       </c>
       <c r="T64" t="s">
-        <v>1817</v>
+        <v>1913</v>
       </c>
       <c r="U64" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=6514,szNote="日记1·东海客",[17]={},[18]={},aFocus={{dwMapID=-1,szDisplay="日记1·东海客",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=6514,szNote="日记1·东海客",[17]={},[18]={},aFocus={{dwMapID=-1,szDisplay="日记1·东海客",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.15">
@@ -21998,14 +22147,14 @@
         <v>6515</v>
       </c>
       <c r="H65" t="s">
-        <v>1818</v>
+        <v>1694</v>
       </c>
       <c r="T65" t="s">
-        <v>1819</v>
+        <v>1914</v>
       </c>
       <c r="U65" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=6515,szNote="日记2·东海客",[17]={},[18]={},aFocus={{dwMapID=-1,szDisplay="日记2·东海客",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=6515,szNote="日记2·东海客",[17]={},[18]={},aFocus={{dwMapID=-1,szDisplay="日记2·东海客",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.15">
@@ -22013,14 +22162,14 @@
         <v>6516</v>
       </c>
       <c r="H66" t="s">
-        <v>1820</v>
+        <v>1695</v>
       </c>
       <c r="T66" t="s">
-        <v>1821</v>
+        <v>1915</v>
       </c>
       <c r="U66" t="str">
         <f t="shared" ref="U66:U129" si="1">IF(ISBLANK(B66)=FALSE,IF(ISBLANK(B65),"},["&amp;B66&amp;"]={","["&amp;B66&amp;"]={"),IF(AND(ISBLANK(B66),ISBLANK(C66),OR(ISBLANK(B65)=FALSE,ISBLANK(C65)=FALSE)),"},},}",IF(ISBLANK(C66),"","{dwID="&amp;C66&amp;","&amp;IF(D66&gt;0,"nCount="&amp;D66&amp;",","")&amp;IF(E66&gt;0,"bAllLeave=true,","")&amp;IF(F66&lt;&gt;"","szName="""&amp;F66&amp;""",","")&amp;IF(G66&lt;&gt;"","tKungFu={"&amp;G66&amp;"},","")&amp;IF(H66&lt;&gt;"","szNote="""&amp;H66&amp;""",","")&amp;IF(I66&lt;&gt;"","col={"&amp;I66&amp;"},","")&amp;"[17]={"&amp;IF(J66&lt;&gt;"","szVoice="""&amp;J66&amp;""",","")&amp;IF(K66&gt;0,"bTeamChannel=true,","")&amp;IF(L66&gt;0,"bWhisperChannel=true,","")&amp;IF(M66&gt;0,"bCenterAlarm=true,","")&amp;IF(N66&gt;0,"bScreenHead=true,","")&amp;IF(O66&gt;0,"bFullScreen=true,","")&amp;"},"&amp;"[18]={"&amp;IF(P66&lt;&gt;"","szVoice="""&amp;P66&amp;""",","")&amp;IF(Q66&gt;0,"bTeamChannel=true,","")&amp;IF(R66&gt;0,"bWhisperChannel=true,","")&amp;IF(S66&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(T66&lt;&gt;"","aFocus={"&amp;T66&amp;"},","")&amp;IF(V66&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,V66:AAA66)&amp;"},","")&amp;"},")))</f>
-        <v>{dwID=6516,szNote="日记3·东海客",[17]={},[18]={},aFocus={{dwMapID=-1,szDisplay="日记3·东海客",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=6516,szNote="日记3·东海客",[17]={},[18]={},aFocus={{dwMapID=-1,szDisplay="日记3·东海客",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.15">
@@ -22028,14 +22177,14 @@
         <v>6517</v>
       </c>
       <c r="H67" t="s">
-        <v>1822</v>
+        <v>1696</v>
       </c>
       <c r="T67" t="s">
-        <v>1823</v>
+        <v>1916</v>
       </c>
       <c r="U67" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=6517,szNote="日记4·东海客",[17]={},[18]={},aFocus={{dwMapID=-1,szDisplay="日记4·东海客",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=6517,szNote="日记4·东海客",[17]={},[18]={},aFocus={{dwMapID=-1,szDisplay="日记4·东海客",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.15">
@@ -22043,14 +22192,14 @@
         <v>6518</v>
       </c>
       <c r="H68" t="s">
-        <v>1824</v>
+        <v>1697</v>
       </c>
       <c r="T68" t="s">
-        <v>1825</v>
+        <v>1917</v>
       </c>
       <c r="U68" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=6518,szNote="日记5·东海客",[17]={},[18]={},aFocus={{dwMapID=-1,szDisplay="日记5·东海客",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=6518,szNote="日记5·东海客",[17]={},[18]={},aFocus={{dwMapID=-1,szDisplay="日记5·东海客",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.15">
@@ -22070,7 +22219,7 @@
         <v>4773</v>
       </c>
       <c r="H70" t="s">
-        <v>1826</v>
+        <v>1698</v>
       </c>
       <c r="I70" t="s">
         <v>1555</v>
@@ -22082,7 +22231,7 @@
         <v>1</v>
       </c>
       <c r="T70" t="s">
-        <v>1827</v>
+        <v>1987</v>
       </c>
       <c r="U70" t="str">
         <f t="shared" si="1"/>
@@ -22094,7 +22243,7 @@
         <v>5316</v>
       </c>
       <c r="H71" t="s">
-        <v>1828</v>
+        <v>1699</v>
       </c>
       <c r="I71" t="s">
         <v>1555</v>
@@ -22106,7 +22255,7 @@
         <v>1</v>
       </c>
       <c r="T71" t="s">
-        <v>1829</v>
+        <v>1988</v>
       </c>
       <c r="U71" t="str">
         <f t="shared" si="1"/>
@@ -22130,7 +22279,7 @@
         <v>5320</v>
       </c>
       <c r="H73" t="s">
-        <v>1830</v>
+        <v>1700</v>
       </c>
       <c r="I73" t="s">
         <v>1555</v>
@@ -22142,7 +22291,7 @@
         <v>1</v>
       </c>
       <c r="T73" t="s">
-        <v>1831</v>
+        <v>1989</v>
       </c>
       <c r="U73" t="str">
         <f t="shared" si="1"/>
@@ -22166,7 +22315,7 @@
         <v>4714</v>
       </c>
       <c r="H75" t="s">
-        <v>1832</v>
+        <v>1701</v>
       </c>
       <c r="I75" t="s">
         <v>1555</v>
@@ -22178,7 +22327,7 @@
         <v>1</v>
       </c>
       <c r="T75" t="s">
-        <v>1833</v>
+        <v>1990</v>
       </c>
       <c r="U75" t="str">
         <f t="shared" si="1"/>
@@ -22190,7 +22339,7 @@
         <v>6103</v>
       </c>
       <c r="H76" t="s">
-        <v>1834</v>
+        <v>1702</v>
       </c>
       <c r="I76" t="s">
         <v>1555</v>
@@ -22199,11 +22348,11 @@
         <v>1</v>
       </c>
       <c r="T76" t="s">
-        <v>1835</v>
+        <v>1918</v>
       </c>
       <c r="U76" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=6103,szNote="神秘书籍·至尊宝",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="神秘书籍·至尊宝",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=6103,szNote="神秘书籍·至尊宝",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="神秘书籍·至尊宝",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.15">
@@ -22211,7 +22360,7 @@
         <v>6104</v>
       </c>
       <c r="H77" t="s">
-        <v>1836</v>
+        <v>1703</v>
       </c>
       <c r="I77" t="s">
         <v>1555</v>
@@ -22220,11 +22369,11 @@
         <v>1</v>
       </c>
       <c r="T77" t="s">
-        <v>1837</v>
+        <v>1919</v>
       </c>
       <c r="U77" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=6104,szNote="空酒坛子·至尊宝",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="空酒坛子·至尊宝",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=6104,szNote="空酒坛子·至尊宝",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="空酒坛子·至尊宝",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.15">
@@ -22232,7 +22381,7 @@
         <v>6105</v>
       </c>
       <c r="H78" t="s">
-        <v>1838</v>
+        <v>1704</v>
       </c>
       <c r="I78" t="s">
         <v>1555</v>
@@ -22241,11 +22390,11 @@
         <v>1</v>
       </c>
       <c r="T78" t="s">
-        <v>1839</v>
+        <v>1920</v>
       </c>
       <c r="U78" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=6105,szNote="不起眼的小土堆·至尊宝",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="不起眼的小土堆·至尊宝",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=6105,szNote="不起眼的小土堆·至尊宝",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="不起眼的小土堆·至尊宝",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.15">
@@ -22265,7 +22414,7 @@
         <v>4772</v>
       </c>
       <c r="H80" t="s">
-        <v>1840</v>
+        <v>1705</v>
       </c>
       <c r="I80" t="s">
         <v>1555</v>
@@ -22277,7 +22426,7 @@
         <v>1</v>
       </c>
       <c r="T80" t="s">
-        <v>1841</v>
+        <v>1991</v>
       </c>
       <c r="U80" t="str">
         <f t="shared" si="1"/>
@@ -22289,7 +22438,7 @@
         <v>6064</v>
       </c>
       <c r="H81" t="s">
-        <v>1842</v>
+        <v>1706</v>
       </c>
       <c r="I81" t="s">
         <v>1555</v>
@@ -22298,11 +22447,11 @@
         <v>1</v>
       </c>
       <c r="T81" t="s">
-        <v>1843</v>
+        <v>1921</v>
       </c>
       <c r="U81" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=6064,szNote="小土堆·石敢当",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="小土堆·石敢当",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=6064,szNote="小土堆·石敢当",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="小土堆·石敢当",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.15">
@@ -22322,7 +22471,7 @@
         <v>6916</v>
       </c>
       <c r="H83" t="s">
-        <v>1844</v>
+        <v>1707</v>
       </c>
       <c r="I83" t="s">
         <v>1555</v>
@@ -22331,11 +22480,11 @@
         <v>1</v>
       </c>
       <c r="T83" t="s">
-        <v>1845</v>
+        <v>1922</v>
       </c>
       <c r="U83" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=6916,szNote="竹叶青·烟花戏",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="竹叶青·烟花戏",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=6916,szNote="竹叶青·烟花戏",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="竹叶青·烟花戏",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.15">
@@ -22355,7 +22504,7 @@
         <v>5157</v>
       </c>
       <c r="H85" t="s">
-        <v>1591</v>
+        <v>1574</v>
       </c>
       <c r="I85" t="s">
         <v>1555</v>
@@ -22364,11 +22513,11 @@
         <v>1</v>
       </c>
       <c r="T85" t="s">
-        <v>1592</v>
+        <v>1815</v>
       </c>
       <c r="U85" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=5157,szNote="马四·枫林酒",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="马四·枫林酒",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=5157,szNote="马四·枫林酒",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="马四·枫林酒",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.15">
@@ -22376,7 +22525,7 @@
         <v>7777</v>
       </c>
       <c r="H86" t="s">
-        <v>1846</v>
+        <v>1708</v>
       </c>
       <c r="I86" t="s">
         <v>1555</v>
@@ -22385,11 +22534,11 @@
         <v>1</v>
       </c>
       <c r="T86" t="s">
-        <v>1847</v>
+        <v>1923</v>
       </c>
       <c r="U86" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=7777,szNote="道旁墓碑·沧海笛",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="道旁墓碑·沧海笛",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=7777,szNote="道旁墓碑·沧海笛",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="道旁墓碑·沧海笛",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.15">
@@ -22409,7 +22558,7 @@
         <v>4298</v>
       </c>
       <c r="H88" t="s">
-        <v>1848</v>
+        <v>1709</v>
       </c>
       <c r="I88" t="s">
         <v>1555</v>
@@ -22421,7 +22570,7 @@
         <v>1</v>
       </c>
       <c r="T88" t="s">
-        <v>1849</v>
+        <v>1992</v>
       </c>
       <c r="U88" t="str">
         <f t="shared" si="1"/>
@@ -22433,7 +22582,7 @@
         <v>6109</v>
       </c>
       <c r="H89" t="s">
-        <v>1850</v>
+        <v>1710</v>
       </c>
       <c r="I89" t="s">
         <v>1555</v>
@@ -22442,11 +22591,11 @@
         <v>1</v>
       </c>
       <c r="T89" t="s">
-        <v>1851</v>
+        <v>1924</v>
       </c>
       <c r="U89" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=6109,szNote="情报箱·兽王佩",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="情报箱·兽王佩",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=6109,szNote="情报箱·兽王佩",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="情报箱·兽王佩",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.15">
@@ -22466,7 +22615,7 @@
         <v>4296</v>
       </c>
       <c r="H91" t="s">
-        <v>1852</v>
+        <v>1711</v>
       </c>
       <c r="I91" t="s">
         <v>1555</v>
@@ -22478,7 +22627,7 @@
         <v>1</v>
       </c>
       <c r="T91" t="s">
-        <v>1853</v>
+        <v>1993</v>
       </c>
       <c r="U91" t="str">
         <f t="shared" si="1"/>
@@ -22502,7 +22651,7 @@
         <v>4278</v>
       </c>
       <c r="H93" t="s">
-        <v>1854</v>
+        <v>1712</v>
       </c>
       <c r="I93" t="s">
         <v>1555</v>
@@ -22514,7 +22663,7 @@
         <v>1</v>
       </c>
       <c r="T93" t="s">
-        <v>1855</v>
+        <v>1994</v>
       </c>
       <c r="U93" t="str">
         <f t="shared" si="1"/>
@@ -22538,7 +22687,7 @@
         <v>6341</v>
       </c>
       <c r="H95" t="s">
-        <v>1856</v>
+        <v>1713</v>
       </c>
       <c r="I95" t="s">
         <v>1555</v>
@@ -22547,11 +22696,11 @@
         <v>1</v>
       </c>
       <c r="T95" t="s">
-        <v>1857</v>
+        <v>1925</v>
       </c>
       <c r="U95" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=6341,szNote="桃花枝·稚子心",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="桃花枝·稚子心",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=6341,szNote="桃花枝·稚子心",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="桃花枝·稚子心",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.15">
@@ -22559,7 +22708,7 @@
         <v>6342</v>
       </c>
       <c r="H96" t="s">
-        <v>1858</v>
+        <v>1714</v>
       </c>
       <c r="I96" t="s">
         <v>1555</v>
@@ -22568,11 +22717,11 @@
         <v>1</v>
       </c>
       <c r="T96" t="s">
-        <v>1859</v>
+        <v>1926</v>
       </c>
       <c r="U96" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=6342,szNote="银鱼·稚子心",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="银鱼·稚子心",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=6342,szNote="银鱼·稚子心",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="银鱼·稚子心",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.15">
@@ -22580,7 +22729,7 @@
         <v>6343</v>
       </c>
       <c r="H97" t="s">
-        <v>1860</v>
+        <v>1715</v>
       </c>
       <c r="I97" t="s">
         <v>1555</v>
@@ -22589,11 +22738,11 @@
         <v>1</v>
       </c>
       <c r="T97" t="s">
-        <v>1861</v>
+        <v>1927</v>
       </c>
       <c r="U97" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=6343,szNote="猴儿酒·稚子心",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="猴儿酒·稚子心",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=6343,szNote="猴儿酒·稚子心",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="猴儿酒·稚子心",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.15">
@@ -22601,7 +22750,7 @@
         <v>6912</v>
       </c>
       <c r="H98" t="s">
-        <v>1862</v>
+        <v>1716</v>
       </c>
       <c r="I98" t="s">
         <v>1555</v>
@@ -22610,11 +22759,11 @@
         <v>1</v>
       </c>
       <c r="T98" t="s">
-        <v>1863</v>
+        <v>1928</v>
       </c>
       <c r="U98" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=6912,szNote="春风酿·烟花戏",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="春风酿·烟花戏",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=6912,szNote="春风酿·烟花戏",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="春风酿·烟花戏",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.15">
@@ -22622,7 +22771,7 @@
         <v>10161</v>
       </c>
       <c r="H99" t="s">
-        <v>1864</v>
+        <v>1717</v>
       </c>
       <c r="I99" t="s">
         <v>1555</v>
@@ -22631,11 +22780,11 @@
         <v>1</v>
       </c>
       <c r="T99" t="s">
-        <v>1865</v>
+        <v>1929</v>
       </c>
       <c r="U99" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=10161,szNote="鱼篓·醉烟波",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="鱼篓·醉烟波",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=10161,szNote="鱼篓·醉烟波",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="鱼篓·醉烟波",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.15">
@@ -22643,7 +22792,7 @@
         <v>10172</v>
       </c>
       <c r="H100" t="s">
-        <v>1866</v>
+        <v>1718</v>
       </c>
       <c r="I100" t="s">
         <v>1555</v>
@@ -22652,11 +22801,11 @@
         <v>1</v>
       </c>
       <c r="T100" t="s">
-        <v>1867</v>
+        <v>1930</v>
       </c>
       <c r="U100" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=10172,szNote="酒·醉烟波",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="酒·醉烟波",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=10172,szNote="酒·醉烟波",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="酒·醉烟波",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.15">
@@ -22676,14 +22825,14 @@
         <v>6115</v>
       </c>
       <c r="H102" t="s">
-        <v>1868</v>
+        <v>1719</v>
       </c>
       <c r="T102" t="s">
-        <v>1869</v>
+        <v>1931</v>
       </c>
       <c r="U102" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=6115,szNote="元和的弩弓·乱世舞姬",[17]={},[18]={},aFocus={{dwMapID=-1,szDisplay="元和的弩弓·乱世",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=6115,szNote="元和的弩弓·乱世舞姬",[17]={},[18]={},aFocus={{dwMapID=-1,szDisplay="元和的弩弓·乱世",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.15">
@@ -22691,10 +22840,10 @@
         <v>6116</v>
       </c>
       <c r="H103" t="s">
-        <v>1870</v>
+        <v>1720</v>
       </c>
       <c r="T103" t="s">
-        <v>1871</v>
+        <v>1721</v>
       </c>
       <c r="U103" t="str">
         <f t="shared" si="1"/>
@@ -22718,7 +22867,7 @@
         <v>5055</v>
       </c>
       <c r="H105" t="s">
-        <v>1872</v>
+        <v>1722</v>
       </c>
       <c r="I105" t="s">
         <v>1555</v>
@@ -22730,7 +22879,7 @@
         <v>1</v>
       </c>
       <c r="T105" t="s">
-        <v>1873</v>
+        <v>1995</v>
       </c>
       <c r="U105" t="str">
         <f t="shared" si="1"/>
@@ -22742,7 +22891,7 @@
         <v>7415</v>
       </c>
       <c r="H106" t="s">
-        <v>1874</v>
+        <v>1723</v>
       </c>
       <c r="I106" t="s">
         <v>1555</v>
@@ -22751,11 +22900,11 @@
         <v>1</v>
       </c>
       <c r="T106" t="s">
-        <v>1875</v>
+        <v>1932</v>
       </c>
       <c r="U106" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=7415,szNote="被抢夺的矿石箱·太行道",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="被抢夺的矿石箱·太行道",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=7415,szNote="被抢夺的矿石箱·太行道",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="被抢夺的矿石箱·太行道",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.15">
@@ -22763,7 +22912,7 @@
         <v>7423</v>
       </c>
       <c r="H107" t="s">
-        <v>1876</v>
+        <v>1724</v>
       </c>
       <c r="I107" t="s">
         <v>1555</v>
@@ -22772,11 +22921,11 @@
         <v>1</v>
       </c>
       <c r="T107" t="s">
-        <v>1877</v>
+        <v>1933</v>
       </c>
       <c r="U107" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=7423,szNote="边澈的辎重箱·太行道",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="边澈的辎重箱·太行道",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=7423,szNote="边澈的辎重箱·太行道",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="边澈的辎重箱·太行道",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.15">
@@ -22796,7 +22945,7 @@
         <v>5749</v>
       </c>
       <c r="H109" t="s">
-        <v>1878</v>
+        <v>1725</v>
       </c>
       <c r="I109" t="s">
         <v>1555</v>
@@ -22805,11 +22954,11 @@
         <v>1</v>
       </c>
       <c r="T109" t="s">
-        <v>1879</v>
+        <v>1934</v>
       </c>
       <c r="U109" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=5749,szNote="奇怪的土堆·碎片一·清茗经",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="土堆·碎片一·清茗经",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=5749,szNote="奇怪的土堆·碎片一·清茗经",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="土堆·碎片一·清茗经",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.15">
@@ -22817,7 +22966,7 @@
         <v>5748</v>
       </c>
       <c r="H110" t="s">
-        <v>1880</v>
+        <v>1726</v>
       </c>
       <c r="I110" t="s">
         <v>1555</v>
@@ -22829,7 +22978,7 @@
         <v>1</v>
       </c>
       <c r="T110" t="s">
-        <v>1881</v>
+        <v>1996</v>
       </c>
       <c r="U110" t="str">
         <f t="shared" si="1"/>
@@ -22853,7 +23002,7 @@
         <v>6368</v>
       </c>
       <c r="H112" t="s">
-        <v>1882</v>
+        <v>1727</v>
       </c>
       <c r="I112" t="s">
         <v>1555</v>
@@ -22862,11 +23011,11 @@
         <v>1</v>
       </c>
       <c r="T112" t="s">
-        <v>1883</v>
+        <v>1935</v>
       </c>
       <c r="U112" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=6368,szNote="拜火教箱子·青草歌",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="拜火教箱子·青草歌",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=6368,szNote="拜火教箱子·青草歌",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="拜火教箱子·青草歌",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.15">
@@ -22886,7 +23035,7 @@
         <v>7274</v>
       </c>
       <c r="H114" t="s">
-        <v>1884</v>
+        <v>1728</v>
       </c>
       <c r="I114" t="s">
         <v>1555</v>
@@ -22895,11 +23044,11 @@
         <v>1</v>
       </c>
       <c r="T114" t="s">
-        <v>1885</v>
+        <v>1936</v>
       </c>
       <c r="U114" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=7274,szNote="寒泉岩·太行道",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="寒泉岩·太行道",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=7274,szNote="寒泉岩·太行道",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="寒泉岩·太行道",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.15">
@@ -22919,7 +23068,7 @@
         <v>8255</v>
       </c>
       <c r="H116" t="s">
-        <v>1886</v>
+        <v>1729</v>
       </c>
       <c r="I116" t="s">
         <v>1555</v>
@@ -22928,11 +23077,11 @@
         <v>1</v>
       </c>
       <c r="T116" t="s">
-        <v>1887</v>
+        <v>1937</v>
       </c>
       <c r="U116" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=8255,szNote="武器箱·露园事",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="武器箱·露园事",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=8255,szNote="武器箱·露园事",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="武器箱·露园事",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.15">
@@ -22940,7 +23089,7 @@
         <v>8258</v>
       </c>
       <c r="H117" t="s">
-        <v>1888</v>
+        <v>1730</v>
       </c>
       <c r="I117" t="s">
         <v>1555</v>
@@ -22949,11 +23098,11 @@
         <v>1</v>
       </c>
       <c r="T117" t="s">
-        <v>1889</v>
+        <v>1938</v>
       </c>
       <c r="U117" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=8258,szNote="陷阱·露园事",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="陷阱·露园事",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=8258,szNote="陷阱·露园事",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="陷阱·露园事",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.15">
@@ -22961,7 +23110,7 @@
         <v>8265</v>
       </c>
       <c r="H118" t="s">
-        <v>1890</v>
+        <v>1731</v>
       </c>
       <c r="I118" t="s">
         <v>1555</v>
@@ -22970,11 +23119,11 @@
         <v>1</v>
       </c>
       <c r="T118" t="s">
-        <v>1891</v>
+        <v>1939</v>
       </c>
       <c r="U118" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=8265,szNote="坑洞·露园事",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="坑洞·露园事",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=8265,szNote="坑洞·露园事",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="坑洞·露园事",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.15">
@@ -22994,7 +23143,7 @@
         <v>7459</v>
       </c>
       <c r="H120" t="s">
-        <v>1892</v>
+        <v>1732</v>
       </c>
       <c r="I120" t="s">
         <v>1555</v>
@@ -23003,11 +23152,11 @@
         <v>1</v>
       </c>
       <c r="T120" t="s">
-        <v>1893</v>
+        <v>1940</v>
       </c>
       <c r="U120" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=7459,szNote="野菜·客江干",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="野菜·客江干",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=7459,szNote="野菜·客江干",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="野菜·客江干",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.15">
@@ -23015,7 +23164,7 @@
         <v>7457</v>
       </c>
       <c r="H121" t="s">
-        <v>1894</v>
+        <v>1733</v>
       </c>
       <c r="I121" t="s">
         <v>1555</v>
@@ -23024,11 +23173,11 @@
         <v>1</v>
       </c>
       <c r="T121" t="s">
-        <v>1895</v>
+        <v>1941</v>
       </c>
       <c r="U121" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=7457,szNote="无名侠士之墓·客江干",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="无名侠士之墓·客江干",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=7457,szNote="无名侠士之墓·客江干",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="无名侠士之墓·客江干",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.15">
@@ -23036,7 +23185,7 @@
         <v>7458</v>
       </c>
       <c r="H122" t="s">
-        <v>1896</v>
+        <v>1734</v>
       </c>
       <c r="I122" t="s">
         <v>1555</v>
@@ -23045,11 +23194,11 @@
         <v>1</v>
       </c>
       <c r="T122" t="s">
-        <v>1897</v>
+        <v>1942</v>
       </c>
       <c r="U122" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=7458,szNote="奇怪的雪堆·客江干",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="奇怪的雪堆·客江干",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=7458,szNote="奇怪的雪堆·客江干",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="奇怪的雪堆·客江干",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.15">
@@ -23057,7 +23206,7 @@
         <v>9309</v>
       </c>
       <c r="H123" t="s">
-        <v>1898</v>
+        <v>1735</v>
       </c>
       <c r="I123" t="s">
         <v>1555</v>
@@ -23066,11 +23215,11 @@
         <v>1</v>
       </c>
       <c r="T123" t="s">
-        <v>1899</v>
+        <v>1943</v>
       </c>
       <c r="U123" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=9309,szNote="一桌酒席·风雨意",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="一桌酒席·风雨意",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=9309,szNote="一桌酒席·风雨意",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="一桌酒席·风雨意",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.15">
@@ -23078,7 +23227,7 @@
         <v>9311</v>
       </c>
       <c r="H124" t="s">
-        <v>1900</v>
+        <v>1736</v>
       </c>
       <c r="I124" t="s">
         <v>1555</v>
@@ -23087,11 +23236,11 @@
         <v>1</v>
       </c>
       <c r="T124" t="s">
-        <v>1901</v>
+        <v>1944</v>
       </c>
       <c r="U124" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=9311,szNote="特地留的书信·风雨意",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="特地留的书信·风雨意",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=9311,szNote="特地留的书信·风雨意",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="特地留的书信·风雨意",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.15">
@@ -23111,7 +23260,7 @@
         <v>7455</v>
       </c>
       <c r="H126" t="s">
-        <v>1902</v>
+        <v>1737</v>
       </c>
       <c r="I126" t="s">
         <v>1555</v>
@@ -23120,11 +23269,11 @@
         <v>1</v>
       </c>
       <c r="T126" t="s">
-        <v>1903</v>
+        <v>1945</v>
       </c>
       <c r="U126" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=7455,szNote="沉甸甸的木桶·秘宝图",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="沉甸甸的木桶·秘宝图",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=7455,szNote="沉甸甸的木桶·秘宝图",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="沉甸甸的木桶·秘宝图",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.15">
@@ -23144,7 +23293,7 @@
         <v>9202</v>
       </c>
       <c r="H128" t="s">
-        <v>1904</v>
+        <v>1738</v>
       </c>
       <c r="I128" t="s">
         <v>1555</v>
@@ -23153,7 +23302,7 @@
         <v>1</v>
       </c>
       <c r="T128" t="s">
-        <v>1905</v>
+        <v>1739</v>
       </c>
       <c r="U128" t="str">
         <f t="shared" si="1"/>
@@ -23177,7 +23326,7 @@
         <v>7707</v>
       </c>
       <c r="H130" t="s">
-        <v>1906</v>
+        <v>1740</v>
       </c>
       <c r="I130" t="s">
         <v>1555</v>
@@ -23186,11 +23335,11 @@
         <v>1</v>
       </c>
       <c r="T130" t="s">
-        <v>1907</v>
+        <v>1946</v>
       </c>
       <c r="U130" t="str">
         <f t="shared" ref="U130:U185" si="2">IF(ISBLANK(B130)=FALSE,IF(ISBLANK(B129),"},["&amp;B130&amp;"]={","["&amp;B130&amp;"]={"),IF(AND(ISBLANK(B130),ISBLANK(C130),OR(ISBLANK(B129)=FALSE,ISBLANK(C129)=FALSE)),"},},}",IF(ISBLANK(C130),"","{dwID="&amp;C130&amp;","&amp;IF(D130&gt;0,"nCount="&amp;D130&amp;",","")&amp;IF(E130&gt;0,"bAllLeave=true,","")&amp;IF(F130&lt;&gt;"","szName="""&amp;F130&amp;""",","")&amp;IF(G130&lt;&gt;"","tKungFu={"&amp;G130&amp;"},","")&amp;IF(H130&lt;&gt;"","szNote="""&amp;H130&amp;""",","")&amp;IF(I130&lt;&gt;"","col={"&amp;I130&amp;"},","")&amp;"[17]={"&amp;IF(J130&lt;&gt;"","szVoice="""&amp;J130&amp;""",","")&amp;IF(K130&gt;0,"bTeamChannel=true,","")&amp;IF(L130&gt;0,"bWhisperChannel=true,","")&amp;IF(M130&gt;0,"bCenterAlarm=true,","")&amp;IF(N130&gt;0,"bScreenHead=true,","")&amp;IF(O130&gt;0,"bFullScreen=true,","")&amp;"},"&amp;"[18]={"&amp;IF(P130&lt;&gt;"","szVoice="""&amp;P130&amp;""",","")&amp;IF(Q130&gt;0,"bTeamChannel=true,","")&amp;IF(R130&gt;0,"bWhisperChannel=true,","")&amp;IF(S130&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(T130&lt;&gt;"","aFocus={"&amp;T130&amp;"},","")&amp;IF(V130&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,V130:AAA130)&amp;"},","")&amp;"},")))</f>
-        <v>{dwID=7707,szNote="水缸·滴水恩",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="水缸·滴水恩",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=7707,szNote="水缸·滴水恩",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="水缸·滴水恩",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.15">
@@ -23198,7 +23347,7 @@
         <v>7833</v>
       </c>
       <c r="H131" t="s">
-        <v>1908</v>
+        <v>1741</v>
       </c>
       <c r="I131" t="s">
         <v>1555</v>
@@ -23207,11 +23356,11 @@
         <v>1</v>
       </c>
       <c r="T131" t="s">
-        <v>1909</v>
+        <v>1947</v>
       </c>
       <c r="U131" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=7833,szNote="死去的鱼虾·滴水恩",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="死去的鱼虾·滴水恩",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=7833,szNote="死去的鱼虾·滴水恩",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="死去的鱼虾·滴水恩",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.15">
@@ -23219,7 +23368,7 @@
         <v>8614</v>
       </c>
       <c r="H132" t="s">
-        <v>1910</v>
+        <v>1742</v>
       </c>
       <c r="I132" t="s">
         <v>1555</v>
@@ -23228,11 +23377,11 @@
         <v>1</v>
       </c>
       <c r="T132" t="s">
-        <v>1911</v>
+        <v>1948</v>
       </c>
       <c r="U132" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=8614,szNote="小土堆·话玄虚",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="小土堆·话玄虚",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=8614,szNote="小土堆·话玄虚",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="小土堆·话玄虚",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.15">
@@ -23240,7 +23389,7 @@
         <v>10696</v>
       </c>
       <c r="H133" t="s">
-        <v>1912</v>
+        <v>1743</v>
       </c>
       <c r="I133" t="s">
         <v>1555</v>
@@ -23249,11 +23398,11 @@
         <v>1</v>
       </c>
       <c r="T133" t="s">
-        <v>1913</v>
+        <v>1949</v>
       </c>
       <c r="U133" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=10696,szNote="功夫·路投石",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="功夫·路投石",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=10696,szNote="功夫·路投石",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="功夫·路投石",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.15">
@@ -23273,7 +23422,7 @@
         <v>8961</v>
       </c>
       <c r="H135" t="s">
-        <v>1914</v>
+        <v>1744</v>
       </c>
       <c r="I135" t="s">
         <v>1555</v>
@@ -23282,11 +23431,11 @@
         <v>1</v>
       </c>
       <c r="T135" t="s">
-        <v>1915</v>
+        <v>1950</v>
       </c>
       <c r="U135" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=8961,szNote="白六娘的樱桃树·丹青记",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="白六娘的樱桃树·丹青记",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=8961,szNote="白六娘的樱桃树·丹青记",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="白六娘的樱桃树·丹青记",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.15">
@@ -23306,7 +23455,7 @@
         <v>8865</v>
       </c>
       <c r="H137" t="s">
-        <v>1916</v>
+        <v>1745</v>
       </c>
       <c r="I137" t="s">
         <v>1555</v>
@@ -23315,11 +23464,11 @@
         <v>1</v>
       </c>
       <c r="T137" t="s">
-        <v>1917</v>
+        <v>1951</v>
       </c>
       <c r="U137" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=8865,szNote="妙妙椅·侠行",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="妙妙椅·侠行",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=8865,szNote="妙妙椅·侠行",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="妙妙椅·侠行",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.15">
@@ -23327,7 +23476,7 @@
         <v>8866</v>
       </c>
       <c r="H138" t="s">
-        <v>1918</v>
+        <v>1746</v>
       </c>
       <c r="I138" t="s">
         <v>1555</v>
@@ -23336,11 +23485,11 @@
         <v>1</v>
       </c>
       <c r="T138" t="s">
-        <v>1919</v>
+        <v>1952</v>
       </c>
       <c r="U138" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=8866,szNote="千丝绸·侠行",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="千丝绸·侠行",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=8866,szNote="千丝绸·侠行",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="千丝绸·侠行",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.15">
@@ -23348,7 +23497,7 @@
         <v>8867</v>
       </c>
       <c r="H139" t="s">
-        <v>1920</v>
+        <v>1747</v>
       </c>
       <c r="I139" t="s">
         <v>1555</v>
@@ -23357,11 +23506,11 @@
         <v>1</v>
       </c>
       <c r="T139" t="s">
-        <v>1921</v>
+        <v>1953</v>
       </c>
       <c r="U139" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=8867,szNote="神机轮·侠行",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="神机轮·侠行",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=8867,szNote="神机轮·侠行",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="神机轮·侠行",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.15">
@@ -23369,7 +23518,7 @@
         <v>10678</v>
       </c>
       <c r="H140" t="s">
-        <v>1922</v>
+        <v>1748</v>
       </c>
       <c r="I140" t="s">
         <v>1555</v>
@@ -23378,11 +23527,11 @@
         <v>1</v>
       </c>
       <c r="T140" t="s">
-        <v>1923</v>
+        <v>1954</v>
       </c>
       <c r="U140" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=10678,szNote="货物堆·觅知音",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="货物堆·觅知音",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=10678,szNote="货物堆·觅知音",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="货物堆·觅知音",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.15">
@@ -23402,7 +23551,7 @@
         <v>8600</v>
       </c>
       <c r="H142" t="s">
-        <v>1924</v>
+        <v>1749</v>
       </c>
       <c r="I142" t="s">
         <v>1555</v>
@@ -23411,11 +23560,11 @@
         <v>1</v>
       </c>
       <c r="T142" t="s">
-        <v>1925</v>
+        <v>1955</v>
       </c>
       <c r="U142" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=8600,szNote="兔子窝1·白月皎",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="兔子窝1·白月皎",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=8600,szNote="兔子窝1·白月皎",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="兔子窝1·白月皎",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.15">
@@ -23423,7 +23572,7 @@
         <v>8604</v>
       </c>
       <c r="H143" t="s">
-        <v>1926</v>
+        <v>1750</v>
       </c>
       <c r="I143" t="s">
         <v>1555</v>
@@ -23432,11 +23581,11 @@
         <v>1</v>
       </c>
       <c r="T143" t="s">
-        <v>1927</v>
+        <v>1956</v>
       </c>
       <c r="U143" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=8604,szNote="兔子窝2·白月皎",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="兔子窝2·白月皎",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=8604,szNote="兔子窝2·白月皎",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="兔子窝2·白月皎",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.15">
@@ -23444,7 +23593,7 @@
         <v>8605</v>
       </c>
       <c r="H144" t="s">
-        <v>1928</v>
+        <v>1751</v>
       </c>
       <c r="I144" t="s">
         <v>1555</v>
@@ -23453,11 +23602,11 @@
         <v>1</v>
       </c>
       <c r="T144" t="s">
-        <v>1929</v>
+        <v>1957</v>
       </c>
       <c r="U144" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=8605,szNote="兔子窝3·白月皎",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="兔子窝3·白月皎",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=8605,szNote="兔子窝3·白月皎",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="兔子窝3·白月皎",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.15">
@@ -23465,14 +23614,14 @@
         <v>8603</v>
       </c>
       <c r="H145" t="s">
-        <v>1930</v>
+        <v>1752</v>
       </c>
       <c r="T145" t="s">
-        <v>1931</v>
+        <v>1958</v>
       </c>
       <c r="U145" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=8603,szNote="散落的画作·白月皎",[17]={},[18]={},aFocus={{dwMapID=-1,szDisplay="散落的画作·白月皎",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=8603,szNote="散落的画作·白月皎",[17]={},[18]={},aFocus={{dwMapID=-1,szDisplay="散落的画作·白月皎",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.15">
@@ -23480,14 +23629,14 @@
         <v>8602</v>
       </c>
       <c r="H146" t="s">
-        <v>1932</v>
+        <v>1753</v>
       </c>
       <c r="T146" t="s">
-        <v>1933</v>
+        <v>1959</v>
       </c>
       <c r="U146" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=8602,szNote="散落的日记·白月皎",[17]={},[18]={},aFocus={{dwMapID=-1,szDisplay="散落的日记·白月皎",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=8602,szNote="散落的日记·白月皎",[17]={},[18]={},aFocus={{dwMapID=-1,szDisplay="散落的日记·白月皎",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.15">
@@ -23495,14 +23644,14 @@
         <v>8606</v>
       </c>
       <c r="H147" t="s">
-        <v>1932</v>
+        <v>1753</v>
       </c>
       <c r="T147" t="s">
-        <v>1933</v>
+        <v>1959</v>
       </c>
       <c r="U147" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=8606,szNote="散落的日记·白月皎",[17]={},[18]={},aFocus={{dwMapID=-1,szDisplay="散落的日记·白月皎",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=8606,szNote="散落的日记·白月皎",[17]={},[18]={},aFocus={{dwMapID=-1,szDisplay="散落的日记·白月皎",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.15">
@@ -23522,7 +23671,7 @@
         <v>9178</v>
       </c>
       <c r="H149" t="s">
-        <v>1934</v>
+        <v>1754</v>
       </c>
       <c r="I149" t="s">
         <v>1555</v>
@@ -23531,7 +23680,7 @@
         <v>1</v>
       </c>
       <c r="T149" t="s">
-        <v>1935</v>
+        <v>1755</v>
       </c>
       <c r="U149" t="str">
         <f t="shared" si="2"/>
@@ -23555,7 +23704,7 @@
         <v>10007</v>
       </c>
       <c r="H151" t="s">
-        <v>1936</v>
+        <v>1756</v>
       </c>
       <c r="I151" t="s">
         <v>1555</v>
@@ -23564,11 +23713,11 @@
         <v>1</v>
       </c>
       <c r="T151" t="s">
-        <v>1937</v>
+        <v>1960</v>
       </c>
       <c r="U151" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=10007,szNote="渔具·重洋客",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="渔具·重洋客",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=10007,szNote="渔具·重洋客",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="渔具·重洋客",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.15">
@@ -23588,14 +23737,14 @@
         <v>10176</v>
       </c>
       <c r="H153" t="s">
-        <v>1938</v>
+        <v>1757</v>
       </c>
       <c r="T153" t="s">
-        <v>1939</v>
+        <v>1961</v>
       </c>
       <c r="U153" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=10176,szNote="光圈·乱红鸾",[17]={},[18]={},aFocus={{dwMapID=-1,szDisplay="光圈·乱红鸾",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=10176,szNote="光圈·乱红鸾",[17]={},[18]={},aFocus={{dwMapID=-1,szDisplay="光圈·乱红鸾",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.15">
@@ -23603,14 +23752,14 @@
         <v>10173</v>
       </c>
       <c r="H154" t="s">
-        <v>1938</v>
+        <v>1757</v>
       </c>
       <c r="T154" t="s">
-        <v>1939</v>
+        <v>1961</v>
       </c>
       <c r="U154" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=10173,szNote="光圈·乱红鸾",[17]={},[18]={},aFocus={{dwMapID=-1,szDisplay="光圈·乱红鸾",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=10173,szNote="光圈·乱红鸾",[17]={},[18]={},aFocus={{dwMapID=-1,szDisplay="光圈·乱红鸾",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.15">
@@ -23618,14 +23767,14 @@
         <v>10174</v>
       </c>
       <c r="H155" t="s">
-        <v>1938</v>
+        <v>1757</v>
       </c>
       <c r="T155" t="s">
-        <v>1939</v>
+        <v>1961</v>
       </c>
       <c r="U155" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=10174,szNote="光圈·乱红鸾",[17]={},[18]={},aFocus={{dwMapID=-1,szDisplay="光圈·乱红鸾",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=10174,szNote="光圈·乱红鸾",[17]={},[18]={},aFocus={{dwMapID=-1,szDisplay="光圈·乱红鸾",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.15">
@@ -23633,14 +23782,14 @@
         <v>10175</v>
       </c>
       <c r="H156" t="s">
-        <v>1938</v>
+        <v>1757</v>
       </c>
       <c r="T156" t="s">
-        <v>1939</v>
+        <v>1961</v>
       </c>
       <c r="U156" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=10175,szNote="光圈·乱红鸾",[17]={},[18]={},aFocus={{dwMapID=-1,szDisplay="光圈·乱红鸾",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=10175,szNote="光圈·乱红鸾",[17]={},[18]={},aFocus={{dwMapID=-1,szDisplay="光圈·乱红鸾",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.15">
@@ -23648,7 +23797,7 @@
         <v>10419</v>
       </c>
       <c r="H157" t="s">
-        <v>1940</v>
+        <v>1758</v>
       </c>
       <c r="I157" t="s">
         <v>1555</v>
@@ -23657,11 +23806,11 @@
         <v>1</v>
       </c>
       <c r="T157" t="s">
-        <v>1941</v>
+        <v>1962</v>
       </c>
       <c r="U157" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=10419,szNote="海螺壳·寓天涯",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="海螺壳·寓天涯",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=10419,szNote="海螺壳·寓天涯",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="海螺壳·寓天涯",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.15">
@@ -23669,7 +23818,7 @@
         <v>10421</v>
       </c>
       <c r="H158" t="s">
-        <v>1942</v>
+        <v>1759</v>
       </c>
       <c r="I158" t="s">
         <v>1555</v>
@@ -23678,11 +23827,11 @@
         <v>1</v>
       </c>
       <c r="T158" t="s">
-        <v>1943</v>
+        <v>1963</v>
       </c>
       <c r="U158" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=10421,szNote="莓莓·寓天涯",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="莓莓·寓天涯",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=10421,szNote="莓莓·寓天涯",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="莓莓·寓天涯",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.15">
@@ -23702,7 +23851,7 @@
         <v>10044</v>
       </c>
       <c r="H160" t="s">
-        <v>1944</v>
+        <v>1760</v>
       </c>
       <c r="I160" t="s">
         <v>1555</v>
@@ -23711,11 +23860,11 @@
         <v>1</v>
       </c>
       <c r="T160" t="s">
-        <v>1945</v>
+        <v>1964</v>
       </c>
       <c r="U160" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=10044,szNote="虹下之泉·子夜歌",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="虹下之泉·子夜歌",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=10044,szNote="虹下之泉·子夜歌",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="虹下之泉·子夜歌",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.15">
@@ -23735,14 +23884,14 @@
         <v>10156</v>
       </c>
       <c r="H162" t="s">
-        <v>1946</v>
+        <v>1761</v>
       </c>
       <c r="T162" t="s">
-        <v>1947</v>
+        <v>1965</v>
       </c>
       <c r="U162" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=10156,szNote="光圈·夜哀鸣",[17]={},[18]={},aFocus={{dwMapID=-1,szDisplay="光圈·夜哀鸣",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=10156,szNote="光圈·夜哀鸣",[17]={},[18]={},aFocus={{dwMapID=-1,szDisplay="光圈·夜哀鸣",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.15">
@@ -23750,14 +23899,14 @@
         <v>10164</v>
       </c>
       <c r="H163" t="s">
-        <v>1948</v>
+        <v>1762</v>
       </c>
       <c r="T163" t="s">
-        <v>1949</v>
+        <v>1966</v>
       </c>
       <c r="U163" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=10164,szNote="止血草·夜哀鸣",[17]={},[18]={},aFocus={{dwMapID=-1,szDisplay="止血草·夜哀鸣",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=10164,szNote="止血草·夜哀鸣",[17]={},[18]={},aFocus={{dwMapID=-1,szDisplay="止血草·夜哀鸣",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.15">
@@ -23765,14 +23914,14 @@
         <v>10167</v>
       </c>
       <c r="H164" t="s">
-        <v>1946</v>
+        <v>1761</v>
       </c>
       <c r="T164" t="s">
-        <v>1947</v>
+        <v>1965</v>
       </c>
       <c r="U164" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=10167,szNote="光圈·夜哀鸣",[17]={},[18]={},aFocus={{dwMapID=-1,szDisplay="光圈·夜哀鸣",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=10167,szNote="光圈·夜哀鸣",[17]={},[18]={},aFocus={{dwMapID=-1,szDisplay="光圈·夜哀鸣",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.15">
@@ -23780,7 +23929,7 @@
         <v>10169</v>
       </c>
       <c r="H165" t="s">
-        <v>1950</v>
+        <v>1763</v>
       </c>
       <c r="I165" t="s">
         <v>1555</v>
@@ -23789,11 +23938,11 @@
         <v>1</v>
       </c>
       <c r="T165" t="s">
-        <v>1951</v>
+        <v>1967</v>
       </c>
       <c r="U165" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=10169,szNote="甜果·夜哀鸣",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="甜果·夜哀鸣",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=10169,szNote="甜果·夜哀鸣",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="甜果·夜哀鸣",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.15">
@@ -23813,7 +23962,7 @@
         <v>10060</v>
       </c>
       <c r="H167" t="s">
-        <v>1952</v>
+        <v>1764</v>
       </c>
       <c r="I167" t="s">
         <v>1555</v>
@@ -23822,7 +23971,7 @@
         <v>1</v>
       </c>
       <c r="T167" t="s">
-        <v>1953</v>
+        <v>1765</v>
       </c>
       <c r="U167" t="str">
         <f t="shared" si="2"/>
@@ -23834,7 +23983,7 @@
         <v>10054</v>
       </c>
       <c r="H168" t="s">
-        <v>1954</v>
+        <v>1766</v>
       </c>
       <c r="I168" t="s">
         <v>1555</v>
@@ -23843,11 +23992,11 @@
         <v>1</v>
       </c>
       <c r="T168" t="s">
-        <v>1955</v>
+        <v>1968</v>
       </c>
       <c r="U168" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=10054,szNote="散落的羽毛·故岁辞",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="散落的羽毛·故岁辞",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=10054,szNote="散落的羽毛·故岁辞",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="散落的羽毛·故岁辞",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.15">
@@ -23855,14 +24004,14 @@
         <v>10057</v>
       </c>
       <c r="H169" t="s">
-        <v>1956</v>
+        <v>1767</v>
       </c>
       <c r="T169" t="s">
-        <v>1957</v>
+        <v>1969</v>
       </c>
       <c r="U169" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=10057,szNote="光圈·故岁辞",[17]={},[18]={},aFocus={{dwMapID=-1,szDisplay="光圈·故岁辞",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=10057,szNote="光圈·故岁辞",[17]={},[18]={},aFocus={{dwMapID=-1,szDisplay="光圈·故岁辞",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.15">
@@ -23870,14 +24019,14 @@
         <v>10058</v>
       </c>
       <c r="H170" t="s">
-        <v>1956</v>
+        <v>1767</v>
       </c>
       <c r="T170" t="s">
-        <v>1957</v>
+        <v>1969</v>
       </c>
       <c r="U170" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=10058,szNote="光圈·故岁辞",[17]={},[18]={},aFocus={{dwMapID=-1,szDisplay="光圈·故岁辞",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=10058,szNote="光圈·故岁辞",[17]={},[18]={},aFocus={{dwMapID=-1,szDisplay="光圈·故岁辞",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.15">
@@ -23885,14 +24034,14 @@
         <v>10059</v>
       </c>
       <c r="H171" t="s">
-        <v>1958</v>
+        <v>1768</v>
       </c>
       <c r="T171" t="s">
-        <v>1959</v>
+        <v>1970</v>
       </c>
       <c r="U171" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=10059,szNote="鸟笼·故岁辞",[17]={},[18]={},aFocus={{dwMapID=-1,szDisplay="鸟笼·故岁辞",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=10059,szNote="鸟笼·故岁辞",[17]={},[18]={},aFocus={{dwMapID=-1,szDisplay="鸟笼·故岁辞",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.15">
@@ -23912,7 +24061,7 @@
         <v>10356</v>
       </c>
       <c r="H173" t="s">
-        <v>1960</v>
+        <v>1769</v>
       </c>
       <c r="I173" t="s">
         <v>1555</v>
@@ -23921,11 +24070,11 @@
         <v>1</v>
       </c>
       <c r="T173" t="s">
-        <v>1961</v>
+        <v>1971</v>
       </c>
       <c r="U173" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=10356,szNote="树叶堆·解心语",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="树叶堆·解心语",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=10356,szNote="树叶堆·解心语",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="树叶堆·解心语",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="174" spans="1:21" x14ac:dyDescent="0.15">
@@ -23933,14 +24082,14 @@
         <v>10381</v>
       </c>
       <c r="H174" t="s">
-        <v>1962</v>
+        <v>1770</v>
       </c>
       <c r="T174" t="s">
-        <v>1963</v>
+        <v>1972</v>
       </c>
       <c r="U174" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=10381,szNote="光圈·解心语",[17]={},[18]={},aFocus={{dwMapID=-1,szDisplay="光圈·解心语",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=10381,szNote="光圈·解心语",[17]={},[18]={},aFocus={{dwMapID=-1,szDisplay="光圈·解心语",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.15">
@@ -23948,14 +24097,14 @@
         <v>10399</v>
       </c>
       <c r="H175" t="s">
-        <v>1962</v>
+        <v>1770</v>
       </c>
       <c r="T175" t="s">
-        <v>1963</v>
+        <v>1972</v>
       </c>
       <c r="U175" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=10399,szNote="光圈·解心语",[17]={},[18]={},aFocus={{dwMapID=-1,szDisplay="光圈·解心语",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=10399,szNote="光圈·解心语",[17]={},[18]={},aFocus={{dwMapID=-1,szDisplay="光圈·解心语",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.15">
@@ -23975,7 +24124,7 @@
         <v>10390</v>
       </c>
       <c r="H177" t="s">
-        <v>1964</v>
+        <v>1771</v>
       </c>
       <c r="I177" t="s">
         <v>1555</v>
@@ -23984,11 +24133,11 @@
         <v>1</v>
       </c>
       <c r="T177" t="s">
-        <v>1965</v>
+        <v>1973</v>
       </c>
       <c r="U177" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=10390,szNote="酒杯·破巧言",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="酒杯·破巧言",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=10390,szNote="酒杯·破巧言",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="酒杯·破巧言",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.15">
@@ -23996,7 +24145,7 @@
         <v>10391</v>
       </c>
       <c r="H178" t="s">
-        <v>1966</v>
+        <v>1772</v>
       </c>
       <c r="I178" t="s">
         <v>1555</v>
@@ -24005,16 +24154,16 @@
         <v>1</v>
       </c>
       <c r="T178" t="s">
-        <v>1967</v>
+        <v>1974</v>
       </c>
       <c r="U178" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=10391,szNote="包袱·破巧言",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="包袱·破巧言",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=10391,szNote="包袱·破巧言",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="包袱·破巧言",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A179" t="s">
-        <v>1983</v>
+        <v>1787</v>
       </c>
       <c r="B179">
         <v>673</v>
@@ -24029,7 +24178,7 @@
         <v>11191</v>
       </c>
       <c r="H180" t="s">
-        <v>1968</v>
+        <v>1773</v>
       </c>
       <c r="I180" t="s">
         <v>1555</v>
@@ -24038,16 +24187,16 @@
         <v>1</v>
       </c>
       <c r="T180" t="s">
-        <v>1969</v>
+        <v>1975</v>
       </c>
       <c r="U180" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=11191,szNote="洞口·匿沙影",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="洞口·匿沙影",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=11191,szNote="洞口·匿沙影",col={0,255,255,},[17]={bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="洞口·匿沙影",nMaxDistance=60,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A181" t="s">
-        <v>1986</v>
+        <v>1790</v>
       </c>
       <c r="B181">
         <v>701</v>
@@ -24062,7 +24211,7 @@
         <v>11466</v>
       </c>
       <c r="H182" t="s">
-        <v>1987</v>
+        <v>1791</v>
       </c>
       <c r="I182" t="s">
         <v>1555</v>
@@ -24071,7 +24220,7 @@
         <v>1</v>
       </c>
       <c r="T182" t="s">
-        <v>1988</v>
+        <v>1792</v>
       </c>
       <c r="U182" t="str">
         <f t="shared" si="2"/>
@@ -24080,7 +24229,7 @@
     </row>
     <row r="183" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A183" t="s">
-        <v>1982</v>
+        <v>1786</v>
       </c>
       <c r="B183">
         <v>718</v>
@@ -24095,7 +24244,7 @@
         <v>11465</v>
       </c>
       <c r="H184" t="s">
-        <v>1984</v>
+        <v>1788</v>
       </c>
       <c r="I184" t="s">
         <v>1555</v>
@@ -24104,7 +24253,7 @@
         <v>1</v>
       </c>
       <c r="T184" t="s">
-        <v>1985</v>
+        <v>1789</v>
       </c>
       <c r="U184" t="str">
         <f t="shared" si="2"/>
@@ -24141,7 +24290,7 @@
         <v>822</v>
       </c>
       <c r="D1" t="s">
-        <v>1970</v>
+        <v>1774</v>
       </c>
       <c r="E1" t="s">
         <v>5</v>
@@ -24150,31 +24299,31 @@
         <v>1491</v>
       </c>
       <c r="G1" t="s">
-        <v>1971</v>
+        <v>1775</v>
       </c>
       <c r="H1" t="s">
-        <v>1972</v>
+        <v>1776</v>
       </c>
       <c r="I1" t="s">
-        <v>1973</v>
+        <v>1777</v>
       </c>
       <c r="J1" t="s">
-        <v>1974</v>
+        <v>1778</v>
       </c>
       <c r="K1" t="s">
-        <v>1975</v>
+        <v>1779</v>
       </c>
       <c r="L1" t="s">
-        <v>1976</v>
+        <v>1780</v>
       </c>
       <c r="M1" t="s">
-        <v>1977</v>
+        <v>1781</v>
       </c>
       <c r="N1" t="s">
-        <v>1978</v>
+        <v>1782</v>
       </c>
       <c r="O1" t="s">
-        <v>1979</v>
+        <v>1783</v>
       </c>
       <c r="P1" t="s">
         <v>1523</v>
@@ -24211,7 +24360,7 @@
         <v>1486</v>
       </c>
       <c r="C1" t="s">
-        <v>1970</v>
+        <v>1774</v>
       </c>
       <c r="D1" t="s">
         <v>5</v>
@@ -24220,31 +24369,31 @@
         <v>1491</v>
       </c>
       <c r="F1" t="s">
-        <v>1971</v>
+        <v>1775</v>
       </c>
       <c r="G1" t="s">
-        <v>1972</v>
+        <v>1776</v>
       </c>
       <c r="H1" t="s">
-        <v>1973</v>
+        <v>1777</v>
       </c>
       <c r="I1" t="s">
-        <v>1974</v>
+        <v>1778</v>
       </c>
       <c r="J1" t="s">
-        <v>1975</v>
+        <v>1779</v>
       </c>
       <c r="K1" t="s">
-        <v>1976</v>
+        <v>1780</v>
       </c>
       <c r="L1" t="s">
-        <v>1977</v>
+        <v>1781</v>
       </c>
       <c r="M1" t="s">
-        <v>1978</v>
+        <v>1782</v>
       </c>
       <c r="N1" t="s">
-        <v>1980</v>
+        <v>1784</v>
       </c>
       <c r="O1" t="s">
         <v>1523</v>

--- a/奇遇/宠物奇遇_通用全部.xlsx
+++ b/奇遇/宠物奇遇_通用全部.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="5"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="茗伊团队监控数据手册" sheetId="2" r:id="rId1"/>
@@ -5264,7 +5264,7 @@
     <t>酒葫芦·小果</t>
   </si>
   <si>
-    <t>{dwMapID=-1,szDisplay="酒葫芦·小果",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+    <t>{dwMapID=-1,szDisplay="酒葫芦·小果",nMaxDistance=120,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
   </si>
   <si>
     <t>一本书·蟹马蓝</t>
@@ -6036,7 +6036,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6162,13 +6162,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -6668,7 +6661,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -6677,10 +6670,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -6692,7 +6685,7 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -6704,7 +6697,7 @@
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -6716,7 +6709,7 @@
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -6728,7 +6721,7 @@
     <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -6740,7 +6733,7 @@
     <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -7247,7 +7240,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="16" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1782993541000,</v>
+        <v>nTimeStamp = 1783501548000,</v>
       </c>
       <c r="B4" s="19" t="s">
         <v>11</v>
@@ -20719,7 +20712,7 @@
       </c>
       <c r="U6" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=4582,szNote="酒葫芦·小果",col={0,255,255,},[17]={bCenterAlarm=true,bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="酒葫芦·小果",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=4582,szNote="酒葫芦·小果",col={0,255,255,},[17]={bCenterAlarm=true,bScreenHead=true,},[18]={},aFocus={{dwMapID=-1,szDisplay="酒葫芦·小果",nMaxDistance=120,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="7" spans="1:22">

--- a/奇遇/宠物奇遇_通用全部.xlsx
+++ b/奇遇/宠物奇遇_通用全部.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="6"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="茗伊团队监控数据手册" sheetId="2" r:id="rId1"/>
@@ -4928,7 +4928,7 @@
     <t>吴为有·石敢当</t>
   </si>
   <si>
-    <t>{dwMapID=-1,szDisplay="吴为有·石敢当",nMaxDistance=120,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
+    <t>{dwMapID=-1,szDisplay="吴为有·石敢当",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},</t>
   </si>
   <si>
     <t>唐御御·烟花戏</t>
@@ -7240,7 +7240,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="16" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1783501548000,</v>
+        <v>nTimeStamp = 1785251968000,</v>
       </c>
       <c r="B4" s="19" t="s">
         <v>11</v>
@@ -18981,7 +18981,7 @@
       </c>
       <c r="W65" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=11969,nFrame=47,szNote="吴为有·石敢当",col={0,255,255,},[3]={bCenterAlarm=true,bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="吴为有·石敢当",nMaxDistance=120,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+        <v>{dwID=11969,nFrame=47,szNote="吴为有·石敢当",col={0,255,255,},[3]={bCenterAlarm=true,bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="吴为有·石敢当",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="66" spans="1:23">
